--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="hmb" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
   <si>
     <t xml:space="preserve">dava tarihi</t>
   </si>
@@ -41,177 +41,26 @@
     <t xml:space="preserve">TL</t>
   </si>
   <si>
-    <t xml:space="preserve">hmb-davacı-icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toyota rav4</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025/15958</t>
   </si>
   <si>
-    <t xml:space="preserve">Rahmi-maphre – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hmb-davacı- 4.asliye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toyota rav4-itirazın kaldırılması</t>
+    <t xml:space="preserve">Maphre-rahmi kesici – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.asl. 2024/124</t>
   </si>
   <si>
     <t xml:space="preserve">2026/392</t>
   </si>
   <si>
-    <t xml:space="preserve">Rahmi-maphre – 4. asliye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bilirkişi raporu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duruşma 1-rapor itirazı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">önceki hasar kayıtları istenecek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ek rapor istenecek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bilirkişi raporu - ek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duruşma 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hmb-davalı-4. asliye ceza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mehmet şmşk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mehmet şmşk-4.asliye ceza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duruşma 1-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tanıklar zorla dinlenecek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tanıklarla olan dava dosyaları istencek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ali umut balcı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tr180006400000158001621930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hesap kapnış</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Talep TL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dosya TL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/3201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salih ant – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">örnek 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 araca haciz talebi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tensip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 günlük itiraz süre başlangıcı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankalara haciz talebi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emniyet haciz eklendi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ziraat bankası 339000 TL haciz işlendi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yapı krediden ödeme makbuzu yolladılar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-1-2026 tarihinde kapalı olan işbank hesabına havale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İşbank tan yapı krediye aynı gün iade edilmiş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">para hesaba geçmemiş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emrullah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11-04-2026 ödeme yapacakmış</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hesap no istemediler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-04-2026 boşaltacakmış</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/19105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 13 – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/1266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salih ant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 14 – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/12483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/22182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/264</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Maphre-rahmi kesici – </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -219,16 +68,155 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samed turgut - </t>
+      <t xml:space="preserve">4.asliye</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">2.sulh huku</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">tazminat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bilirkişi raporu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duruşma 1-rapor itirazı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">önceki hasar kayıtları istenecek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ek rapor istenecek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bilirkişi raporu - ek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duruşma 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mehmet şmşk-4.asliye ceza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duruşma 1-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tanıklar zorla dinlenecek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tanıklarla olan dava dosyaları istencek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ali umut balcı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tr180006400000158001621930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hesap kapnış</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Talep TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dosya TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">örnek 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 araca haciz talebi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tensip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 günlük itiraz süre başlangıcı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bankalara haciz talebi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emniyet haciz eklendi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ziraat bankası 339000 TL haciz işlendi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yapı krediden ödeme makbuzu yolladılar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-1-2026 tarihinde kapalı olan işbank hesabına havale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İşbank tan yapı krediye aynı gün iade edilmiş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">para hesaba geçmemiş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emrullah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-04-2026 ödeme yapacakmış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hesap no istemediler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-04-2026 boşaltacakmış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/19105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 13 – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/1266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 14 – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/12483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/22182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut - 2.sulh huku</t>
   </si>
   <si>
     <t xml:space="preserve">itirazın kaldırılması – 2024/12483 ve 2024/22182</t>
@@ -246,23 +234,7 @@
     <t xml:space="preserve">2024/22053</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">metin çelik</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve"> – icra</t>
-    </r>
+    <t xml:space="preserve">metin çelik – icra</t>
   </si>
   <si>
     <t xml:space="preserve">2025/559</t>
@@ -818,6 +790,18 @@
       <charset val="162"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -831,18 +815,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -1010,8 +982,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999"/>
-        <bgColor rgb="FFDDE8CB"/>
+        <fgColor rgb="FFFFE994"/>
+        <bgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -1022,26 +994,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FFA9D18E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE994"/>
-        <bgColor rgb="FFFFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FFA9D18E"/>
       </patternFill>
     </fill>
     <fill>
@@ -1066,6 +1032,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.7998"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.7999"/>
+        <bgColor rgb="FFDDE8CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1235,7 +1207,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="211">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1260,7 +1232,23 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1268,231 +1256,179 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1524,7 +1460,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1532,7 +1468,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1548,23 +1484,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1632,59 +1572,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1692,39 +1632,39 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1736,7 +1676,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1792,19 +1732,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1812,31 +1752,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1852,11 +1792,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1884,23 +1824,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="4" fillId="11" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1932,23 +1872,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1956,7 +1896,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1964,7 +1904,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2052,7 +1992,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2088,7 +2028,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2387,163 +2327,154 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="n">
+        <v>45905</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>455688</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>45902</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7" t="n">
-        <v>45905</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>455688</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="C7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>46044</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="9" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17"/>
+      <c r="C12" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="10" t="s">
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>0.413194444444444</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="C12" s="10" t="s">
+      <c r="D13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
-        <v>46177</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="C17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="22"/>
+      <c r="D19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="18" t="n">
         <v>46132</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="14"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-    </row>
+      <c r="B20" s="23" t="n">
+        <v>0.423611111111111</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2565,24 +2496,24 @@
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="26" t="n">
         <v>45725</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2599,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2611,32 +2542,32 @@
       <c r="F4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="6" t="n">
         <v>46076</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="20" t="n">
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>46088</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="19" t="n">
+      <c r="E5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>402082</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="12" t="n">
         <v>515608</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3"/>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
@@ -2646,10 +2577,10 @@
         <v>46120</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
@@ -2659,10 +2590,10 @@
         <v>46121</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
@@ -2672,10 +2603,10 @@
         <v>46120</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -2685,10 +2616,10 @@
         <v>46121</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
@@ -2699,7 +2630,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
@@ -2710,57 +2641,57 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
+        <v>37</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3"/>
       <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+        <v>39</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+        <v>40</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" s="5"/>
     </row>
@@ -2768,11 +2699,11 @@
       <c r="A18" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>46</v>
+      <c r="B18" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F18" s="5"/>
     </row>
@@ -2780,38 +2711,38 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="6" t="n">
         <v>45959</v>
       </c>
-      <c r="B20" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30" t="n">
+      <c r="B20" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33" t="n">
         <v>46009</v>
       </c>
-      <c r="F20" s="31" t="n">
+      <c r="F20" s="34" t="n">
         <v>196170</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="24"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3"/>
@@ -2819,34 +2750,34 @@
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="6" t="n">
         <v>45676</v>
       </c>
-      <c r="B24" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30" t="n">
+      <c r="B24" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33" t="n">
         <v>45698</v>
       </c>
-      <c r="F24" s="31"/>
+      <c r="F24" s="34"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3"/>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
     </row>
@@ -2856,79 +2787,79 @@
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="6" t="n">
         <v>45475</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33" t="n">
+        <v>45482</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="32"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
+        <v>45604</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="D30" s="32"/>
+      <c r="E30" s="33" t="n">
+        <v>45615</v>
+      </c>
+      <c r="F30" s="34" t="n">
+        <v>140835</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="32"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>45704</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30" t="n">
-        <v>45482</v>
-      </c>
-      <c r="F28" s="31" t="n">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="19" t="s">
+      <c r="C32" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="n">
-        <v>45604</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="30" t="n">
-        <v>45615</v>
-      </c>
-      <c r="F30" s="31" t="n">
-        <v>140835</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="31"/>
-    </row>
-    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="24"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="3"/>
       <c r="C33" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="5"/>
@@ -2939,23 +2870,23 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="24"/>
+        <v>60</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="28" t="n">
         <v>46042</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="24" t="s">
-        <v>66</v>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="31"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2969,25 +2900,25 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="6" t="n">
         <v>45603</v>
       </c>
-      <c r="B38" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="30" t="n">
+      <c r="B38" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="32"/>
+      <c r="E38" s="33" t="n">
         <v>45615</v>
       </c>
-      <c r="F38" s="31"/>
+      <c r="F38" s="34"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="5" t="n">
@@ -2998,11 +2929,11 @@
       <c r="A40" s="1" t="n">
         <v>45704</v>
       </c>
-      <c r="B40" s="38" t="s">
-        <v>69</v>
+      <c r="B40" s="22" t="s">
+        <v>65</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
@@ -3010,13 +2941,13 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="3"/>
       <c r="C41" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>86000</v>
       </c>
-      <c r="F41" s="39" t="s">
-        <v>72</v>
+      <c r="F41" s="37" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3024,10 +2955,10 @@
         <v>46086</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="5"/>
@@ -3035,7 +2966,7 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3"/>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="5"/>
@@ -3043,25 +2974,25 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3"/>
       <c r="C44" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="40" t="n">
+      <c r="A45" s="18" t="n">
         <v>46196</v>
       </c>
-      <c r="B45" s="41" t="n">
+      <c r="B45" s="23" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="38"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="24" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,25 +3001,25 @@
       <c r="F46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="6" t="n">
         <v>45588</v>
       </c>
-      <c r="B47" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="30" t="n">
+      <c r="B47" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="32"/>
+      <c r="E47" s="33" t="n">
         <v>45596</v>
       </c>
-      <c r="F47" s="31"/>
+      <c r="F47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3"/>
       <c r="C48" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="5"/>
@@ -3097,11 +3028,11 @@
       <c r="A49" s="1" t="n">
         <v>45704</v>
       </c>
-      <c r="B49" s="38" t="s">
-        <v>81</v>
+      <c r="B49" s="22" t="s">
+        <v>77</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="5"/>
@@ -3111,9 +3042,9 @@
         <v>46021</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="26"/>
+        <v>79</v>
+      </c>
+      <c r="C50" s="30"/>
       <c r="E50" s="4"/>
       <c r="F50" s="5"/>
     </row>
@@ -3122,26 +3053,26 @@
         <v>46036</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="28" t="n">
         <v>46155</v>
       </c>
-      <c r="B52" s="25"/>
-      <c r="C52" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D52" s="27"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="31"/>
       <c r="E52" s="4"/>
       <c r="F52" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3155,27 +3086,27 @@
       <c r="F54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="6" t="n">
         <v>45475</v>
       </c>
-      <c r="B55" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="30" t="n">
+      <c r="B55" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="32"/>
+      <c r="E55" s="33" t="n">
         <v>45482</v>
       </c>
-      <c r="F55" s="31" t="n">
+      <c r="F55" s="34" t="n">
         <v>158437</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="3"/>
       <c r="C56" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="5"/>
@@ -3184,19 +3115,19 @@
       <c r="A57" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>87</v>
+      <c r="B57" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="3"/>
-      <c r="C58" s="44" t="s">
-        <v>71</v>
+      <c r="C58" s="25" t="s">
+        <v>67</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="5"/>
@@ -3207,23 +3138,23 @@
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="45" t="n">
+      <c r="A60" s="39" t="n">
         <v>46175</v>
       </c>
-      <c r="B60" s="41" t="n">
+      <c r="B60" s="23" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C60" s="42" t="s">
-        <v>90</v>
+      <c r="C60" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,35 +3168,35 @@
       <c r="F62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="6" t="n">
         <v>46205</v>
       </c>
-      <c r="B63" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D63" s="29"/>
-      <c r="E63" s="30" t="n">
+      <c r="B63" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" s="32"/>
+      <c r="E63" s="33" t="n">
         <v>45482</v>
       </c>
-      <c r="F63" s="31" t="n">
+      <c r="F63" s="34" t="n">
         <v>86000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="3"/>
       <c r="C64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="32"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="26"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="30"/>
       <c r="E65" s="4"/>
       <c r="F65" s="5"/>
     </row>
@@ -3275,267 +3206,261 @@
       <c r="F66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="34"/>
-      <c r="B67" s="46"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="37"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="2"/>
       <c r="E67" s="4"/>
       <c r="F67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18" t="n">
+      <c r="A68" s="6" t="n">
         <v>45342</v>
       </c>
-      <c r="B68" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E68" s="33"/>
-      <c r="F68" s="31"/>
+      <c r="B68" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="36"/>
+      <c r="F68" s="34"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="34"/>
-      <c r="B69" s="46"/>
-      <c r="C69" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D69" s="37"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="2"/>
       <c r="E69" s="4"/>
       <c r="F69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34" t="n">
+      <c r="A70" s="1" t="n">
         <v>45450</v>
       </c>
-      <c r="B70" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C70" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>46</v>
+      <c r="B70" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="34" t="n">
+      <c r="A71" s="1" t="n">
         <v>45680</v>
       </c>
-      <c r="B71" s="46"/>
-      <c r="C71" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>98</v>
+      <c r="B71" s="3"/>
+      <c r="C71" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="34" t="n">
+      <c r="A72" s="1" t="n">
         <v>45726</v>
       </c>
-      <c r="B72" s="48"/>
-      <c r="C72" s="0" t="s">
-        <v>99</v>
+      <c r="C72" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="n">
+      <c r="A73" s="28" t="n">
         <v>45765</v>
       </c>
-      <c r="B73" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="C73" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="24" t="s">
-        <v>66</v>
+      <c r="B73" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="31"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="34"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" s="37"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="4"/>
       <c r="F74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="34"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="37"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="2"/>
       <c r="E75" s="4"/>
       <c r="F75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="34"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="37"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="2"/>
       <c r="E76" s="4"/>
       <c r="F76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="50" t="n">
+      <c r="A77" s="42" t="n">
         <v>45588</v>
       </c>
-      <c r="B77" s="51" t="s">
+      <c r="B77" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" s="45"/>
+      <c r="E77" s="46"/>
+      <c r="F77" s="47"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="42"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="45"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="47"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="48" t="n">
+        <v>45438</v>
+      </c>
+      <c r="B79" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="C79" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="D79" s="51"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="53"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="48"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="51"/>
+      <c r="E80" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="F80" s="53" t="n">
+        <v>193500</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="48" t="n">
+        <v>45288</v>
+      </c>
+      <c r="B81" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="C77" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D77" s="53"/>
-      <c r="E77" s="54"/>
-      <c r="F77" s="55"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="50"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="D78" s="53"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="55"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="56" t="n">
-        <v>45438</v>
-      </c>
-      <c r="B79" s="57" t="s">
+      <c r="C81" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="C79" s="58" t="s">
+      <c r="D81" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" s="52"/>
+      <c r="F81" s="53"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="48"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="55"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="53"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="48" t="n">
+        <v>45148</v>
+      </c>
+      <c r="B83" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="61"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="56"/>
-      <c r="B80" s="57"/>
-      <c r="C80" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="D80" s="59"/>
-      <c r="E80" s="60" t="s">
+      <c r="C83" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="F80" s="61" t="n">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="56" t="n">
-        <v>45288</v>
-      </c>
-      <c r="B81" s="62" t="s">
+      <c r="D83" s="55"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="53"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="48"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="55"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="53"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="48" t="n">
+        <v>44928</v>
+      </c>
+      <c r="B85" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="C81" s="63" t="s">
+      <c r="C85" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="55"/>
+      <c r="E85" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="F85" s="53" t="n">
+        <v>24316</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="48"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="55"/>
+      <c r="D86" s="55"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="53"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="48" t="n">
+        <v>44333</v>
+      </c>
+      <c r="B87" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="D81" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="E81" s="60"/>
-      <c r="F81" s="61"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="56"/>
-      <c r="B82" s="62"/>
-      <c r="C82" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="D82" s="64"/>
-      <c r="E82" s="60"/>
-      <c r="F82" s="61"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="56" t="n">
-        <v>45148</v>
-      </c>
-      <c r="B83" s="62" t="s">
+      <c r="C87" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C83" s="63" t="s">
-        <v>110</v>
-      </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="60"/>
-      <c r="F83" s="61"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="56"/>
-      <c r="B84" s="62"/>
-      <c r="C84" s="63"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="60"/>
-      <c r="F84" s="61"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="56" t="n">
-        <v>44928</v>
-      </c>
-      <c r="B85" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="63" t="s">
-        <v>105</v>
-      </c>
-      <c r="D85" s="64"/>
-      <c r="E85" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="F85" s="61" t="n">
-        <v>24316</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="56"/>
-      <c r="B86" s="62"/>
-      <c r="C86" s="63"/>
-      <c r="D86" s="64"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="61"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="56" t="n">
-        <v>44333</v>
-      </c>
-      <c r="B87" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="C87" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="D87" s="64"/>
-      <c r="E87" s="60"/>
-      <c r="F87" s="61"/>
+      <c r="D87" s="55"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="53"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="56"/>
-      <c r="B88" s="62"/>
-      <c r="C88" s="63"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="60"/>
-      <c r="F88" s="61"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="55"/>
+      <c r="D88" s="55"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="53"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="3"/>
@@ -3569,8 +3494,8 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="3"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="65"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="56"/>
       <c r="F95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3579,44 +3504,37 @@
       <c r="F96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0"/>
-      <c r="B97" s="48"/>
-      <c r="C97" s="0"/>
+      <c r="A97" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="0"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
       <c r="F100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
       <c r="F106" s="2"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="0"/>
-      <c r="C119" s="0"/>
+      <c r="B119" s="2"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="0"/>
-      <c r="C120" s="0"/>
+      <c r="B120" s="2"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="0"/>
-      <c r="C121" s="0"/>
+      <c r="B121" s="2"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="0"/>
-      <c r="C122" s="0"/>
+      <c r="B122" s="2"/>
     </row>
     <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3689,7 +3607,7 @@
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="66" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="57" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="4"/>
@@ -3699,105 +3617,105 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="58"/>
+      <c r="B2" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="58"/>
+      <c r="B4" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67"/>
-      <c r="B2" s="71" t="s">
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="H4" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="67"/>
-      <c r="B4" s="72" t="s">
+      <c r="I4" s="59"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58"/>
+      <c r="B5" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="71" t="s">
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="71" t="s">
+      <c r="H5" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="59"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58"/>
+      <c r="B7" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="71" t="s">
+      <c r="C7" s="57" t="n">
+        <v>45827</v>
+      </c>
+      <c r="D7" s="60" t="s">
         <v>120</v>
-      </c>
-      <c r="I4" s="68"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67"/>
-      <c r="B5" s="72" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="68"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67"/>
-      <c r="B7" s="74" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="66" t="n">
-        <v>45827</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>124</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>9</v>
@@ -3805,77 +3723,77 @@
       <c r="F7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="59"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58"/>
+      <c r="B9" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="57" t="n">
+        <v>45939</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" s="59"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="58"/>
+      <c r="B10" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="60" t="n">
+        <v>45939</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" s="61"/>
+      <c r="H10" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="59"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58"/>
+      <c r="B11" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="60" t="n">
+        <v>45952</v>
+      </c>
+      <c r="D11" s="59" t="s">
         <v>125</v>
-      </c>
-      <c r="I7" s="68"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="67"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="67"/>
-      <c r="B9" s="75" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="66" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D9" s="76" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="76" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="76" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="68"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="67"/>
-      <c r="B10" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="69" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D10" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="68" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="68" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" s="70"/>
-      <c r="H10" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" s="68"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="67"/>
-      <c r="B11" s="75" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="69" t="n">
-        <v>45952</v>
-      </c>
-      <c r="D11" s="68" t="s">
-        <v>129</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>9</v>
@@ -3883,664 +3801,664 @@
       <c r="F11" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68" t="s">
+      <c r="G11" s="59"/>
+      <c r="H11" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="61"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="58"/>
+      <c r="B12" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="60" t="n">
+        <v>45952</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="61"/>
+      <c r="H12" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="61"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="61"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="58"/>
+      <c r="I14" s="59"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58"/>
+      <c r="I15" s="59"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="68"/>
+      <c r="J16" s="25"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="69"/>
+      <c r="B17" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="70"/>
+      <c r="E17" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="72"/>
+      <c r="G17" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="I11" s="70"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="67"/>
-      <c r="B12" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="69" t="n">
-        <v>45952</v>
-      </c>
-      <c r="D12" s="68" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="68" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="68" t="n">
-        <v>35</v>
-      </c>
-      <c r="G12" s="70"/>
-      <c r="H12" s="68" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" s="70"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="67"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="70"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="67"/>
-      <c r="I14" s="68"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="67"/>
-      <c r="I15" s="68"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="77"/>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="78"/>
-      <c r="B17" s="79" t="s">
+      <c r="I17" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="J17" s="74"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="77" t="n">
+        <v>45342</v>
+      </c>
+      <c r="D18" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="81"/>
-      <c r="G17" s="82" t="s">
+      <c r="E18" s="78"/>
+      <c r="F18" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="H17" s="79" t="s">
+      <c r="G18" s="80"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="74"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="75"/>
+      <c r="B19" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="I17" s="79" t="s">
+      <c r="C19" s="77" t="n">
+        <v>45537</v>
+      </c>
+      <c r="D19" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="83" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="84" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="85" t="n">
-        <v>45342</v>
-      </c>
-      <c r="D18" s="83" t="s">
+      <c r="E19" s="78"/>
+      <c r="F19" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87" t="s">
+      <c r="G19" s="80" t="n">
+        <v>45691</v>
+      </c>
+      <c r="H19" s="78"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="74"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="85" t="s">
         <v>137</v>
-      </c>
-      <c r="G18" s="88"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="83"/>
-      <c r="B19" s="89" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="85" t="n">
-        <v>45537</v>
-      </c>
-      <c r="D19" s="83" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="86"/>
-      <c r="F19" s="90" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" s="88" t="n">
-        <v>45691</v>
-      </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93" t="s">
-        <v>141</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="8"/>
+      <c r="J20" s="74"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="C21" s="94" t="n">
+      <c r="C21" s="86" t="n">
         <v>45726</v>
       </c>
-      <c r="D21" s="95" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="8"/>
+      <c r="D21" s="87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="74"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="8"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="74"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="77"/>
-      <c r="J23" s="8"/>
+      <c r="A23" s="68"/>
+      <c r="J23" s="74"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="102"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="77"/>
+      <c r="A25" s="68"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="77"/>
+      <c r="A26" s="68"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="105"/>
-      <c r="B27" s="106" t="s">
+      <c r="A27" s="97"/>
+      <c r="B27" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="98"/>
+      <c r="E27" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="100"/>
+      <c r="G27" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="98" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="106"/>
-      <c r="E27" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="108"/>
-      <c r="G27" s="109" t="s">
-        <v>133</v>
-      </c>
-      <c r="H27" s="106" t="s">
-        <v>134</v>
-      </c>
-      <c r="I27" s="106" t="s">
-        <v>135</v>
-      </c>
-      <c r="J27" s="110"/>
+      <c r="J27" s="102"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="77" t="s">
-        <v>143</v>
+      <c r="A28" s="68" t="s">
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="112" t="n">
+        <v>140</v>
+      </c>
+      <c r="H28" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="104" t="n">
         <v>45712</v>
       </c>
-      <c r="J28" s="110"/>
+      <c r="J28" s="102"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="77"/>
-      <c r="J29" s="110"/>
+      <c r="A29" s="68"/>
+      <c r="J29" s="102"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
-      <c r="B30" s="15"/>
+      <c r="B30" s="25"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="113" t="s">
+      <c r="I30" s="105" t="s">
+        <v>142</v>
+      </c>
+      <c r="J30" s="102"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="106"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="102"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="68"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="68"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="109"/>
+      <c r="B34" s="110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="110"/>
+      <c r="E34" s="112" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="112"/>
+      <c r="G34" s="113" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" s="110" t="s">
+        <v>131</v>
+      </c>
+      <c r="J34" s="74"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="106" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="95" t="n">
+        <v>45475</v>
+      </c>
+      <c r="D35" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="114" t="n">
+        <v>97</v>
+      </c>
+      <c r="F35" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="I35" s="96" t="n">
+        <v>45705</v>
+      </c>
+      <c r="J35" s="74"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="103"/>
+      <c r="B36" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="95" t="n">
+        <v>45604</v>
+      </c>
+      <c r="D36" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="114" t="n">
+        <v>178</v>
+      </c>
+      <c r="F36" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="H36" s="116" t="s">
         <v>146</v>
       </c>
-      <c r="J30" s="110"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="114"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="114"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="110"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="77"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="77"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="117"/>
-      <c r="B34" s="118" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="119" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="118"/>
-      <c r="E34" s="120" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="120"/>
-      <c r="G34" s="121" t="s">
-        <v>133</v>
-      </c>
-      <c r="H34" s="118" t="s">
-        <v>134</v>
-      </c>
-      <c r="I34" s="118" t="s">
-        <v>135</v>
-      </c>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="114" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="84" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="103" t="n">
-        <v>45475</v>
-      </c>
-      <c r="D35" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="122" t="n">
-        <v>97</v>
-      </c>
-      <c r="F35" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="H35" s="111" t="s">
-        <v>149</v>
-      </c>
-      <c r="I35" s="104" t="n">
+      <c r="I36" s="117" t="n">
         <v>45705</v>
       </c>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="111"/>
-      <c r="B36" s="123" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="103" t="n">
-        <v>45604</v>
-      </c>
-      <c r="D36" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="122" t="n">
-        <v>178</v>
-      </c>
-      <c r="F36" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="124" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="125" t="n">
-        <v>45705</v>
-      </c>
-      <c r="J36" s="8"/>
+      <c r="J36" s="74"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
-      <c r="B37" s="126" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="66" t="n">
+      <c r="B37" s="118" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="57" t="n">
         <v>45704</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="J37" s="8"/>
+      <c r="D37" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="J37" s="74"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C38" s="57" t="n">
         <v>45705</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="J38" s="8"/>
+      <c r="J38" s="74"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
-      <c r="C39" s="127"/>
+      <c r="C39" s="119"/>
       <c r="D39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="J39" s="8"/>
+      <c r="J39" s="74"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
-      <c r="C40" s="127" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" s="38" t="s">
-        <v>154</v>
+      <c r="C40" s="119" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="J40" s="8"/>
+      <c r="J40" s="74"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
-      <c r="C41" s="128" t="n">
+      <c r="C41" s="120" t="n">
         <v>45717</v>
       </c>
-      <c r="D41" s="129" t="s">
+      <c r="D41" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="130" t="s">
-        <v>155</v>
-      </c>
-      <c r="F41" s="129"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="129" t="s">
-        <v>156</v>
-      </c>
-      <c r="I41" s="132" t="s">
-        <v>157</v>
-      </c>
-      <c r="J41" s="8"/>
+      <c r="E41" s="122" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="121"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="121" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" s="124" t="s">
+        <v>153</v>
+      </c>
+      <c r="J41" s="74"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
-      <c r="C42" s="133"/>
+      <c r="C42" s="125"/>
       <c r="D42" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J42" s="74"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="126"/>
+      <c r="B43" s="127" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="128" t="n">
+        <v>45805</v>
+      </c>
+      <c r="D43" s="129" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="E43" s="126" t="s">
+        <v>157</v>
+      </c>
+      <c r="F43" s="126"/>
+      <c r="G43" s="130"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="130"/>
+      <c r="J43" s="131"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="103"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="132" t="n">
+        <v>45805</v>
+      </c>
+      <c r="D44" s="114" t="s">
         <v>158</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="134"/>
-      <c r="B43" s="135" t="s">
-        <v>160</v>
-      </c>
-      <c r="C43" s="136" t="n">
-        <v>45805</v>
-      </c>
-      <c r="D43" s="137" t="n">
-        <v>0.409722222222222</v>
-      </c>
-      <c r="E43" s="134" t="s">
-        <v>161</v>
-      </c>
-      <c r="F43" s="134"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="134"/>
-      <c r="I43" s="138"/>
-      <c r="J43" s="139"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="111"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="140" t="n">
-        <v>45805</v>
-      </c>
-      <c r="D44" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" s="122"/>
-      <c r="F44" s="122"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="8"/>
+      <c r="E44" s="114"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="133"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="74"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
-      <c r="C46" s="127"/>
+      <c r="C46" s="119"/>
       <c r="D46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="117"/>
-      <c r="B47" s="118" t="s">
+      <c r="A47" s="109"/>
+      <c r="B47" s="110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="110"/>
+      <c r="E47" s="112" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="112"/>
+      <c r="G47" s="113" t="s">
+        <v>129</v>
+      </c>
+      <c r="H47" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="I47" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="119" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="118"/>
-      <c r="E47" s="120" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="120"/>
-      <c r="G47" s="121" t="s">
+      <c r="J47" s="74"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="134" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D48" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" s="74"/>
+      <c r="F48" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="H47" s="118" t="s">
-        <v>134</v>
-      </c>
-      <c r="I47" s="118" t="s">
-        <v>135</v>
-      </c>
-      <c r="J47" s="8"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="111" t="s">
-        <v>147</v>
-      </c>
-      <c r="B48" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="142" t="n">
-        <v>45588</v>
-      </c>
-      <c r="D48" s="122" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="H48" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="I48" s="104" t="n">
+      <c r="H48" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="I48" s="96" t="n">
         <v>45630</v>
       </c>
-      <c r="J48" s="8"/>
+      <c r="J48" s="74"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="111"/>
-      <c r="B49" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="103"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="111"/>
-      <c r="H49" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="I49" s="104" t="n">
+      <c r="A49" s="103"/>
+      <c r="B49" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="95"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="103"/>
+      <c r="H49" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="I49" s="96" t="n">
         <v>45630</v>
       </c>
-      <c r="J49" s="8"/>
+      <c r="J49" s="74"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="111"/>
-      <c r="B50" s="126" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="143" t="n">
+      <c r="A50" s="103"/>
+      <c r="B50" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="135" t="n">
         <v>45704</v>
       </c>
-      <c r="D50" s="38" t="s">
-        <v>166</v>
+      <c r="D50" s="22" t="s">
+        <v>162</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="J50" s="8"/>
+      <c r="J50" s="74"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C51" s="57" t="n">
         <v>45709</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="J51" s="8"/>
+      <c r="J51" s="74"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
-      <c r="C52" s="127" t="s">
-        <v>153</v>
+      <c r="C52" s="119" t="s">
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="J52" s="8"/>
+      <c r="J52" s="74"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
-      <c r="C53" s="127" t="n">
+      <c r="C53" s="119" t="n">
         <v>45712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="J53" s="8"/>
+      <c r="J53" s="74"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
-      <c r="C54" s="144" t="n">
+      <c r="C54" s="136" t="n">
         <v>45717</v>
       </c>
-      <c r="D54" s="145" t="s">
+      <c r="D54" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="146" t="s">
-        <v>155</v>
-      </c>
-      <c r="F54" s="145"/>
-      <c r="G54" s="147"/>
-      <c r="H54" s="145" t="s">
-        <v>156</v>
-      </c>
-      <c r="I54" s="148"/>
-      <c r="J54" s="8"/>
+      <c r="E54" s="138" t="s">
+        <v>151</v>
+      </c>
+      <c r="F54" s="137"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="137" t="s">
+        <v>152</v>
+      </c>
+      <c r="I54" s="140"/>
+      <c r="J54" s="74"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="149"/>
-      <c r="H55" s="150"/>
-      <c r="I55" s="149"/>
-      <c r="J55" s="8"/>
+      <c r="G55" s="141"/>
+      <c r="H55" s="142"/>
+      <c r="I55" s="141"/>
+      <c r="J55" s="74"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F56" s="1"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="150"/>
-      <c r="I56" s="151" t="s">
-        <v>157</v>
-      </c>
-      <c r="J56" s="8"/>
+      <c r="G56" s="141"/>
+      <c r="H56" s="142"/>
+      <c r="I56" s="143" t="s">
+        <v>153</v>
+      </c>
+      <c r="J56" s="74"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
-      <c r="B57" s="152" t="s">
-        <v>160</v>
-      </c>
-      <c r="C57" s="153" t="n">
+      <c r="B57" s="144" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="145" t="n">
         <v>45805</v>
       </c>
-      <c r="D57" s="154" t="n">
+      <c r="D57" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="8"/>
+      <c r="J57" s="74"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="111"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="155" t="n">
+      <c r="A58" s="103"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="147" t="n">
         <v>45805</v>
       </c>
-      <c r="D58" s="111" t="s">
-        <v>170</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="104"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="8"/>
+      <c r="D58" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="96"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="96"/>
+      <c r="J58" s="74"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="127"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="119"/>
       <c r="D59" s="3"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="J59" s="15"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="127"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="119"/>
       <c r="D60" s="3"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="J60" s="15"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
@@ -4550,849 +4468,849 @@
       <c r="H61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="156"/>
-      <c r="B62" s="157" t="s">
+      <c r="A62" s="148"/>
+      <c r="B62" s="149" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="149"/>
+      <c r="E62" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="151"/>
+      <c r="G62" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="H62" s="149" t="s">
+        <v>130</v>
+      </c>
+      <c r="I62" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="158" t="s">
-        <v>132</v>
-      </c>
-      <c r="D62" s="157"/>
-      <c r="E62" s="159" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="159"/>
-      <c r="G62" s="160" t="s">
+      <c r="J62" s="153"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="106" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" s="76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="95" t="n">
+        <v>45475</v>
+      </c>
+      <c r="D63" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E63" s="114" t="n">
+        <v>214</v>
+      </c>
+      <c r="F63" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="H62" s="157" t="s">
-        <v>134</v>
-      </c>
-      <c r="I62" s="157" t="s">
-        <v>135</v>
-      </c>
-      <c r="J62" s="161"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="114" t="s">
-        <v>171</v>
-      </c>
-      <c r="B63" s="84" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" s="103" t="n">
-        <v>45475</v>
-      </c>
-      <c r="D63" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="122" t="n">
-        <v>214</v>
-      </c>
-      <c r="F63" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="H63" s="111" t="s">
-        <v>172</v>
-      </c>
-      <c r="I63" s="104" t="n">
+      <c r="H63" s="103" t="s">
+        <v>168</v>
+      </c>
+      <c r="I63" s="96" t="n">
         <v>45702</v>
       </c>
-      <c r="J63" s="161"/>
+      <c r="J63" s="153"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="114"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="103"/>
-      <c r="D64" s="162" t="n">
+      <c r="A64" s="106"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="154" t="n">
         <v>158437</v>
       </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="111"/>
-      <c r="H64" s="124" t="s">
-        <v>173</v>
-      </c>
-      <c r="I64" s="104" t="n">
+      <c r="E64" s="74"/>
+      <c r="F64" s="103"/>
+      <c r="H64" s="116" t="s">
+        <v>169</v>
+      </c>
+      <c r="I64" s="96" t="n">
         <v>45702</v>
       </c>
-      <c r="J64" s="161"/>
+      <c r="J64" s="153"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
-      <c r="B65" s="126" t="s">
-        <v>87</v>
-      </c>
-      <c r="C65" s="66" t="n">
+      <c r="B65" s="118" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="57" t="n">
         <v>45704</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="J65" s="161"/>
+      <c r="J65" s="153"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C66" s="57" t="n">
         <v>45705</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="J66" s="161"/>
+      <c r="J66" s="153"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="J67" s="161"/>
+      <c r="J67" s="153"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
-      <c r="C68" s="127" t="s">
-        <v>153</v>
-      </c>
-      <c r="D68" s="38" t="s">
-        <v>177</v>
+      <c r="C68" s="119" t="s">
+        <v>149</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>173</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="J68" s="161"/>
+      <c r="J68" s="153"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
-      <c r="C69" s="163" t="n">
+      <c r="C69" s="155" t="n">
         <v>45711</v>
       </c>
-      <c r="D69" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" s="164"/>
-      <c r="F69" s="164"/>
-      <c r="G69" s="165"/>
-      <c r="H69" s="164"/>
-      <c r="I69" s="166"/>
-      <c r="J69" s="161"/>
+      <c r="D69" s="156" t="s">
+        <v>174</v>
+      </c>
+      <c r="E69" s="156"/>
+      <c r="F69" s="156"/>
+      <c r="G69" s="157"/>
+      <c r="H69" s="156"/>
+      <c r="I69" s="158"/>
+      <c r="J69" s="153"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="133" t="s">
-        <v>179</v>
-      </c>
-      <c r="D70" s="150"/>
-      <c r="E70" s="150"/>
-      <c r="F70" s="150"/>
-      <c r="G70" s="149"/>
-      <c r="H70" s="150"/>
-      <c r="I70" s="149"/>
-      <c r="J70" s="161"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="125" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="142"/>
+      <c r="E70" s="142"/>
+      <c r="F70" s="142"/>
+      <c r="G70" s="141"/>
+      <c r="H70" s="142"/>
+      <c r="I70" s="141"/>
+      <c r="J70" s="153"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="133" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="150"/>
-      <c r="F71" s="150"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="150"/>
-      <c r="I71" s="149"/>
-      <c r="J71" s="161"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="125" t="s">
+        <v>176</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E71" s="142"/>
+      <c r="F71" s="142"/>
+      <c r="G71" s="141"/>
+      <c r="H71" s="142"/>
+      <c r="I71" s="141"/>
+      <c r="J71" s="153"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="113" t="s">
-        <v>183</v>
-      </c>
-      <c r="J72" s="161"/>
+      <c r="I72" s="105" t="s">
+        <v>179</v>
+      </c>
+      <c r="J72" s="153"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
-      <c r="C73" s="133"/>
+      <c r="C73" s="125"/>
       <c r="D73" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="J73" s="161"/>
+      <c r="I73" s="105" t="s">
+        <v>181</v>
+      </c>
+      <c r="J73" s="153"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
-      <c r="B74" s="135" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="167" t="n">
+      <c r="B74" s="127" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="159" t="n">
         <v>45792</v>
       </c>
-      <c r="D74" s="137" t="n">
+      <c r="D74" s="129" t="n">
         <v>0.399305555555556</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="J74" s="161"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="J74" s="153"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="168"/>
-      <c r="B75" s="169" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="170" t="n">
+      <c r="A75" s="160"/>
+      <c r="B75" s="161" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="162" t="n">
         <v>45939</v>
       </c>
-      <c r="D75" s="171" t="n">
+      <c r="D75" s="163" t="n">
         <v>0.402777777777778</v>
       </c>
-      <c r="E75" s="172"/>
-      <c r="F75" s="172"/>
-      <c r="G75" s="173" t="s">
-        <v>186</v>
-      </c>
-      <c r="H75" s="173" t="s">
-        <v>187</v>
-      </c>
-      <c r="I75" s="173" t="s">
-        <v>188</v>
-      </c>
-      <c r="J75" s="161"/>
+      <c r="E75" s="164"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="165" t="s">
+        <v>182</v>
+      </c>
+      <c r="H75" s="165" t="s">
+        <v>183</v>
+      </c>
+      <c r="I75" s="165" t="s">
+        <v>184</v>
+      </c>
+      <c r="J75" s="153"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
-      <c r="C76" s="127"/>
+      <c r="C76" s="119"/>
       <c r="D76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
-      <c r="C77" s="127"/>
+      <c r="C77" s="119"/>
       <c r="D77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="174"/>
-      <c r="B78" s="175" t="s">
+      <c r="A78" s="166"/>
+      <c r="B78" s="167" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" s="168" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" s="167"/>
+      <c r="E78" s="169" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="169"/>
+      <c r="G78" s="170" t="s">
+        <v>129</v>
+      </c>
+      <c r="H78" s="167" t="s">
+        <v>130</v>
+      </c>
+      <c r="I78" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="C78" s="176" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" s="175"/>
-      <c r="E78" s="177" t="s">
-        <v>4</v>
-      </c>
-      <c r="F78" s="177"/>
-      <c r="G78" s="178" t="s">
+      <c r="J78" s="102"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="103" t="s">
+        <v>167</v>
+      </c>
+      <c r="B79" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="95" t="n">
+        <v>45676</v>
+      </c>
+      <c r="D79" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" s="103"/>
+      <c r="F79" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="H78" s="175" t="s">
-        <v>134</v>
-      </c>
-      <c r="I78" s="175" t="s">
-        <v>135</v>
-      </c>
-      <c r="J78" s="110"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="111" t="s">
-        <v>171</v>
-      </c>
-      <c r="B79" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="103" t="n">
-        <v>45676</v>
-      </c>
-      <c r="D79" s="122" t="s">
-        <v>163</v>
-      </c>
-      <c r="E79" s="111"/>
-      <c r="F79" s="111" t="s">
-        <v>137</v>
-      </c>
       <c r="H79" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J79" s="110"/>
+        <v>185</v>
+      </c>
+      <c r="J79" s="102"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="111" t="s">
-        <v>171</v>
-      </c>
-      <c r="B80" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="C80" s="103"/>
-      <c r="D80" s="111"/>
-      <c r="E80" s="111"/>
-      <c r="F80" s="111"/>
-      <c r="H80" s="124" t="s">
-        <v>190</v>
-      </c>
-      <c r="I80" s="179" t="n">
+      <c r="A80" s="103" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80" s="95"/>
+      <c r="D80" s="103"/>
+      <c r="E80" s="103"/>
+      <c r="F80" s="103"/>
+      <c r="H80" s="116" t="s">
+        <v>186</v>
+      </c>
+      <c r="I80" s="171" t="n">
         <v>45714</v>
       </c>
-      <c r="J80" s="110"/>
+      <c r="J80" s="102"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
-      <c r="B81" s="15"/>
+      <c r="B81" s="25"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="J81" s="110"/>
+      <c r="J81" s="102"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
-      <c r="B82" s="15"/>
+      <c r="B82" s="25"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="113" t="s">
-        <v>146</v>
-      </c>
-      <c r="J82" s="110"/>
+      <c r="I82" s="105" t="s">
+        <v>142</v>
+      </c>
+      <c r="J82" s="102"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="114"/>
-      <c r="B83" s="110"/>
-      <c r="C83" s="115"/>
-      <c r="D83" s="114"/>
-      <c r="E83" s="114"/>
-      <c r="F83" s="114"/>
-      <c r="G83" s="116"/>
-      <c r="H83" s="114"/>
-      <c r="I83" s="116"/>
-      <c r="J83" s="110"/>
+      <c r="A83" s="106"/>
+      <c r="B83" s="102"/>
+      <c r="C83" s="107"/>
+      <c r="D83" s="106"/>
+      <c r="E83" s="106"/>
+      <c r="F83" s="106"/>
+      <c r="G83" s="108"/>
+      <c r="H83" s="106"/>
+      <c r="I83" s="108"/>
+      <c r="J83" s="102"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
-      <c r="C84" s="127"/>
+      <c r="C84" s="119"/>
       <c r="D84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
-      <c r="C85" s="127"/>
+      <c r="C85" s="119"/>
       <c r="D85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="156"/>
-      <c r="B86" s="157" t="s">
+      <c r="A86" s="148"/>
+      <c r="B86" s="149" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="149"/>
+      <c r="E86" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" s="151"/>
+      <c r="G86" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="H86" s="149" t="s">
+        <v>130</v>
+      </c>
+      <c r="I86" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="C86" s="158" t="s">
-        <v>132</v>
-      </c>
-      <c r="D86" s="157"/>
-      <c r="E86" s="159" t="s">
-        <v>4</v>
-      </c>
-      <c r="F86" s="159"/>
-      <c r="G86" s="160" t="s">
+      <c r="J86" s="153"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B87" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="C87" s="172" t="n">
+        <v>45603</v>
+      </c>
+      <c r="D87" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E87" s="114" t="n">
+        <v>156000</v>
+      </c>
+      <c r="F87" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="H86" s="157" t="s">
-        <v>134</v>
-      </c>
-      <c r="I86" s="157" t="s">
-        <v>135</v>
-      </c>
-      <c r="J86" s="161"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="111" t="s">
-        <v>191</v>
-      </c>
-      <c r="B87" s="84" t="s">
-        <v>67</v>
-      </c>
-      <c r="C87" s="180" t="n">
-        <v>45603</v>
-      </c>
-      <c r="D87" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E87" s="122" t="n">
-        <v>156000</v>
-      </c>
-      <c r="F87" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="G87" s="104"/>
+      <c r="G87" s="96"/>
       <c r="H87" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J87" s="161"/>
+      <c r="J87" s="153"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="111"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="103"/>
-      <c r="D88" s="111"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="111"/>
-      <c r="G88" s="104"/>
-      <c r="H88" s="124" t="s">
-        <v>193</v>
+      <c r="A88" s="103"/>
+      <c r="B88" s="74"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="103"/>
+      <c r="E88" s="74"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="96"/>
+      <c r="H88" s="116" t="s">
+        <v>189</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J88" s="161"/>
+      <c r="J88" s="153"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
-      <c r="B89" s="126" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" s="143" t="n">
+      <c r="B89" s="118" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" s="135" t="n">
         <v>45704</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="J89" s="161"/>
+      <c r="J89" s="153"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C90" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C90" s="57" t="n">
         <v>45705</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="J90" s="161"/>
+      <c r="J90" s="153"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
-      <c r="J91" s="161"/>
+      <c r="J91" s="153"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
-      <c r="C92" s="127" t="s">
-        <v>153</v>
-      </c>
-      <c r="D92" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="G92" s="181"/>
+      <c r="C92" s="119" t="s">
+        <v>149</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="G92" s="173"/>
       <c r="H92" s="3"/>
-      <c r="J92" s="161"/>
+      <c r="J92" s="153"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
-      <c r="C93" s="127" t="n">
+      <c r="C93" s="119" t="n">
         <v>45706</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="J93" s="161"/>
+      <c r="J93" s="153"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
-      <c r="C94" s="182" t="n">
+      <c r="C94" s="174" t="n">
         <v>45711</v>
       </c>
-      <c r="D94" s="145" t="s">
-        <v>178</v>
-      </c>
-      <c r="E94" s="145"/>
-      <c r="F94" s="145"/>
-      <c r="G94" s="147"/>
-      <c r="H94" s="145"/>
-      <c r="I94" s="148"/>
-      <c r="J94" s="161"/>
+      <c r="D94" s="137" t="s">
+        <v>174</v>
+      </c>
+      <c r="E94" s="137"/>
+      <c r="F94" s="137"/>
+      <c r="G94" s="139"/>
+      <c r="H94" s="137"/>
+      <c r="I94" s="140"/>
+      <c r="J94" s="153"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C95" s="183"/>
+        <v>192</v>
+      </c>
+      <c r="C95" s="175"/>
       <c r="D95" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="J95" s="161"/>
+      <c r="J95" s="153"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="J96" s="161"/>
+      <c r="J96" s="153"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="D97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="113" t="s">
-        <v>199</v>
-      </c>
-      <c r="J97" s="161"/>
+      <c r="I97" s="105" t="s">
+        <v>195</v>
+      </c>
+      <c r="J97" s="153"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="113" t="s">
-        <v>183</v>
-      </c>
-      <c r="J98" s="161"/>
+      <c r="I98" s="105" t="s">
+        <v>179</v>
+      </c>
+      <c r="J98" s="153"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="184" t="s">
-        <v>160</v>
-      </c>
-      <c r="C99" s="185" t="n">
+      <c r="B99" s="176" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="177" t="n">
         <v>45792</v>
       </c>
-      <c r="D99" s="186" t="n">
+      <c r="D99" s="178" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15" t="s">
+      <c r="E99" s="25"/>
+      <c r="F99" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="H99" s="25"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="153"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="153"/>
+      <c r="B100" s="179" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" s="180" t="n">
+        <v>45939</v>
+      </c>
+      <c r="D100" s="181" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="E100" s="153"/>
+      <c r="F100" s="153"/>
+      <c r="G100" s="182"/>
+      <c r="H100" s="153"/>
+      <c r="I100" s="153"/>
+      <c r="J100" s="153"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="67"/>
+      <c r="B101" s="183"/>
+      <c r="C101" s="184"/>
+      <c r="D101" s="185"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="67"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="67"/>
+      <c r="I101" s="67"/>
+      <c r="J101" s="67"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="67"/>
+      <c r="B102" s="183"/>
+      <c r="C102" s="184"/>
+      <c r="D102" s="185"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="67"/>
+      <c r="G102" s="61"/>
+      <c r="H102" s="67"/>
+      <c r="I102" s="67"/>
+      <c r="J102" s="67"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="186"/>
+      <c r="B103" s="186"/>
+      <c r="C103" s="187"/>
+      <c r="D103" s="186"/>
+      <c r="E103" s="186"/>
+      <c r="F103" s="186"/>
+      <c r="G103" s="188"/>
+      <c r="H103" s="186"/>
+      <c r="I103" s="188"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="B104" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C104" s="77" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D104" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="E104" s="78"/>
+      <c r="F104" s="78"/>
+      <c r="G104" s="189" t="n">
+        <v>45672</v>
+      </c>
+      <c r="H104" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="I104" s="80" t="n">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="75"/>
+      <c r="B105" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="C105" s="77"/>
+      <c r="D105" s="75"/>
+      <c r="E105" s="78"/>
+      <c r="F105" s="78"/>
+      <c r="G105" s="189"/>
+      <c r="H105" s="75"/>
+      <c r="I105" s="80"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" s="77" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D106" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="E106" s="78"/>
+      <c r="F106" s="78"/>
+      <c r="G106" s="189" t="n">
+        <v>45672</v>
+      </c>
+      <c r="H106" s="190" t="s">
+        <v>199</v>
+      </c>
+      <c r="I106" s="80" t="n">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="116" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C107" s="191" t="n">
+        <v>45475</v>
+      </c>
+      <c r="D107" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107" s="192" t="n">
+        <v>113</v>
+      </c>
+      <c r="F107" s="116" t="s">
+        <v>133</v>
+      </c>
+      <c r="G107" s="189" t="n">
+        <v>45672</v>
+      </c>
+      <c r="H107" s="116" t="s">
+        <v>188</v>
+      </c>
+      <c r="I107" s="193" t="n">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="116"/>
+      <c r="B108" s="76" t="s">
         <v>200</v>
       </c>
-      <c r="H99" s="15"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="161"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="161"/>
-      <c r="B100" s="187" t="s">
-        <v>73</v>
-      </c>
-      <c r="C100" s="188" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D100" s="189" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="E100" s="161"/>
-      <c r="F100" s="161"/>
-      <c r="G100" s="190"/>
-      <c r="H100" s="161"/>
-      <c r="I100" s="161"/>
-      <c r="J100" s="161"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="76"/>
-      <c r="B101" s="191"/>
-      <c r="C101" s="192"/>
-      <c r="D101" s="193"/>
-      <c r="E101" s="76"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="70"/>
-      <c r="H101" s="76"/>
-      <c r="I101" s="76"/>
-      <c r="J101" s="76"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="76"/>
-      <c r="B102" s="191"/>
-      <c r="C102" s="192"/>
-      <c r="D102" s="193"/>
-      <c r="E102" s="76"/>
-      <c r="F102" s="76"/>
-      <c r="G102" s="70"/>
-      <c r="H102" s="76"/>
-      <c r="I102" s="76"/>
-      <c r="J102" s="76"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="194"/>
-      <c r="B103" s="194"/>
-      <c r="C103" s="195"/>
-      <c r="D103" s="194"/>
-      <c r="E103" s="194"/>
-      <c r="F103" s="194"/>
-      <c r="G103" s="196"/>
-      <c r="H103" s="194"/>
-      <c r="I103" s="196"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="83" t="s">
-        <v>191</v>
-      </c>
-      <c r="B104" s="84" t="s">
-        <v>103</v>
-      </c>
-      <c r="C104" s="85" t="n">
+      <c r="C108" s="191"/>
+      <c r="D108" s="116"/>
+      <c r="E108" s="192"/>
+      <c r="F108" s="116"/>
+      <c r="G108" s="189"/>
+      <c r="H108" s="116"/>
+      <c r="I108" s="193"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="116" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C109" s="191"/>
+      <c r="D109" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E109" s="192" t="n">
+        <v>113</v>
+      </c>
+      <c r="F109" s="116" t="s">
+        <v>133</v>
+      </c>
+      <c r="G109" s="189" t="n">
+        <v>45672</v>
+      </c>
+      <c r="H109" s="194" t="s">
+        <v>189</v>
+      </c>
+      <c r="I109" s="193" t="n">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="195"/>
+      <c r="B113" s="186"/>
+      <c r="C113" s="187"/>
+      <c r="D113" s="195"/>
+      <c r="E113" s="186"/>
+      <c r="F113" s="188"/>
+      <c r="G113" s="188"/>
+      <c r="H113" s="188"/>
+      <c r="I113" s="188"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="B114" s="160" t="s">
+        <v>100</v>
+      </c>
+      <c r="C114" s="196" t="n">
+        <v>45438</v>
+      </c>
+      <c r="D114" s="75" t="s">
+        <v>144</v>
+      </c>
+      <c r="E114" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="197" t="s">
+        <v>202</v>
+      </c>
+      <c r="G114" s="79"/>
+      <c r="H114" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="I114" s="79"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="75"/>
+      <c r="B115" s="198" t="s">
+        <v>204</v>
+      </c>
+      <c r="C115" s="199" t="n">
+        <v>45486</v>
+      </c>
+      <c r="D115" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="E115" s="75"/>
+      <c r="F115" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="G115" s="201" t="n">
         <v>45588</v>
       </c>
-      <c r="D104" s="83" t="s">
-        <v>163</v>
-      </c>
-      <c r="E104" s="86"/>
-      <c r="F104" s="86"/>
-      <c r="G104" s="197" t="n">
-        <v>45672</v>
-      </c>
-      <c r="H104" s="83" t="s">
-        <v>201</v>
-      </c>
-      <c r="I104" s="88" t="n">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="83"/>
-      <c r="B105" s="84" t="s">
+      <c r="H115" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="I115" s="79"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="75"/>
+      <c r="B116" s="198" t="s">
+        <v>207</v>
+      </c>
+      <c r="C116" s="199" t="n">
+        <v>45590</v>
+      </c>
+      <c r="D116" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="E116" s="75"/>
+      <c r="F116" s="200" t="s">
         <v>202</v>
       </c>
-      <c r="C105" s="85"/>
-      <c r="D105" s="83"/>
-      <c r="E105" s="86"/>
-      <c r="F105" s="86"/>
-      <c r="G105" s="197"/>
-      <c r="H105" s="83"/>
-      <c r="I105" s="88"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="83" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" s="84" t="s">
-        <v>103</v>
-      </c>
-      <c r="C106" s="85" t="n">
-        <v>45588</v>
-      </c>
-      <c r="D106" s="83" t="s">
-        <v>163</v>
-      </c>
-      <c r="E106" s="86"/>
-      <c r="F106" s="86"/>
-      <c r="G106" s="197" t="n">
-        <v>45672</v>
-      </c>
-      <c r="H106" s="198" t="s">
-        <v>203</v>
-      </c>
-      <c r="I106" s="88" t="n">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="124" t="s">
-        <v>191</v>
-      </c>
-      <c r="B107" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="C107" s="199" t="n">
-        <v>45475</v>
-      </c>
-      <c r="D107" s="124" t="s">
-        <v>148</v>
-      </c>
-      <c r="E107" s="200" t="n">
-        <v>113</v>
-      </c>
-      <c r="F107" s="124" t="s">
-        <v>137</v>
-      </c>
-      <c r="G107" s="197" t="n">
-        <v>45672</v>
-      </c>
-      <c r="H107" s="124" t="s">
-        <v>192</v>
-      </c>
-      <c r="I107" s="201" t="n">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="124"/>
-      <c r="B108" s="84" t="s">
-        <v>204</v>
-      </c>
-      <c r="C108" s="199"/>
-      <c r="D108" s="124"/>
-      <c r="E108" s="200"/>
-      <c r="F108" s="124"/>
-      <c r="G108" s="197"/>
-      <c r="H108" s="124"/>
-      <c r="I108" s="201"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="124" t="s">
-        <v>191</v>
-      </c>
-      <c r="B109" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="C109" s="199"/>
-      <c r="D109" s="124" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="200" t="n">
-        <v>113</v>
-      </c>
-      <c r="F109" s="124" t="s">
-        <v>137</v>
-      </c>
-      <c r="G109" s="197" t="n">
-        <v>45672</v>
-      </c>
-      <c r="H109" s="202" t="s">
-        <v>193</v>
-      </c>
-      <c r="I109" s="201" t="n">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="203"/>
-      <c r="B113" s="194"/>
-      <c r="C113" s="195"/>
-      <c r="D113" s="203"/>
-      <c r="E113" s="194"/>
-      <c r="F113" s="196"/>
-      <c r="G113" s="196"/>
-      <c r="H113" s="196"/>
-      <c r="I113" s="196"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="83" t="s">
-        <v>205</v>
-      </c>
-      <c r="B114" s="168" t="s">
-        <v>104</v>
-      </c>
-      <c r="C114" s="204" t="n">
-        <v>45438</v>
-      </c>
-      <c r="D114" s="83" t="s">
-        <v>148</v>
-      </c>
-      <c r="E114" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="205" t="s">
-        <v>206</v>
-      </c>
-      <c r="G114" s="87"/>
-      <c r="H114" s="83" t="s">
-        <v>207</v>
-      </c>
-      <c r="I114" s="87"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="83"/>
-      <c r="B115" s="206" t="s">
+      <c r="G116" s="201" t="n">
+        <v>45688</v>
+      </c>
+      <c r="H116" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="C115" s="207" t="n">
-        <v>45486</v>
-      </c>
-      <c r="D115" s="83" t="s">
+      <c r="I116" s="79"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="75"/>
+      <c r="B117" s="202"/>
+      <c r="C117" s="203"/>
+      <c r="D117" s="202" t="s">
         <v>209</v>
       </c>
-      <c r="E115" s="83"/>
-      <c r="F115" s="208" t="s">
-        <v>206</v>
-      </c>
-      <c r="G115" s="209" t="n">
-        <v>45588</v>
-      </c>
-      <c r="H115" s="83" t="s">
+      <c r="E117" s="202"/>
+      <c r="F117" s="204"/>
+      <c r="G117" s="205" t="n">
+        <v>45782</v>
+      </c>
+      <c r="H117" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="I115" s="87"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="83"/>
-      <c r="B116" s="206" t="s">
-        <v>211</v>
-      </c>
-      <c r="C116" s="207" t="n">
-        <v>45590</v>
-      </c>
-      <c r="D116" s="83" t="s">
-        <v>141</v>
-      </c>
-      <c r="E116" s="83"/>
-      <c r="F116" s="208" t="s">
-        <v>206</v>
-      </c>
-      <c r="G116" s="209" t="n">
-        <v>45688</v>
-      </c>
-      <c r="H116" s="83" t="s">
-        <v>212</v>
-      </c>
-      <c r="I116" s="87"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="83"/>
-      <c r="B117" s="210"/>
-      <c r="C117" s="211"/>
-      <c r="D117" s="210" t="s">
-        <v>213</v>
-      </c>
-      <c r="E117" s="210"/>
-      <c r="F117" s="212"/>
-      <c r="G117" s="213" t="n">
-        <v>45782</v>
-      </c>
-      <c r="H117" s="83" t="s">
-        <v>214</v>
-      </c>
-      <c r="I117" s="87"/>
+      <c r="I117" s="79"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
-      <c r="B118" s="214"/>
-      <c r="C118" s="215"/>
+      <c r="B118" s="206"/>
+      <c r="C118" s="207"/>
       <c r="D118" s="3"/>
-      <c r="E118" s="214"/>
-      <c r="F118" s="216"/>
-      <c r="G118" s="217"/>
+      <c r="E118" s="206"/>
+      <c r="F118" s="208"/>
+      <c r="G118" s="209"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
-      <c r="B119" s="214"/>
-      <c r="C119" s="215"/>
+      <c r="B119" s="206"/>
+      <c r="C119" s="207"/>
       <c r="D119" s="3"/>
-      <c r="E119" s="214"/>
-      <c r="F119" s="216"/>
-      <c r="G119" s="217"/>
+      <c r="E119" s="206"/>
+      <c r="F119" s="208"/>
+      <c r="G119" s="209"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5422,13 +5340,13 @@
         <v>45967</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5436,13 +5354,13 @@
         <v>45927</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5450,52 +5368,52 @@
         <v>45708</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="E8" s="218" t="n">
+      <c r="E8" s="210" t="n">
         <v>0.416666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E15" s="218" t="n">
+      <c r="E15" s="210" t="n">
         <v>0.427083333333333</v>
       </c>
     </row>
@@ -5515,40 +5433,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B9:D13"/>
+  <dimension ref="B1:D13"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="32.72"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="11" t="n">
         <v>45725</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -5,14 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="hmb" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="AUB" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sayfa1" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sayfa5" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="ali" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="atila" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sayfa1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sayfa5" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="228">
   <si>
     <t xml:space="preserve">dava tarihi</t>
   </si>
@@ -53,23 +55,7 @@
     <t xml:space="preserve">2026/392</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Maphre-rahmi kesici – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.asliye</t>
-    </r>
+    <t xml:space="preserve">Maphre-rahmi kesici – 4.asliye</t>
   </si>
   <si>
     <t xml:space="preserve">tazminat</t>
@@ -370,6 +356,18 @@
   </si>
   <si>
     <t xml:space="preserve">dursun durmuş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">murat çalışkan – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adem kesici – icra</t>
   </si>
   <si>
     <t xml:space="preserve">Dosya Listesi</t>
@@ -754,7 +752,7 @@
     <numFmt numFmtId="169" formatCode="hh:mm"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -795,11 +793,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1207,7 +1200,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="209">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1244,7 +1237,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1260,11 +1253,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1308,15 +1301,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1333,10 +1322,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1536,7 +1521,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1552,15 +1537,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1572,15 +1557,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1628,7 +1613,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1704,7 +1689,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1712,27 +1697,27 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1752,47 +1737,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1828,23 +1813,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1852,23 +1837,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1904,7 +1889,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1912,27 +1897,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="14" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1940,15 +1925,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1964,11 +1949,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1984,7 +1969,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1992,59 +1977,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2496,7 +2481,7 @@
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.57"/>
   </cols>
   <sheetData>
@@ -2506,7 +2491,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="n">
+      <c r="B2" s="25" t="n">
         <v>45725</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2554,7 +2539,7 @@
       <c r="D5" s="10" t="n">
         <v>46088</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="8" t="n">
@@ -2671,12 +2656,12 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
     </row>
@@ -2699,7 +2684,7 @@
       <c r="A18" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2720,11 +2705,11 @@
       <c r="C20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33" t="n">
+      <c r="D20" s="9"/>
+      <c r="E20" s="31" t="n">
         <v>46009</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="32" t="n">
         <v>196170</v>
       </c>
     </row>
@@ -2737,10 +2722,10 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
     </row>
@@ -2759,11 +2744,11 @@
       <c r="C24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33" t="n">
+      <c r="D24" s="9"/>
+      <c r="E24" s="31" t="n">
         <v>45698</v>
       </c>
-      <c r="F24" s="34"/>
+      <c r="F24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3"/>
@@ -2774,10 +2759,10 @@
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
     </row>
@@ -2796,11 +2781,11 @@
       <c r="C28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33" t="n">
+      <c r="D28" s="9"/>
+      <c r="E28" s="31" t="n">
         <v>45482</v>
       </c>
-      <c r="F28" s="34" t="n">
+      <c r="F28" s="32" t="n">
         <v>74000</v>
       </c>
     </row>
@@ -2810,9 +2795,9 @@
       <c r="C29" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="n">
@@ -2824,11 +2809,11 @@
       <c r="C30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33" t="n">
+      <c r="D30" s="9"/>
+      <c r="E30" s="31" t="n">
         <v>45615</v>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F30" s="32" t="n">
         <v>140835</v>
       </c>
     </row>
@@ -2838,18 +2823,18 @@
       <c r="C31" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="34"/>
-    </row>
-    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="9"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="32"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>45704</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="13" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="2"/>
@@ -2876,14 +2861,14 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="27" t="n">
         <v>46042</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="31"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="4"/>
       <c r="F35" s="5" t="s">
         <v>62</v>
@@ -2899,7 +2884,7 @@
       <c r="E37" s="4"/>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
         <v>45603</v>
       </c>
@@ -2909,11 +2894,11 @@
       <c r="C38" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="33" t="n">
+      <c r="D38" s="9"/>
+      <c r="E38" s="31" t="n">
         <v>45615</v>
       </c>
-      <c r="F38" s="34"/>
+      <c r="F38" s="32"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="3"/>
@@ -2946,7 +2931,7 @@
       <c r="E41" s="4" t="n">
         <v>86000</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="35" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2989,7 +2974,7 @@
       <c r="C45" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="38"/>
+      <c r="D45" s="36"/>
       <c r="E45" s="4"/>
       <c r="F45" s="5" t="s">
         <v>73</v>
@@ -3010,11 +2995,11 @@
       <c r="C47" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="33" t="n">
+      <c r="D47" s="9"/>
+      <c r="E47" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="F47" s="34"/>
+      <c r="F47" s="32"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3"/>
@@ -3044,7 +3029,7 @@
       <c r="B50" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="30"/>
+      <c r="C50" s="29"/>
       <c r="E50" s="4"/>
       <c r="F50" s="5"/>
     </row>
@@ -3062,14 +3047,14 @@
       <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="n">
+      <c r="A52" s="27" t="n">
         <v>46155</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="28"/>
+      <c r="C52" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="4"/>
       <c r="F52" s="5" t="s">
         <v>73</v>
@@ -3095,11 +3080,11 @@
       <c r="C55" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="33" t="n">
+      <c r="D55" s="9"/>
+      <c r="E55" s="31" t="n">
         <v>45482</v>
       </c>
-      <c r="F55" s="34" t="n">
+      <c r="F55" s="32" t="n">
         <v>158437</v>
       </c>
     </row>
@@ -3126,7 +3111,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="3"/>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="13" t="s">
         <v>67</v>
       </c>
       <c r="E58" s="4"/>
@@ -3144,7 +3129,7 @@
       <c r="F59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="39" t="n">
+      <c r="A60" s="37" t="n">
         <v>46175</v>
       </c>
       <c r="B60" s="23" t="n">
@@ -3177,11 +3162,11 @@
       <c r="C63" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="33" t="n">
+      <c r="D63" s="9"/>
+      <c r="E63" s="31" t="n">
         <v>45482</v>
       </c>
-      <c r="F63" s="34" t="n">
+      <c r="F63" s="32" t="n">
         <v>86000</v>
       </c>
     </row>
@@ -3194,9 +3179,9 @@
       <c r="F64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="35"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="30"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="29"/>
       <c r="E65" s="4"/>
       <c r="F65" s="5"/>
     </row>
@@ -3207,7 +3192,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="3"/>
-      <c r="C67" s="25"/>
+      <c r="C67" s="13"/>
       <c r="D67" s="2"/>
       <c r="E67" s="4"/>
       <c r="F67" s="5"/>
@@ -3216,21 +3201,21 @@
       <c r="A68" s="6" t="n">
         <v>45342</v>
       </c>
-      <c r="B68" s="40" t="s">
+      <c r="B68" s="38" t="s">
         <v>89</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E68" s="36"/>
-      <c r="F68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="32"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="3"/>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D69" s="2"/>
@@ -3244,7 +3229,7 @@
       <c r="B70" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -3258,7 +3243,7 @@
         <v>45680</v>
       </c>
       <c r="B71" s="3"/>
-      <c r="C71" s="25" t="s">
+      <c r="C71" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -3276,16 +3261,16 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="28" t="n">
+      <c r="A73" s="27" t="n">
         <v>45765</v>
       </c>
-      <c r="B73" s="41" t="s">
+      <c r="B73" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C73" s="30" t="s">
+      <c r="C73" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="31"/>
+      <c r="D73" s="30"/>
       <c r="E73" s="4"/>
       <c r="F73" s="5" t="s">
         <v>62</v>
@@ -3293,7 +3278,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="3"/>
-      <c r="C74" s="25" t="s">
+      <c r="C74" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D74" s="2"/>
@@ -3302,165 +3287,165 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="3"/>
-      <c r="C75" s="25"/>
+      <c r="C75" s="13"/>
       <c r="D75" s="2"/>
       <c r="E75" s="4"/>
       <c r="F75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="3"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="13"/>
       <c r="D76" s="2"/>
       <c r="E76" s="4"/>
       <c r="F76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="42" t="n">
+      <c r="A77" s="40" t="n">
         <v>45588</v>
       </c>
-      <c r="B77" s="43" t="s">
+      <c r="B77" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="44" t="s">
+      <c r="C77" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D77" s="45"/>
-      <c r="E77" s="46"/>
-      <c r="F77" s="47"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="45"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="42"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="44" t="s">
+      <c r="A78" s="40"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D78" s="45"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="47"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="45"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="48" t="n">
+      <c r="A79" s="46" t="n">
         <v>45438</v>
       </c>
-      <c r="B79" s="49" t="s">
+      <c r="B79" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="D79" s="51"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="53"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="51"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="48"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="50" t="s">
+      <c r="A80" s="46"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D80" s="51"/>
-      <c r="E80" s="52" t="s">
+      <c r="D80" s="49"/>
+      <c r="E80" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="F80" s="53" t="n">
+      <c r="F80" s="51" t="n">
         <v>193500</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="48" t="n">
+      <c r="A81" s="46" t="n">
         <v>45288</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C81" s="55" t="s">
+      <c r="C81" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="D81" s="55" t="s">
+      <c r="D81" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="E81" s="52"/>
-      <c r="F81" s="53"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="51"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="48"/>
-      <c r="B82" s="54"/>
-      <c r="C82" s="55" t="s">
+      <c r="A82" s="46"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D82" s="55"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="51"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="48" t="n">
+      <c r="A83" s="46" t="n">
         <v>45148</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="C83" s="55" t="s">
+      <c r="C83" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D83" s="55"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="51"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="48"/>
-      <c r="B84" s="54"/>
-      <c r="C84" s="55"/>
-      <c r="D84" s="55"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="53"/>
+      <c r="A84" s="46"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="51"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="48" t="n">
+      <c r="A85" s="46" t="n">
         <v>44928</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="C85" s="55" t="s">
+      <c r="C85" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="D85" s="55"/>
-      <c r="E85" s="52" t="s">
+      <c r="D85" s="53"/>
+      <c r="E85" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="F85" s="53" t="n">
+      <c r="F85" s="51" t="n">
         <v>24316</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="48"/>
-      <c r="B86" s="54"/>
-      <c r="C86" s="55"/>
-      <c r="D86" s="55"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="53"/>
+      <c r="A86" s="46"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="51"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="48" t="n">
+      <c r="A87" s="46" t="n">
         <v>44333</v>
       </c>
-      <c r="B87" s="54" t="s">
+      <c r="B87" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="C87" s="55" t="s">
+      <c r="C87" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D87" s="55"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="51"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="48"/>
-      <c r="B88" s="54"/>
-      <c r="C88" s="55"/>
-      <c r="D88" s="55"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="53"/>
+      <c r="A88" s="46"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="51"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="3"/>
@@ -3495,7 +3480,7 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="3"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="56"/>
+      <c r="E95" s="54"/>
       <c r="F95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3603,11 +3588,263 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A3:F1048576"/>
+  <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.57"/>
+  </cols>
+  <sheetData>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="3"/>
+      <c r="D10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>0.413194444444444</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A3:F1048576"/>
+  <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.57"/>
+  </cols>
+  <sheetData>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+      <c r="D14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>0.413194444444444</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="11"/>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:J119"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="57" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="55" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="4"/>
@@ -3617,105 +3854,105 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="A1" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="58"/>
-      <c r="B2" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="58"/>
-      <c r="B4" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="62" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="I4" s="59"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58"/>
-      <c r="B5" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="H5" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="59"/>
+      <c r="D5" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="57"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="58"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58"/>
-      <c r="B7" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="57" t="n">
+      <c r="A7" s="56"/>
+      <c r="B7" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="55" t="n">
         <v>45827</v>
       </c>
-      <c r="D7" s="60" t="s">
-        <v>120</v>
+      <c r="D7" s="58" t="s">
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>9</v>
@@ -3723,77 +3960,77 @@
       <c r="F7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="I7" s="57"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="56"/>
+      <c r="B9" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="55" t="n">
+        <v>45939</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="65" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="65" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="57"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="56"/>
+      <c r="B10" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="58" t="n">
+        <v>45939</v>
+      </c>
+      <c r="D10" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="I7" s="59"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="58"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58"/>
-      <c r="B9" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="57" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="67" t="n">
+      <c r="E10" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="67" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="I9" s="59"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="58"/>
-      <c r="B10" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="60" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="59" t="n">
+      <c r="F10" s="57" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="I10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="57"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58"/>
-      <c r="B11" s="66" t="s">
+      <c r="A11" s="56"/>
+      <c r="B11" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="60" t="n">
+      <c r="C11" s="58" t="n">
         <v>45952</v>
       </c>
-      <c r="D11" s="59" t="s">
-        <v>125</v>
+      <c r="D11" s="57" t="s">
+        <v>129</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>9</v>
@@ -3801,664 +4038,664 @@
       <c r="F11" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="61"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="59"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="58"/>
-      <c r="B12" s="66" t="s">
+      <c r="A12" s="56"/>
+      <c r="B12" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="58" t="n">
         <v>45952</v>
       </c>
-      <c r="D12" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="59" t="n">
+      <c r="D12" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="59" t="n">
+      <c r="F12" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="G12" s="61"/>
-      <c r="H12" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="61"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="59"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="61"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="59"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="58"/>
-      <c r="I14" s="59"/>
+      <c r="A14" s="56"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58"/>
-      <c r="I15" s="59"/>
+      <c r="A15" s="56"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="68"/>
-      <c r="J16" s="25"/>
+      <c r="A16" s="66"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="69"/>
-      <c r="B17" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="72" t="s">
+      <c r="A17" s="67"/>
+      <c r="B17" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="68"/>
+      <c r="E17" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="74"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="72"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="76" t="s">
+      <c r="A18" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="77" t="n">
+      <c r="C18" s="75" t="n">
         <v>45342</v>
       </c>
-      <c r="D18" s="75" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="78"/>
-      <c r="F18" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="80"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="74"/>
+      <c r="D18" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="78"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="72"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="75"/>
-      <c r="B19" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="77" t="n">
+      <c r="A19" s="73"/>
+      <c r="B19" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="75" t="n">
         <v>45537</v>
       </c>
-      <c r="D19" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="82" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="80" t="n">
+      <c r="D19" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="76"/>
+      <c r="F19" s="80" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="78" t="n">
         <v>45691</v>
       </c>
-      <c r="H19" s="78"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="74"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="72"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="85" t="s">
-        <v>137</v>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="83" t="s">
+        <v>141</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="74"/>
+      <c r="J20" s="72"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="C21" s="86" t="n">
+      <c r="C21" s="84" t="n">
         <v>45726</v>
       </c>
-      <c r="D21" s="87" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="87"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="74"/>
+      <c r="D21" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="85"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="72"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="74"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="72"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68"/>
-      <c r="J23" s="74"/>
+      <c r="A23" s="66"/>
+      <c r="J23" s="72"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="94"/>
-      <c r="B24" s="74"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="68"/>
+      <c r="A25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="68"/>
+      <c r="A26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="97"/>
-      <c r="B27" s="98" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="98"/>
-      <c r="E27" s="100" t="s">
+      <c r="A27" s="95"/>
+      <c r="B27" s="96" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="96"/>
+      <c r="E27" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="100"/>
-      <c r="G27" s="101" t="s">
-        <v>129</v>
-      </c>
-      <c r="H27" s="98" t="s">
-        <v>130</v>
-      </c>
-      <c r="I27" s="98" t="s">
-        <v>131</v>
-      </c>
-      <c r="J27" s="102"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="96" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="96" t="s">
+        <v>135</v>
+      </c>
+      <c r="J27" s="100"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="68" t="s">
-        <v>139</v>
+      <c r="A28" s="66" t="s">
+        <v>143</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H28" s="103" t="s">
-        <v>141</v>
-      </c>
-      <c r="I28" s="104" t="n">
+        <v>144</v>
+      </c>
+      <c r="H28" s="101" t="s">
+        <v>145</v>
+      </c>
+      <c r="I28" s="102" t="n">
         <v>45712</v>
       </c>
-      <c r="J28" s="102"/>
+      <c r="J28" s="100"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="68"/>
-      <c r="J29" s="102"/>
+      <c r="A29" s="66"/>
+      <c r="J29" s="100"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
-      <c r="B30" s="25"/>
+      <c r="B30" s="13"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="105" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="102"/>
+      <c r="I30" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="J30" s="100"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="106"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="107"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="102"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="100"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="68"/>
+      <c r="A32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="68"/>
+      <c r="A33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="109"/>
-      <c r="B34" s="110" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="110"/>
-      <c r="E34" s="112" t="s">
+      <c r="A34" s="107"/>
+      <c r="B34" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="108"/>
+      <c r="E34" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="112"/>
-      <c r="G34" s="113" t="s">
-        <v>129</v>
-      </c>
-      <c r="H34" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" s="110" t="s">
-        <v>131</v>
-      </c>
-      <c r="J34" s="74"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="111" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="J34" s="72"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="106" t="s">
-        <v>143</v>
-      </c>
-      <c r="B35" s="76" t="s">
+      <c r="A35" s="104" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="95" t="n">
+      <c r="C35" s="93" t="n">
         <v>45475</v>
       </c>
-      <c r="D35" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="114" t="n">
+      <c r="D35" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="112" t="n">
         <v>97</v>
       </c>
-      <c r="F35" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="103" t="s">
-        <v>145</v>
-      </c>
-      <c r="I35" s="96" t="n">
+      <c r="F35" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="H35" s="101" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" s="94" t="n">
         <v>45705</v>
       </c>
-      <c r="J35" s="74"/>
+      <c r="J35" s="72"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="103"/>
-      <c r="B36" s="115" t="s">
+      <c r="A36" s="101"/>
+      <c r="B36" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="95" t="n">
+      <c r="C36" s="93" t="n">
         <v>45604</v>
       </c>
-      <c r="D36" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" s="114" t="n">
+      <c r="D36" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" s="112" t="n">
         <v>178</v>
       </c>
-      <c r="F36" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="H36" s="116" t="s">
-        <v>146</v>
-      </c>
-      <c r="I36" s="117" t="n">
+      <c r="F36" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="114" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" s="115" t="n">
         <v>45705</v>
       </c>
-      <c r="J36" s="74"/>
+      <c r="J36" s="72"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
-      <c r="B37" s="118" t="s">
+      <c r="B37" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="57" t="n">
+      <c r="C37" s="55" t="n">
         <v>45704</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="J37" s="74"/>
+        <v>151</v>
+      </c>
+      <c r="J37" s="72"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="57" t="n">
+      <c r="C38" s="55" t="n">
         <v>45705</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="J38" s="74"/>
+      <c r="J38" s="72"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
-      <c r="C39" s="119"/>
+      <c r="C39" s="117"/>
       <c r="D39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="J39" s="74"/>
+      <c r="J39" s="72"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
-      <c r="C40" s="119" t="s">
-        <v>149</v>
+      <c r="C40" s="117" t="s">
+        <v>153</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="J40" s="74"/>
+      <c r="J40" s="72"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
-      <c r="C41" s="120" t="n">
+      <c r="C41" s="118" t="n">
         <v>45717</v>
       </c>
-      <c r="D41" s="121" t="s">
+      <c r="D41" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="122" t="s">
-        <v>151</v>
-      </c>
-      <c r="F41" s="121"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="121" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="124" t="s">
-        <v>153</v>
-      </c>
-      <c r="J41" s="74"/>
+      <c r="E41" s="120" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="119"/>
+      <c r="G41" s="121"/>
+      <c r="H41" s="119" t="s">
+        <v>156</v>
+      </c>
+      <c r="I41" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="J41" s="72"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
-      <c r="C42" s="125"/>
+      <c r="C42" s="123"/>
       <c r="D42" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J42" s="74"/>
+        <v>159</v>
+      </c>
+      <c r="J42" s="72"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="126"/>
-      <c r="B43" s="127" t="s">
-        <v>156</v>
-      </c>
-      <c r="C43" s="128" t="n">
+      <c r="A43" s="124"/>
+      <c r="B43" s="125" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="126" t="n">
         <v>45805</v>
       </c>
-      <c r="D43" s="129" t="n">
+      <c r="D43" s="127" t="n">
         <v>0.409722222222222</v>
       </c>
-      <c r="E43" s="126" t="s">
-        <v>157</v>
-      </c>
-      <c r="F43" s="126"/>
-      <c r="G43" s="130"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="130"/>
-      <c r="J43" s="131"/>
+      <c r="E43" s="124" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="124"/>
+      <c r="G43" s="128"/>
+      <c r="H43" s="124"/>
+      <c r="I43" s="128"/>
+      <c r="J43" s="129"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="103"/>
-      <c r="B44" s="74"/>
-      <c r="C44" s="132" t="n">
+      <c r="A44" s="101"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="130" t="n">
         <v>45805</v>
       </c>
-      <c r="D44" s="114" t="s">
-        <v>158</v>
-      </c>
-      <c r="E44" s="114"/>
-      <c r="F44" s="114"/>
-      <c r="G44" s="133"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="74"/>
+      <c r="D44" s="112" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="112"/>
+      <c r="F44" s="112"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="72"/>
+      <c r="I44" s="94"/>
+      <c r="J44" s="72"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
-      <c r="C46" s="119"/>
+      <c r="C46" s="117"/>
       <c r="D46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="109"/>
-      <c r="B47" s="110" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="D47" s="110"/>
-      <c r="E47" s="112" t="s">
+      <c r="A47" s="107"/>
+      <c r="B47" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="108"/>
+      <c r="E47" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="112"/>
-      <c r="G47" s="113" t="s">
-        <v>129</v>
-      </c>
-      <c r="H47" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="110" t="s">
-        <v>131</v>
-      </c>
-      <c r="J47" s="74"/>
+      <c r="F47" s="110"/>
+      <c r="G47" s="111" t="s">
+        <v>133</v>
+      </c>
+      <c r="H47" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="I47" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="J47" s="72"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="103" t="s">
-        <v>143</v>
-      </c>
-      <c r="B48" s="76" t="s">
+      <c r="A48" s="101" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="134" t="n">
+      <c r="C48" s="132" t="n">
         <v>45588</v>
       </c>
-      <c r="D48" s="114" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" s="74"/>
-      <c r="F48" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="H48" s="103" t="s">
-        <v>160</v>
-      </c>
-      <c r="I48" s="96" t="n">
+      <c r="D48" s="112" t="s">
+        <v>163</v>
+      </c>
+      <c r="E48" s="72"/>
+      <c r="F48" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="H48" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" s="94" t="n">
         <v>45630</v>
       </c>
-      <c r="J48" s="74"/>
+      <c r="J48" s="72"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="103"/>
-      <c r="B49" s="76" t="s">
+      <c r="A49" s="101"/>
+      <c r="B49" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="95"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="103"/>
-      <c r="H49" s="116" t="s">
-        <v>161</v>
-      </c>
-      <c r="I49" s="96" t="n">
+      <c r="C49" s="93"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="101"/>
+      <c r="H49" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" s="94" t="n">
         <v>45630</v>
       </c>
-      <c r="J49" s="74"/>
+      <c r="J49" s="72"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="103"/>
-      <c r="B50" s="118" t="s">
+      <c r="A50" s="101"/>
+      <c r="B50" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="135" t="n">
+      <c r="C50" s="133" t="n">
         <v>45704</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="J50" s="74"/>
+      <c r="J50" s="72"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="57" t="n">
+      <c r="C51" s="55" t="n">
         <v>45709</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="J51" s="74"/>
+      <c r="J51" s="72"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
-      <c r="C52" s="119" t="s">
-        <v>149</v>
+      <c r="C52" s="117" t="s">
+        <v>153</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="J52" s="74"/>
+      <c r="J52" s="72"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
-      <c r="C53" s="119" t="n">
+      <c r="C53" s="117" t="n">
         <v>45712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="J53" s="74"/>
+      <c r="J53" s="72"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
-      <c r="C54" s="136" t="n">
+      <c r="C54" s="134" t="n">
         <v>45717</v>
       </c>
-      <c r="D54" s="137" t="s">
+      <c r="D54" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="138" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" s="137"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="137" t="s">
-        <v>152</v>
-      </c>
-      <c r="I54" s="140"/>
-      <c r="J54" s="74"/>
+      <c r="E54" s="136" t="s">
+        <v>155</v>
+      </c>
+      <c r="F54" s="135"/>
+      <c r="G54" s="137"/>
+      <c r="H54" s="135" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="138"/>
+      <c r="J54" s="72"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="141"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="141"/>
-      <c r="J55" s="74"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="140"/>
+      <c r="I55" s="139"/>
+      <c r="J55" s="72"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F56" s="1"/>
-      <c r="G56" s="141"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="143" t="s">
-        <v>153</v>
-      </c>
-      <c r="J56" s="74"/>
+      <c r="G56" s="139"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="141" t="s">
+        <v>157</v>
+      </c>
+      <c r="J56" s="72"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
-      <c r="B57" s="144" t="s">
-        <v>156</v>
-      </c>
-      <c r="C57" s="145" t="n">
+      <c r="B57" s="142" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="143" t="n">
         <v>45805</v>
       </c>
-      <c r="D57" s="146" t="n">
+      <c r="D57" s="144" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="74"/>
+      <c r="J57" s="72"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="103"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="147" t="n">
+      <c r="A58" s="101"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="145" t="n">
         <v>45805</v>
       </c>
-      <c r="D58" s="103" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="96"/>
-      <c r="H58" s="74"/>
-      <c r="I58" s="96"/>
-      <c r="J58" s="74"/>
+      <c r="D58" s="101" t="s">
+        <v>170</v>
+      </c>
+      <c r="E58" s="72"/>
+      <c r="F58" s="72"/>
+      <c r="G58" s="94"/>
+      <c r="H58" s="72"/>
+      <c r="I58" s="94"/>
+      <c r="J58" s="72"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="119"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="117"/>
       <c r="D59" s="3"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="H59" s="25"/>
-      <c r="J59" s="25"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="119"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="117"/>
       <c r="D60" s="3"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="J60" s="25"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
@@ -4468,849 +4705,849 @@
       <c r="H61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="148"/>
-      <c r="B62" s="149" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="150" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="149"/>
-      <c r="E62" s="151" t="s">
+      <c r="A62" s="146"/>
+      <c r="B62" s="147" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" s="147"/>
+      <c r="E62" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="151"/>
-      <c r="G62" s="152" t="s">
-        <v>129</v>
-      </c>
-      <c r="H62" s="149" t="s">
-        <v>130</v>
-      </c>
-      <c r="I62" s="149" t="s">
-        <v>131</v>
-      </c>
-      <c r="J62" s="153"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="147" t="s">
+        <v>134</v>
+      </c>
+      <c r="I62" s="147" t="s">
+        <v>135</v>
+      </c>
+      <c r="J62" s="151"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="106" t="s">
-        <v>167</v>
-      </c>
-      <c r="B63" s="76" t="s">
+      <c r="A63" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="95" t="n">
+      <c r="C63" s="93" t="n">
         <v>45475</v>
       </c>
-      <c r="D63" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" s="114" t="n">
+      <c r="D63" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="112" t="n">
         <v>214</v>
       </c>
-      <c r="F63" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="H63" s="103" t="s">
-        <v>168</v>
-      </c>
-      <c r="I63" s="96" t="n">
+      <c r="F63" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="H63" s="101" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="94" t="n">
         <v>45702</v>
       </c>
-      <c r="J63" s="153"/>
+      <c r="J63" s="151"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="106"/>
-      <c r="B64" s="74"/>
-      <c r="C64" s="95"/>
-      <c r="D64" s="154" t="n">
+      <c r="A64" s="104"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="93"/>
+      <c r="D64" s="152" t="n">
         <v>158437</v>
       </c>
-      <c r="E64" s="74"/>
-      <c r="F64" s="103"/>
-      <c r="H64" s="116" t="s">
-        <v>169</v>
-      </c>
-      <c r="I64" s="96" t="n">
+      <c r="E64" s="72"/>
+      <c r="F64" s="101"/>
+      <c r="H64" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="94" t="n">
         <v>45702</v>
       </c>
-      <c r="J64" s="153"/>
+      <c r="J64" s="151"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
-      <c r="B65" s="118" t="s">
+      <c r="B65" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="57" t="n">
+      <c r="C65" s="55" t="n">
         <v>45704</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="J65" s="153"/>
+      <c r="J65" s="151"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C66" s="57" t="n">
+      <c r="C66" s="55" t="n">
         <v>45705</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="J66" s="153"/>
+      <c r="J66" s="151"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="J67" s="153"/>
+      <c r="J67" s="151"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
-      <c r="C68" s="119" t="s">
-        <v>149</v>
+      <c r="C68" s="117" t="s">
+        <v>153</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="J68" s="153"/>
+      <c r="J68" s="151"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
-      <c r="C69" s="155" t="n">
+      <c r="C69" s="153" t="n">
         <v>45711</v>
       </c>
-      <c r="D69" s="156" t="s">
-        <v>174</v>
-      </c>
-      <c r="E69" s="156"/>
-      <c r="F69" s="156"/>
-      <c r="G69" s="157"/>
-      <c r="H69" s="156"/>
-      <c r="I69" s="158"/>
-      <c r="J69" s="153"/>
+      <c r="D69" s="154" t="s">
+        <v>178</v>
+      </c>
+      <c r="E69" s="154"/>
+      <c r="F69" s="154"/>
+      <c r="G69" s="155"/>
+      <c r="H69" s="154"/>
+      <c r="I69" s="156"/>
+      <c r="J69" s="151"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="25"/>
-      <c r="C70" s="125" t="s">
-        <v>175</v>
-      </c>
-      <c r="D70" s="142"/>
-      <c r="E70" s="142"/>
-      <c r="F70" s="142"/>
-      <c r="G70" s="141"/>
-      <c r="H70" s="142"/>
-      <c r="I70" s="141"/>
-      <c r="J70" s="153"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="123" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" s="140"/>
+      <c r="E70" s="140"/>
+      <c r="F70" s="140"/>
+      <c r="G70" s="139"/>
+      <c r="H70" s="140"/>
+      <c r="I70" s="139"/>
+      <c r="J70" s="151"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B71" s="25"/>
-      <c r="C71" s="125" t="s">
-        <v>176</v>
+      <c r="B71" s="13"/>
+      <c r="C71" s="123" t="s">
+        <v>180</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" s="142"/>
-      <c r="F71" s="142"/>
-      <c r="G71" s="141"/>
-      <c r="H71" s="142"/>
-      <c r="I71" s="141"/>
-      <c r="J71" s="153"/>
+        <v>181</v>
+      </c>
+      <c r="E71" s="140"/>
+      <c r="F71" s="140"/>
+      <c r="G71" s="139"/>
+      <c r="H71" s="140"/>
+      <c r="I71" s="139"/>
+      <c r="J71" s="151"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="105" t="s">
-        <v>179</v>
-      </c>
-      <c r="J72" s="153"/>
+      <c r="I72" s="103" t="s">
+        <v>183</v>
+      </c>
+      <c r="J72" s="151"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
-      <c r="C73" s="125"/>
+      <c r="C73" s="123"/>
       <c r="D73" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="105" t="s">
-        <v>181</v>
-      </c>
-      <c r="J73" s="153"/>
+      <c r="I73" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="J73" s="151"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
-      <c r="B74" s="127" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" s="159" t="n">
+      <c r="B74" s="125" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="157" t="n">
         <v>45792</v>
       </c>
-      <c r="D74" s="129" t="n">
+      <c r="D74" s="127" t="n">
         <v>0.399305555555556</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="J74" s="153"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="J74" s="151"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="160"/>
-      <c r="B75" s="161" t="s">
+      <c r="A75" s="158"/>
+      <c r="B75" s="159" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="162" t="n">
+      <c r="C75" s="160" t="n">
         <v>45939</v>
       </c>
-      <c r="D75" s="163" t="n">
+      <c r="D75" s="161" t="n">
         <v>0.402777777777778</v>
       </c>
-      <c r="E75" s="164"/>
-      <c r="F75" s="164"/>
-      <c r="G75" s="165" t="s">
-        <v>182</v>
-      </c>
-      <c r="H75" s="165" t="s">
-        <v>183</v>
-      </c>
-      <c r="I75" s="165" t="s">
-        <v>184</v>
-      </c>
-      <c r="J75" s="153"/>
+      <c r="E75" s="162"/>
+      <c r="F75" s="162"/>
+      <c r="G75" s="163" t="s">
+        <v>186</v>
+      </c>
+      <c r="H75" s="163" t="s">
+        <v>187</v>
+      </c>
+      <c r="I75" s="163" t="s">
+        <v>188</v>
+      </c>
+      <c r="J75" s="151"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
-      <c r="C76" s="119"/>
+      <c r="C76" s="117"/>
       <c r="D76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
-      <c r="C77" s="119"/>
+      <c r="C77" s="117"/>
       <c r="D77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="166"/>
-      <c r="B78" s="167" t="s">
-        <v>127</v>
-      </c>
-      <c r="C78" s="168" t="s">
-        <v>128</v>
-      </c>
-      <c r="D78" s="167"/>
-      <c r="E78" s="169" t="s">
+      <c r="A78" s="164"/>
+      <c r="B78" s="165" t="s">
+        <v>131</v>
+      </c>
+      <c r="C78" s="166" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="165"/>
+      <c r="E78" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="169"/>
-      <c r="G78" s="170" t="s">
-        <v>129</v>
-      </c>
-      <c r="H78" s="167" t="s">
-        <v>130</v>
-      </c>
-      <c r="I78" s="167" t="s">
-        <v>131</v>
-      </c>
-      <c r="J78" s="102"/>
+      <c r="F78" s="167"/>
+      <c r="G78" s="168" t="s">
+        <v>133</v>
+      </c>
+      <c r="H78" s="165" t="s">
+        <v>134</v>
+      </c>
+      <c r="I78" s="165" t="s">
+        <v>135</v>
+      </c>
+      <c r="J78" s="100"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="103" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="76" t="s">
+      <c r="A79" s="101" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="C79" s="95" t="n">
+      <c r="C79" s="93" t="n">
         <v>45676</v>
       </c>
-      <c r="D79" s="114" t="s">
-        <v>159</v>
-      </c>
-      <c r="E79" s="103"/>
-      <c r="F79" s="103" t="s">
-        <v>133</v>
+      <c r="D79" s="112" t="s">
+        <v>163</v>
+      </c>
+      <c r="E79" s="101"/>
+      <c r="F79" s="101" t="s">
+        <v>137</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J79" s="102"/>
+        <v>189</v>
+      </c>
+      <c r="J79" s="100"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="103" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="76" t="s">
+      <c r="A80" s="101" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="C80" s="95"/>
-      <c r="D80" s="103"/>
-      <c r="E80" s="103"/>
-      <c r="F80" s="103"/>
-      <c r="H80" s="116" t="s">
-        <v>186</v>
-      </c>
-      <c r="I80" s="171" t="n">
+      <c r="C80" s="93"/>
+      <c r="D80" s="101"/>
+      <c r="E80" s="101"/>
+      <c r="F80" s="101"/>
+      <c r="H80" s="114" t="s">
+        <v>190</v>
+      </c>
+      <c r="I80" s="169" t="n">
         <v>45714</v>
       </c>
-      <c r="J80" s="102"/>
+      <c r="J80" s="100"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
-      <c r="B81" s="25"/>
+      <c r="B81" s="13"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="J81" s="102"/>
+      <c r="J81" s="100"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
-      <c r="B82" s="25"/>
+      <c r="B82" s="13"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="105" t="s">
-        <v>142</v>
-      </c>
-      <c r="J82" s="102"/>
+      <c r="I82" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="J82" s="100"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="106"/>
-      <c r="B83" s="102"/>
-      <c r="C83" s="107"/>
-      <c r="D83" s="106"/>
-      <c r="E83" s="106"/>
-      <c r="F83" s="106"/>
-      <c r="G83" s="108"/>
-      <c r="H83" s="106"/>
-      <c r="I83" s="108"/>
-      <c r="J83" s="102"/>
+      <c r="A83" s="104"/>
+      <c r="B83" s="100"/>
+      <c r="C83" s="105"/>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="104"/>
+      <c r="G83" s="106"/>
+      <c r="H83" s="104"/>
+      <c r="I83" s="106"/>
+      <c r="J83" s="100"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
-      <c r="C84" s="119"/>
+      <c r="C84" s="117"/>
       <c r="D84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
-      <c r="C85" s="119"/>
+      <c r="C85" s="117"/>
       <c r="D85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="148"/>
-      <c r="B86" s="149" t="s">
-        <v>127</v>
-      </c>
-      <c r="C86" s="150" t="s">
-        <v>128</v>
-      </c>
-      <c r="D86" s="149"/>
-      <c r="E86" s="151" t="s">
+      <c r="A86" s="146"/>
+      <c r="B86" s="147" t="s">
+        <v>131</v>
+      </c>
+      <c r="C86" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86" s="147"/>
+      <c r="E86" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="F86" s="151"/>
-      <c r="G86" s="152" t="s">
-        <v>129</v>
-      </c>
-      <c r="H86" s="149" t="s">
-        <v>130</v>
-      </c>
-      <c r="I86" s="149" t="s">
-        <v>131</v>
-      </c>
-      <c r="J86" s="153"/>
+      <c r="F86" s="149"/>
+      <c r="G86" s="150" t="s">
+        <v>133</v>
+      </c>
+      <c r="H86" s="147" t="s">
+        <v>134</v>
+      </c>
+      <c r="I86" s="147" t="s">
+        <v>135</v>
+      </c>
+      <c r="J86" s="151"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="103" t="s">
-        <v>187</v>
-      </c>
-      <c r="B87" s="76" t="s">
+      <c r="A87" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="C87" s="172" t="n">
+      <c r="C87" s="170" t="n">
         <v>45603</v>
       </c>
-      <c r="D87" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="E87" s="114" t="n">
+      <c r="D87" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="E87" s="112" t="n">
         <v>156000</v>
       </c>
-      <c r="F87" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="G87" s="96"/>
+      <c r="F87" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="G87" s="94"/>
       <c r="H87" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J87" s="153"/>
+      <c r="J87" s="151"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="103"/>
-      <c r="B88" s="74"/>
-      <c r="C88" s="95"/>
-      <c r="D88" s="103"/>
-      <c r="E88" s="74"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="96"/>
-      <c r="H88" s="116" t="s">
-        <v>189</v>
+      <c r="A88" s="101"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="93"/>
+      <c r="D88" s="101"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="101"/>
+      <c r="G88" s="94"/>
+      <c r="H88" s="114" t="s">
+        <v>193</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J88" s="153"/>
+      <c r="J88" s="151"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
-      <c r="B89" s="118" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" s="135" t="n">
+      <c r="B89" s="116" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" s="133" t="n">
         <v>45704</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="J89" s="153"/>
+      <c r="J89" s="151"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C90" s="57" t="n">
+      <c r="C90" s="55" t="n">
         <v>45705</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="J90" s="153"/>
+      <c r="J90" s="151"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
-      <c r="J91" s="153"/>
+      <c r="J91" s="151"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
-      <c r="C92" s="119" t="s">
-        <v>149</v>
+      <c r="C92" s="117" t="s">
+        <v>153</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="G92" s="173"/>
+        <v>177</v>
+      </c>
+      <c r="G92" s="171"/>
       <c r="H92" s="3"/>
-      <c r="J92" s="153"/>
+      <c r="J92" s="151"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
-      <c r="C93" s="119" t="n">
+      <c r="C93" s="117" t="n">
         <v>45706</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="J93" s="153"/>
+      <c r="J93" s="151"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
-      <c r="C94" s="174" t="n">
+      <c r="C94" s="172" t="n">
         <v>45711</v>
       </c>
-      <c r="D94" s="137" t="s">
-        <v>174</v>
-      </c>
-      <c r="E94" s="137"/>
-      <c r="F94" s="137"/>
-      <c r="G94" s="139"/>
-      <c r="H94" s="137"/>
-      <c r="I94" s="140"/>
-      <c r="J94" s="153"/>
+      <c r="D94" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="E94" s="135"/>
+      <c r="F94" s="135"/>
+      <c r="G94" s="137"/>
+      <c r="H94" s="135"/>
+      <c r="I94" s="138"/>
+      <c r="J94" s="151"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C95" s="175"/>
+        <v>196</v>
+      </c>
+      <c r="C95" s="173"/>
       <c r="D95" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="J95" s="153"/>
+      <c r="J95" s="151"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="J96" s="153"/>
+      <c r="J96" s="151"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="D97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="105" t="s">
-        <v>195</v>
-      </c>
-      <c r="J97" s="153"/>
+      <c r="I97" s="103" t="s">
+        <v>199</v>
+      </c>
+      <c r="J97" s="151"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="105" t="s">
-        <v>179</v>
-      </c>
-      <c r="J98" s="153"/>
+      <c r="I98" s="103" t="s">
+        <v>183</v>
+      </c>
+      <c r="J98" s="151"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="176" t="s">
-        <v>156</v>
-      </c>
-      <c r="C99" s="177" t="n">
+      <c r="B99" s="174" t="s">
+        <v>160</v>
+      </c>
+      <c r="C99" s="175" t="n">
         <v>45792</v>
       </c>
-      <c r="D99" s="178" t="n">
+      <c r="D99" s="176" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="H99" s="25"/>
-      <c r="I99" s="25"/>
-      <c r="J99" s="153"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="151"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="153"/>
-      <c r="B100" s="179" t="s">
+      <c r="A100" s="151"/>
+      <c r="B100" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="180" t="n">
+      <c r="C100" s="178" t="n">
         <v>45939</v>
       </c>
-      <c r="D100" s="181" t="n">
+      <c r="D100" s="179" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E100" s="153"/>
-      <c r="F100" s="153"/>
-      <c r="G100" s="182"/>
-      <c r="H100" s="153"/>
-      <c r="I100" s="153"/>
-      <c r="J100" s="153"/>
+      <c r="E100" s="151"/>
+      <c r="F100" s="151"/>
+      <c r="G100" s="180"/>
+      <c r="H100" s="151"/>
+      <c r="I100" s="151"/>
+      <c r="J100" s="151"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="67"/>
-      <c r="B101" s="183"/>
-      <c r="C101" s="184"/>
-      <c r="D101" s="185"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="67"/>
-      <c r="G101" s="61"/>
-      <c r="H101" s="67"/>
-      <c r="I101" s="67"/>
-      <c r="J101" s="67"/>
+      <c r="A101" s="65"/>
+      <c r="B101" s="181"/>
+      <c r="C101" s="182"/>
+      <c r="D101" s="183"/>
+      <c r="E101" s="65"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="65"/>
+      <c r="I101" s="65"/>
+      <c r="J101" s="65"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="67"/>
-      <c r="B102" s="183"/>
-      <c r="C102" s="184"/>
-      <c r="D102" s="185"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="67"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="67"/>
-      <c r="I102" s="67"/>
-      <c r="J102" s="67"/>
+      <c r="A102" s="65"/>
+      <c r="B102" s="181"/>
+      <c r="C102" s="182"/>
+      <c r="D102" s="183"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="65"/>
+      <c r="J102" s="65"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="186"/>
-      <c r="B103" s="186"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="186"/>
-      <c r="E103" s="186"/>
-      <c r="F103" s="186"/>
-      <c r="G103" s="188"/>
-      <c r="H103" s="186"/>
-      <c r="I103" s="188"/>
+      <c r="A103" s="184"/>
+      <c r="B103" s="184"/>
+      <c r="C103" s="185"/>
+      <c r="D103" s="184"/>
+      <c r="E103" s="184"/>
+      <c r="F103" s="184"/>
+      <c r="G103" s="186"/>
+      <c r="H103" s="184"/>
+      <c r="I103" s="186"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="B104" s="76" t="s">
+      <c r="A104" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="B104" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="77" t="n">
+      <c r="C104" s="75" t="n">
         <v>45588</v>
       </c>
-      <c r="D104" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E104" s="78"/>
-      <c r="F104" s="78"/>
-      <c r="G104" s="189" t="n">
+      <c r="D104" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E104" s="76"/>
+      <c r="F104" s="76"/>
+      <c r="G104" s="187" t="n">
         <v>45672</v>
       </c>
-      <c r="H104" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="I104" s="80" t="n">
+      <c r="H104" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="I104" s="78" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="75"/>
-      <c r="B105" s="76" t="s">
-        <v>198</v>
-      </c>
-      <c r="C105" s="77"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="78"/>
-      <c r="F105" s="78"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="75"/>
-      <c r="I105" s="80"/>
+      <c r="A105" s="73"/>
+      <c r="B105" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="C105" s="75"/>
+      <c r="D105" s="73"/>
+      <c r="E105" s="76"/>
+      <c r="F105" s="76"/>
+      <c r="G105" s="187"/>
+      <c r="H105" s="73"/>
+      <c r="I105" s="78"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="B106" s="76" t="s">
+      <c r="A106" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="B106" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="C106" s="77" t="n">
+      <c r="C106" s="75" t="n">
         <v>45588</v>
       </c>
-      <c r="D106" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E106" s="78"/>
-      <c r="F106" s="78"/>
-      <c r="G106" s="189" t="n">
+      <c r="D106" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E106" s="76"/>
+      <c r="F106" s="76"/>
+      <c r="G106" s="187" t="n">
         <v>45672</v>
       </c>
-      <c r="H106" s="190" t="s">
-        <v>199</v>
-      </c>
-      <c r="I106" s="80" t="n">
+      <c r="H106" s="188" t="s">
+        <v>203</v>
+      </c>
+      <c r="I106" s="78" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="B107" s="76" t="s">
+      <c r="A107" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="B107" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="C107" s="191" t="n">
+      <c r="C107" s="189" t="n">
         <v>45475</v>
       </c>
-      <c r="D107" s="116" t="s">
-        <v>144</v>
-      </c>
-      <c r="E107" s="192" t="n">
+      <c r="D107" s="114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E107" s="190" t="n">
         <v>113</v>
       </c>
-      <c r="F107" s="116" t="s">
-        <v>133</v>
-      </c>
-      <c r="G107" s="189" t="n">
+      <c r="F107" s="114" t="s">
+        <v>137</v>
+      </c>
+      <c r="G107" s="187" t="n">
         <v>45672</v>
       </c>
-      <c r="H107" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="I107" s="193" t="n">
+      <c r="H107" s="114" t="s">
+        <v>192</v>
+      </c>
+      <c r="I107" s="191" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="116"/>
-      <c r="B108" s="76" t="s">
-        <v>200</v>
-      </c>
-      <c r="C108" s="191"/>
-      <c r="D108" s="116"/>
-      <c r="E108" s="192"/>
-      <c r="F108" s="116"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="116"/>
-      <c r="I108" s="193"/>
+      <c r="A108" s="114"/>
+      <c r="B108" s="74" t="s">
+        <v>204</v>
+      </c>
+      <c r="C108" s="189"/>
+      <c r="D108" s="114"/>
+      <c r="E108" s="190"/>
+      <c r="F108" s="114"/>
+      <c r="G108" s="187"/>
+      <c r="H108" s="114"/>
+      <c r="I108" s="191"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="B109" s="76" t="s">
+      <c r="A109" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="C109" s="191"/>
-      <c r="D109" s="116" t="s">
-        <v>144</v>
-      </c>
-      <c r="E109" s="192" t="n">
+      <c r="C109" s="189"/>
+      <c r="D109" s="114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E109" s="190" t="n">
         <v>113</v>
       </c>
-      <c r="F109" s="116" t="s">
-        <v>133</v>
-      </c>
-      <c r="G109" s="189" t="n">
+      <c r="F109" s="114" t="s">
+        <v>137</v>
+      </c>
+      <c r="G109" s="187" t="n">
         <v>45672</v>
       </c>
-      <c r="H109" s="194" t="s">
-        <v>189</v>
-      </c>
-      <c r="I109" s="193" t="n">
+      <c r="H109" s="192" t="s">
+        <v>193</v>
+      </c>
+      <c r="I109" s="191" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="195"/>
-      <c r="B113" s="186"/>
-      <c r="C113" s="187"/>
-      <c r="D113" s="195"/>
-      <c r="E113" s="186"/>
-      <c r="F113" s="188"/>
-      <c r="G113" s="188"/>
-      <c r="H113" s="188"/>
-      <c r="I113" s="188"/>
+      <c r="A113" s="193"/>
+      <c r="B113" s="184"/>
+      <c r="C113" s="185"/>
+      <c r="D113" s="193"/>
+      <c r="E113" s="184"/>
+      <c r="F113" s="186"/>
+      <c r="G113" s="186"/>
+      <c r="H113" s="186"/>
+      <c r="I113" s="186"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="B114" s="160" t="s">
+      <c r="A114" s="73" t="s">
+        <v>205</v>
+      </c>
+      <c r="B114" s="158" t="s">
         <v>100</v>
       </c>
-      <c r="C114" s="196" t="n">
+      <c r="C114" s="194" t="n">
         <v>45438</v>
       </c>
-      <c r="D114" s="75" t="s">
-        <v>144</v>
-      </c>
-      <c r="E114" s="75" t="n">
+      <c r="D114" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="197" t="s">
-        <v>202</v>
-      </c>
-      <c r="G114" s="79"/>
-      <c r="H114" s="75" t="s">
-        <v>203</v>
-      </c>
-      <c r="I114" s="79"/>
+      <c r="F114" s="195" t="s">
+        <v>206</v>
+      </c>
+      <c r="G114" s="77"/>
+      <c r="H114" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="75"/>
-      <c r="B115" s="198" t="s">
-        <v>204</v>
-      </c>
-      <c r="C115" s="199" t="n">
+      <c r="A115" s="73"/>
+      <c r="B115" s="196" t="s">
+        <v>208</v>
+      </c>
+      <c r="C115" s="197" t="n">
         <v>45486</v>
       </c>
-      <c r="D115" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="E115" s="75"/>
-      <c r="F115" s="200" t="s">
-        <v>202</v>
-      </c>
-      <c r="G115" s="201" t="n">
+      <c r="D115" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="E115" s="73"/>
+      <c r="F115" s="198" t="s">
+        <v>206</v>
+      </c>
+      <c r="G115" s="199" t="n">
         <v>45588</v>
       </c>
-      <c r="H115" s="75" t="s">
+      <c r="H115" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="I115" s="77"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="73"/>
+      <c r="B116" s="196" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" s="197" t="n">
+        <v>45590</v>
+      </c>
+      <c r="D116" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="E116" s="73"/>
+      <c r="F116" s="198" t="s">
         <v>206</v>
       </c>
-      <c r="I115" s="79"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="75"/>
-      <c r="B116" s="198" t="s">
-        <v>207</v>
-      </c>
-      <c r="C116" s="199" t="n">
-        <v>45590</v>
-      </c>
-      <c r="D116" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="E116" s="75"/>
-      <c r="F116" s="200" t="s">
-        <v>202</v>
-      </c>
-      <c r="G116" s="201" t="n">
+      <c r="G116" s="199" t="n">
         <v>45688</v>
       </c>
-      <c r="H116" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="I116" s="79"/>
+      <c r="H116" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="I116" s="77"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="75"/>
-      <c r="B117" s="202"/>
-      <c r="C117" s="203"/>
-      <c r="D117" s="202" t="s">
-        <v>209</v>
-      </c>
-      <c r="E117" s="202"/>
-      <c r="F117" s="204"/>
-      <c r="G117" s="205" t="n">
+      <c r="A117" s="73"/>
+      <c r="B117" s="200"/>
+      <c r="C117" s="201"/>
+      <c r="D117" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="E117" s="200"/>
+      <c r="F117" s="202"/>
+      <c r="G117" s="203" t="n">
         <v>45782</v>
       </c>
-      <c r="H117" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="I117" s="79"/>
+      <c r="H117" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="I117" s="77"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
-      <c r="B118" s="206"/>
-      <c r="C118" s="207"/>
+      <c r="B118" s="204"/>
+      <c r="C118" s="205"/>
       <c r="D118" s="3"/>
-      <c r="E118" s="206"/>
-      <c r="F118" s="208"/>
-      <c r="G118" s="209"/>
+      <c r="E118" s="204"/>
+      <c r="F118" s="206"/>
+      <c r="G118" s="207"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
-      <c r="B119" s="206"/>
-      <c r="C119" s="207"/>
+      <c r="B119" s="204"/>
+      <c r="C119" s="205"/>
       <c r="D119" s="3"/>
-      <c r="E119" s="206"/>
-      <c r="F119" s="208"/>
-      <c r="G119" s="209"/>
+      <c r="E119" s="204"/>
+      <c r="F119" s="206"/>
+      <c r="G119" s="207"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5323,7 +5560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5340,13 +5577,13 @@
         <v>45967</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5354,13 +5591,13 @@
         <v>45927</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5368,21 +5605,21 @@
         <v>45708</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5392,28 +5629,28 @@
       <c r="D8" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="E8" s="210" t="n">
+      <c r="E8" s="208" t="n">
         <v>0.416666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E15" s="210" t="n">
+      <c r="E15" s="208" t="n">
         <v>0.427083333333333</v>
       </c>
     </row>
@@ -5428,7 +5665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>

--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="hmb" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="244">
   <si>
     <t xml:space="preserve">dava tarihi</t>
   </si>
@@ -94,6 +94,9 @@
     <t xml:space="preserve">tanıklarla olan dava dosyaları istencek</t>
   </si>
   <si>
+    <t xml:space="preserve">Karar 1 yıl ceza – istinafa gidilecek</t>
+  </si>
+  <si>
     <t xml:space="preserve">ali umut balcı</t>
   </si>
   <si>
@@ -109,16 +112,181 @@
     <t xml:space="preserve">dosya TL</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/19105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-9-25*30-9-26 – 192500 TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 13 – icra – itiraz edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSYA AÇILACAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/12483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-9-2023-24 – 74000 TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 13 – icra – imzaya itiraz edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/22182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-9-2024 – 137314 TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut - 2.sulh huku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itirazın kaldırılması – 2024/12483 ve 2024/22182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adli tıptan rapor talebi -samsun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adli tıptan rapor talebi – istanbul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duruşma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*******</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/22053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metin çelik – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-9-2024-25 – 156000 TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metin çelik – 2. sulh hukuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itirazın kaldırılması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">istenmiş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 2 haftalık sürede ödeme makbuz tebliği</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- bankadan teyidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- hesap uzmanına yollama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/21115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut -icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 14-icra – imzaya itiraz edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samed turgut – 1. sulh hukuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atıpraporu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adli tıp raporunun beklenmesine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/12482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024- 158437 TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant – 2.sulh hukuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yemin için duruşma günü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yemin duruşması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/3369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ali demirel -icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ayşe uyar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 14 – itiraz edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ali demirel – 2.sulh hukuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emrullah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dava reddedildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">istinaf başvurusu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/1410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ali demirel – BAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*********</t>
+  </si>
+  <si>
+    <t xml:space="preserve">istinaf</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/3201</t>
   </si>
   <si>
-    <t xml:space="preserve">salih ant – icra</t>
-  </si>
-  <si>
     <t xml:space="preserve">yok</t>
   </si>
   <si>
-    <t xml:space="preserve">örnek 13</t>
+    <t xml:space="preserve">Örnek 13 – icra – itiraz edilmedi</t>
   </si>
   <si>
     <t xml:space="preserve">talep</t>
@@ -154,9 +322,6 @@
     <t xml:space="preserve">para hesaba geçmemiş</t>
   </si>
   <si>
-    <t xml:space="preserve">emrullah</t>
-  </si>
-  <si>
     <t xml:space="preserve">11-04-2026 ödeme yapacakmış</t>
   </si>
   <si>
@@ -166,174 +331,54 @@
     <t xml:space="preserve">30-04-2026 boşaltacakmış</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/19105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut</t>
+    <t xml:space="preserve">Avukattan 375000 TL umuta havale geldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant icraya 480000 TL ödeme yapmış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tahliye henüz olmadı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSYA KAPANDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/1266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salih ant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 14 – icra – itiraz edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İtirazın kaldırılması için dava açılmadı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tahliye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/12481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metin çelik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/21114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 14 – icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/9993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merdal kipel</t>
   </si>
   <si>
     <t xml:space="preserve">Örnek 13 – icra</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/1266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salih ant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 14 – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/12483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/22182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut - 2.sulh huku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itirazın kaldırılması – 2024/12483 ve 2024/22182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adli tıptan rapor talebi -samsun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adli tıptan rapor talebi – istanbul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*********</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/22053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metin çelik – icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metin çelik – 2. sulh hukuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itirazın kaldırılması</t>
-  </si>
-  <si>
-    <t xml:space="preserve">istenmiş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duruşma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 2 haftalık sürede ödeme makbuz tebliği</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- bankadan teyidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- hesap uzmanına yollama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*******</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/21115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut -icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samed turgut – 1. sulh hukuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atıpraporu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adli tıp raporunun beklenmesine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/12482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek 13 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salih ant – 2.sulh hukuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yemin için duruşma günü</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yemin duruşması</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/12481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metin çelik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/3369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ali demirel -icra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ayşe uyar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ali demirel – 2.sulh hukuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dava reddedildi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">istinaf başvurusu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/1410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ali demirel – BAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">istinaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/21114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024/9993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merdal kipel</t>
-  </si>
-  <si>
     <t xml:space="preserve">yatan para</t>
   </si>
   <si>
@@ -347,6 +392,9 @@
   </si>
   <si>
     <t xml:space="preserve">ahmet ilter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İzinsiz devir</t>
   </si>
   <si>
     <t xml:space="preserve">2023/64</t>
@@ -752,7 +800,7 @@
     <numFmt numFmtId="169" formatCode="hh:mm"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -808,6 +856,14 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
     <font>
       <b val="true"/>
@@ -966,7 +1022,7 @@
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -993,20 +1049,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFF10D0C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFC00000"/>
+        <fgColor rgb="FFF10D0C"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF860D"/>
+        <bgColor rgb="FFED7D31"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFB4C7DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1019,6 +1087,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
         <bgColor rgb="FFDDE8CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FF9DC3E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1048,7 +1122,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.3998"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFB4C7DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1066,7 +1140,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -1200,7 +1274,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="235">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1305,26 +1379,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1333,7 +1387,31 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1341,14 +1419,30 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1357,7 +1451,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1365,39 +1463,87 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1409,12 +1555,44 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1445,7 +1623,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1453,11 +1631,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1469,35 +1647,155 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1505,167 +1803,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1689,7 +1867,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1697,39 +1875,39 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1765,15 +1943,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1781,35 +1959,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="4" fillId="11" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="14" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1829,59 +2007,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="20" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1897,43 +2075,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="15" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1949,27 +2127,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="21" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="21" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="21" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1977,59 +2155,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="26" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="28" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2064,20 +2242,20 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFC5E0B4"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFDEEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FFF10D0C"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
@@ -2086,13 +2264,13 @@
       <rgbColor rgb="FFFFE994"/>
       <rgbColor rgb="FF9DC3E6"/>
       <rgbColor rgb="FFF4B183"/>
-      <rgbColor rgb="FFC5E0B4"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FFFFD966"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFC000"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF860D"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FFA9D18E"/>
@@ -2335,7 +2513,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2627,9 @@
       <c r="C20" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="24"/>
+      <c r="D20" s="24" t="s">
+        <v>22</v>
+      </c>
       <c r="F20" s="11"/>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2477,7 +2657,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.22"/>
@@ -2487,7 +2667,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2495,10 +2675,10 @@
         <v>45725</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2515,678 +2695,657 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3"/>
-      <c r="E4" s="4"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
-        <v>46076</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>27</v>
+        <v>45959</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>46088</v>
-      </c>
-      <c r="E5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>402082</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>515608</v>
+      <c r="D5" s="9"/>
+      <c r="E5" s="26" t="n">
+        <v>46009</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>196170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3"/>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="28" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="32"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B9" s="3"/>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3"/>
-      <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3"/>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="6" t="n">
+        <v>45475</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="26" t="n">
+        <v>45482</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>45604</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="26" t="n">
+        <v>45615</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>140835</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3"/>
-      <c r="C15" s="2" t="s">
+      <c r="D18" s="9"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="27"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>45704</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29" t="s">
+      <c r="C20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
-        <v>45959</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="31" t="n">
-        <v>46009</v>
-      </c>
-      <c r="F20" s="32" t="n">
-        <v>196170</v>
-      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="30"/>
+      <c r="A22" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3"/>
+      <c r="A23" s="36" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="39"/>
       <c r="E23" s="4"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="31" t="n">
-        <v>45698</v>
-      </c>
-      <c r="F24" s="32"/>
+      <c r="A24" s="18" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>0.377777777777778</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="40"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3"/>
-      <c r="C25" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="33"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="5"/>
+      <c r="A26" s="6" t="n">
+        <v>45603</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="26" t="n">
+        <v>45615</v>
+      </c>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
-        <v>45475</v>
-      </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5" t="n">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>45704</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3"/>
+      <c r="C30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="E30" s="4" t="n">
+        <v>86000</v>
+      </c>
+      <c r="F30" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="31" t="n">
-        <v>45482</v>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="8" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="n">
-        <v>45604</v>
-      </c>
-      <c r="B30" s="21" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3"/>
+      <c r="C32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="31" t="n">
-        <v>45615</v>
-      </c>
-      <c r="F30" s="32" t="n">
-        <v>140835</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="32"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" s="2"/>
       <c r="E32" s="4"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="3"/>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>45989</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="A34" s="18" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B34" s="23" t="n">
+        <v>0.413194444444444</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="40"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="27" t="n">
-        <v>46042</v>
-      </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="30"/>
+      <c r="B35" s="3"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="F35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="6" t="n">
+        <v>45588</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="26" t="n">
+        <v>45596</v>
+      </c>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3"/>
+      <c r="C37" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="n">
-        <v>45603</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="31" t="n">
-        <v>45615</v>
-      </c>
-      <c r="F38" s="32"/>
+      <c r="A38" s="1" t="n">
+        <v>45704</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="3"/>
-      <c r="C39" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A39" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="31"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="5" t="n">
-        <v>156000</v>
-      </c>
+      <c r="F39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>65</v>
+        <v>46036</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="3"/>
-      <c r="C41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>86000</v>
-      </c>
-      <c r="F41" s="35" t="s">
-        <v>68</v>
-      </c>
+      <c r="A41" s="36" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="39"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>46086</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A42" s="18" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B42" s="23" t="n">
+        <v>0.377083333333333</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="40"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3"/>
-      <c r="C43" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="3"/>
-      <c r="C44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="6" t="n">
+        <v>45475</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="26" t="n">
+        <v>45482</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>158437</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="n">
-        <v>46196</v>
-      </c>
-      <c r="B45" s="23" t="n">
-        <v>0.413194444444444</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="3"/>
+      <c r="C46" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="E46" s="4"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
-        <v>45588</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="31" t="n">
-        <v>45596</v>
-      </c>
-      <c r="F47" s="32"/>
+      <c r="A47" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3"/>
-      <c r="C48" s="2" t="s">
-        <v>76</v>
+      <c r="C48" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>77</v>
-      </c>
+        <v>46077</v>
+      </c>
+      <c r="B49" s="3"/>
       <c r="C49" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>46021</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="42" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B50" s="23" t="n">
+        <v>0.413194444444444</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>46036</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="B51" s="3"/>
       <c r="E51" s="4"/>
       <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="27" t="n">
-        <v>46155</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="30"/>
+      <c r="B52" s="3"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="F52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="3"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="5"/>
+      <c r="A53" s="0"/>
+      <c r="B53" s="0"/>
+      <c r="C53" s="0"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="3"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="5"/>
+      <c r="A54" s="0"/>
+      <c r="B54" s="0"/>
+      <c r="C54" s="0"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
-        <v>45475</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="31" t="n">
-        <v>45482</v>
-      </c>
-      <c r="F55" s="32" t="n">
-        <v>158437</v>
-      </c>
+      <c r="A55" s="0"/>
+      <c r="B55" s="0"/>
+      <c r="C55" s="0"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="3"/>
-      <c r="C56" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>46069</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="2"/>
       <c r="E57" s="4"/>
       <c r="F57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="3"/>
-      <c r="C58" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="5"/>
+      <c r="A58" s="6" t="n">
+        <v>45342</v>
+      </c>
+      <c r="B58" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="35"/>
+      <c r="F58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>46077</v>
-      </c>
       <c r="B59" s="3"/>
-      <c r="C59" s="2" t="s">
-        <v>85</v>
-      </c>
+      <c r="C59" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="2"/>
       <c r="E59" s="4"/>
       <c r="F59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="37" t="n">
-        <v>46175</v>
-      </c>
-      <c r="B60" s="23" t="n">
-        <v>0.413194444444444</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A60" s="44" t="n">
+        <v>45450</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
+        <v>45680</v>
+      </c>
       <c r="B61" s="3"/>
+      <c r="C61" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>78</v>
+      </c>
       <c r="E61" s="4"/>
       <c r="F61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="3"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="5"/>
+      <c r="A62" s="1" t="n">
+        <v>45726</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="n">
-        <v>46205</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" s="9"/>
-      <c r="E63" s="31" t="n">
-        <v>45482</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>86000</v>
-      </c>
+      <c r="A63" s="46" t="n">
+        <v>45765</v>
+      </c>
+      <c r="B63" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="32"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="3"/>
-      <c r="C64" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="C64" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="2"/>
       <c r="E64" s="4"/>
       <c r="F64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="33"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="2"/>
       <c r="E65" s="4"/>
       <c r="F65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="3"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="4"/>
       <c r="F66" s="5"/>
     </row>
@@ -3198,348 +3357,566 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="n">
-        <v>45342</v>
-      </c>
-      <c r="B68" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E68" s="34"/>
-      <c r="F68" s="32"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="3"/>
-      <c r="C69" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="48" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D69" s="50" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E69" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="49" t="n">
+        <v>402082</v>
+      </c>
+      <c r="G69" s="20" t="n">
+        <v>515608</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>45450</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="A70" s="48"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D70" s="52"/>
       <c r="E70" s="4"/>
       <c r="F70" s="5"/>
+      <c r="G70" s="52"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>94</v>
+      <c r="A71" s="48" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="5"/>
+      <c r="G71" s="52"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>45726</v>
+      <c r="A72" s="48" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="52"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="27" t="n">
-        <v>45765</v>
-      </c>
-      <c r="B73" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="D73" s="30"/>
+      <c r="A73" s="48" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="E73" s="4"/>
-      <c r="F73" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="52"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="3"/>
-      <c r="C74" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74" s="2"/>
+      <c r="A74" s="48" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="E74" s="4"/>
       <c r="F74" s="5"/>
+      <c r="G74" s="52"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="48" t="n">
+        <v>46121</v>
+      </c>
       <c r="B75" s="3"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="2"/>
+      <c r="C75" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="E75" s="4"/>
       <c r="F75" s="5"/>
+      <c r="G75" s="52"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="48" t="n">
+        <v>46122</v>
+      </c>
       <c r="B76" s="3"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="2"/>
+      <c r="C76" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="E76" s="4"/>
       <c r="F76" s="5"/>
+      <c r="G76" s="52"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="40" t="n">
-        <v>45588</v>
-      </c>
-      <c r="B77" s="41" t="s">
+      <c r="A77" s="48"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="52"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="48"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="52"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="48"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="52"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="48"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="32"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="52"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="48" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D77" s="43"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="45"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="40"/>
-      <c r="B78" s="41"/>
-      <c r="C78" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="D78" s="43"/>
-      <c r="E78" s="44"/>
-      <c r="F78" s="45"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="46" t="n">
-        <v>45438</v>
-      </c>
-      <c r="B79" s="47" t="s">
+      <c r="F81" s="5"/>
+      <c r="G81" s="52"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="48" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C79" s="48" t="s">
+      <c r="F82" s="5"/>
+      <c r="G82" s="52"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="48" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="D79" s="49"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="51"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="46"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="D80" s="49"/>
-      <c r="E80" s="50" t="s">
+      <c r="D83" s="53"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="55" t="n">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="48"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="F80" s="51" t="n">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="46" t="n">
-        <v>45288</v>
-      </c>
-      <c r="B81" s="52" t="s">
+      <c r="D84" s="53"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="52"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="48"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C81" s="53" t="s">
+      <c r="E85" s="4"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="52"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="D81" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="50"/>
-      <c r="F81" s="51"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="46"/>
-      <c r="B82" s="52"/>
-      <c r="C82" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="D82" s="53"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="51"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="46" t="n">
-        <v>45148</v>
-      </c>
-      <c r="B83" s="52" t="s">
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="3"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="5"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="48" t="n">
+        <v>45676</v>
+      </c>
+      <c r="B88" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C83" s="53" t="s">
+      <c r="C88" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="D83" s="53"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="51"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="46"/>
-      <c r="B84" s="52"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="51"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="46" t="n">
-        <v>44928</v>
-      </c>
-      <c r="B85" s="52" t="s">
+      <c r="D88" s="40"/>
+      <c r="E88" s="57" t="n">
+        <v>45698</v>
+      </c>
+      <c r="F88" s="58"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="48"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C85" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D85" s="53"/>
-      <c r="E85" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="F85" s="51" t="n">
-        <v>24316</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="46"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="53"/>
-      <c r="D86" s="53"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="51"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="46" t="n">
-        <v>44333</v>
-      </c>
-      <c r="B87" s="52" t="s">
+      <c r="E89" s="4"/>
+      <c r="F89" s="58"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="48"/>
+      <c r="B90" s="56"/>
+      <c r="C90" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C87" s="53" t="s">
+      <c r="D90" s="49"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="D87" s="53"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="51"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="46"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="53"/>
-      <c r="D88" s="53"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="51"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="3"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="5"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="3"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="5"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="3"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="5"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="3"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="5"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="91" s="63" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="36"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="60"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="62"/>
+    </row>
+    <row r="92" s="63" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="48" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B92" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="40"/>
+      <c r="E92" s="57" t="n">
+        <v>45482</v>
+      </c>
+      <c r="F92" s="58"/>
+    </row>
+    <row r="93" s="63" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="48"/>
       <c r="B93" s="3"/>
+      <c r="C93" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" s="0"/>
       <c r="E93" s="4"/>
-      <c r="F93" s="5"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="3"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="5"/>
+      <c r="F93" s="58"/>
+    </row>
+    <row r="94" s="63" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="48" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B94" s="56"/>
+      <c r="C94" s="49"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="58" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="3"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="54"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="4"/>
       <c r="F95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="3"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="5"/>
+      <c r="A96" s="64" t="n">
+        <v>45588</v>
+      </c>
+      <c r="B96" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C96" s="66" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="67"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="58" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
+      <c r="A97" s="64"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="D97" s="67"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="69"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="70" t="n">
+        <v>45438</v>
+      </c>
+      <c r="B98" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="C98" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="D98" s="73"/>
+      <c r="E98" s="74"/>
+      <c r="F98" s="75"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="70"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="D99" s="73"/>
+      <c r="E99" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F99" s="58" t="n">
+        <v>193500</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="2"/>
+      <c r="A100" s="70" t="n">
+        <v>45288</v>
+      </c>
+      <c r="B100" s="76" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="E100" s="74"/>
+      <c r="F100" s="75"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
+      <c r="A101" s="70"/>
+      <c r="B101" s="76"/>
+      <c r="C101" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="D101" s="77"/>
+      <c r="E101" s="74"/>
+      <c r="F101" s="75"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="70" t="n">
+        <v>45148</v>
+      </c>
+      <c r="B102" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="D102" s="77"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="79" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="70"/>
+      <c r="B103" s="76"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="74"/>
+      <c r="F103" s="75"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
+      <c r="A104" s="70" t="n">
+        <v>44928</v>
+      </c>
+      <c r="B104" s="76" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="D104" s="77"/>
+      <c r="E104" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" s="58" t="n">
+        <v>24316</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="70"/>
+      <c r="B105" s="76"/>
+      <c r="C105" s="77"/>
+      <c r="D105" s="77"/>
+      <c r="E105" s="74"/>
+      <c r="F105" s="75"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="2"/>
+      <c r="A106" s="70" t="n">
+        <v>44333</v>
+      </c>
+      <c r="B106" s="76" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D106" s="77"/>
+      <c r="E106" s="59"/>
+      <c r="F106" s="58"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="70"/>
+      <c r="B107" s="76"/>
+      <c r="C107" s="77"/>
+      <c r="D107" s="77"/>
+      <c r="E107" s="74"/>
+      <c r="F107" s="75"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="5"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0"/>
+      <c r="B109" s="0"/>
+      <c r="C109" s="0"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0"/>
+      <c r="B110" s="0"/>
+      <c r="C110" s="0"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0"/>
+      <c r="B111" s="0"/>
+      <c r="C111" s="0"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="5"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="3"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="5"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="3"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="80"/>
+      <c r="F114" s="5"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="3"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="5"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="2"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="2"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="2"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="2"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="2"/>
-    </row>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="2"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="2"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="2"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="2"/>
+    </row>
     <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3613,48 +3990,48 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C7" s="13"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="3"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="3"/>
       <c r="D10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="16"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17"/>
       <c r="C12" s="16"/>
       <c r="D12" s="11"/>
@@ -3733,9 +4110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -3752,51 +4127,50 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C11" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="3"/>
       <c r="D14" s="15"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17"/>
       <c r="C16" s="16"/>
       <c r="D16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
         <v>46177</v>
       </c>
@@ -3844,7 +4218,7 @@
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="55" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="81" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="4"/>
@@ -3854,105 +4228,105 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="A1" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="56"/>
-      <c r="B2" s="60" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="86" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="56"/>
-      <c r="B4" s="61" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="60" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" s="57"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="87" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="86" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="86" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="86" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="83"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="56"/>
-      <c r="B5" s="61" t="s">
-        <v>117</v>
+      <c r="A5" s="82"/>
+      <c r="B5" s="87" t="s">
+        <v>133</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="57"/>
+        <v>105</v>
+      </c>
+      <c r="D5" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="83"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="56"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56"/>
-      <c r="B7" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="55" t="n">
+      <c r="A7" s="82"/>
+      <c r="B7" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="81" t="n">
         <v>45827</v>
       </c>
-      <c r="D7" s="58" t="s">
-        <v>124</v>
+      <c r="D7" s="84" t="s">
+        <v>140</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>9</v>
@@ -3960,77 +4334,77 @@
       <c r="F7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H7" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="57"/>
+      <c r="H7" s="83" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56"/>
-      <c r="B9" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="55" t="n">
+      <c r="A9" s="82"/>
+      <c r="B9" s="90" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="81" t="n">
         <v>45939</v>
       </c>
-      <c r="D9" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="65" t="n">
+      <c r="D9" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="91" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="65" t="n">
+      <c r="F9" s="91" t="n">
         <v>30</v>
       </c>
-      <c r="H9" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="57"/>
+      <c r="H9" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="56"/>
-      <c r="B10" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="58" t="n">
+      <c r="A10" s="82"/>
+      <c r="B10" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="84" t="n">
         <v>45939</v>
       </c>
-      <c r="D10" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="57" t="n">
+      <c r="D10" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="83" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="57" t="n">
+      <c r="F10" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" s="57"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="56"/>
-      <c r="B11" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="58" t="n">
+      <c r="A11" s="82"/>
+      <c r="B11" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="84" t="n">
         <v>45952</v>
       </c>
-      <c r="D11" s="57" t="s">
-        <v>129</v>
+      <c r="D11" s="83" t="s">
+        <v>145</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>9</v>
@@ -4038,227 +4412,227 @@
       <c r="F11" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="59"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="85"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="56"/>
-      <c r="B12" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="58" t="n">
+      <c r="A12" s="82"/>
+      <c r="B12" s="90" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="84" t="n">
         <v>45952</v>
       </c>
-      <c r="D12" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="57" t="n">
+      <c r="D12" s="83" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="83" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="57" t="n">
+      <c r="F12" s="83" t="n">
         <v>35</v>
       </c>
-      <c r="G12" s="59"/>
-      <c r="H12" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" s="59"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="85"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="56"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="59"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="85"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="56"/>
-      <c r="I14" s="57"/>
+      <c r="A14" s="82"/>
+      <c r="I14" s="83"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="56"/>
-      <c r="I15" s="57"/>
+      <c r="A15" s="82"/>
+      <c r="I15" s="83"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="66"/>
+      <c r="A16" s="92"/>
       <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="67"/>
-      <c r="B17" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="70" t="s">
+      <c r="A17" s="93"/>
+      <c r="B17" s="94" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="94"/>
+      <c r="E17" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71" t="s">
-        <v>133</v>
-      </c>
-      <c r="H17" s="68" t="s">
+      <c r="F17" s="96"/>
+      <c r="G17" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="94" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="J17" s="98"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="I17" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="J17" s="72"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="74" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="75" t="n">
+      <c r="B18" s="100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="101" t="n">
         <v>45342</v>
       </c>
-      <c r="D18" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77" t="s">
-        <v>137</v>
-      </c>
-      <c r="G18" s="78"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="72"/>
+      <c r="D18" s="99" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="102"/>
+      <c r="F18" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="104"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="98"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="73"/>
-      <c r="B19" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="75" t="n">
+      <c r="A19" s="99"/>
+      <c r="B19" s="105" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="101" t="n">
         <v>45537</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="80" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" s="78" t="n">
+      <c r="D19" s="99" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="102"/>
+      <c r="F19" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="104" t="n">
         <v>45691</v>
       </c>
-      <c r="H19" s="76"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="72"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="98"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83" t="s">
-        <v>141</v>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="109" t="s">
+        <v>157</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="72"/>
+      <c r="J20" s="98"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="C21" s="84" t="n">
+      <c r="C21" s="110" t="n">
         <v>45726</v>
       </c>
-      <c r="D21" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="85"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="86"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="72"/>
+      <c r="D21" s="111" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="111"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="98"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="72"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="66"/>
-      <c r="J23" s="72"/>
+      <c r="A23" s="92"/>
+      <c r="J23" s="98"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="92"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
+      <c r="A24" s="118"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="66"/>
+      <c r="A25" s="92"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="66"/>
+      <c r="A26" s="92"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="95"/>
-      <c r="B27" s="96" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="97" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="96"/>
-      <c r="E27" s="98" t="s">
+      <c r="A27" s="121"/>
+      <c r="B27" s="122" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="123" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="122"/>
+      <c r="E27" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="98"/>
-      <c r="G27" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="H27" s="96" t="s">
-        <v>134</v>
-      </c>
-      <c r="I27" s="96" t="s">
-        <v>135</v>
-      </c>
-      <c r="J27" s="100"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="125" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="122" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="122" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="126"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="66" t="s">
-        <v>143</v>
+      <c r="A28" s="92" t="s">
+        <v>159</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="101" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="102" t="n">
+        <v>160</v>
+      </c>
+      <c r="H28" s="127" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="128" t="n">
         <v>45712</v>
       </c>
-      <c r="J28" s="100"/>
+      <c r="J28" s="126"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="66"/>
-      <c r="J29" s="100"/>
+      <c r="A29" s="92"/>
+      <c r="J29" s="126"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
@@ -4267,420 +4641,420 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="103" t="s">
-        <v>146</v>
-      </c>
-      <c r="J30" s="100"/>
+      <c r="I30" s="129" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="126"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="104"/>
-      <c r="B31" s="100"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="100"/>
+      <c r="A31" s="130"/>
+      <c r="B31" s="126"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="126"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="66"/>
+      <c r="A32" s="92"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="66"/>
+      <c r="A33" s="92"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="107"/>
-      <c r="B34" s="108" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="108"/>
-      <c r="E34" s="110" t="s">
+      <c r="A34" s="133"/>
+      <c r="B34" s="134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="135" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="134"/>
+      <c r="E34" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="110"/>
-      <c r="G34" s="111" t="s">
-        <v>133</v>
-      </c>
-      <c r="H34" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="I34" s="108" t="s">
-        <v>135</v>
-      </c>
-      <c r="J34" s="72"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="137" t="s">
+        <v>149</v>
+      </c>
+      <c r="H34" s="134" t="s">
+        <v>150</v>
+      </c>
+      <c r="I34" s="134" t="s">
+        <v>151</v>
+      </c>
+      <c r="J34" s="98"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="104" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="74" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="93" t="n">
+      <c r="A35" s="130" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="119" t="n">
         <v>45475</v>
       </c>
-      <c r="D35" s="101" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="112" t="n">
+      <c r="D35" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" s="138" t="n">
         <v>97</v>
       </c>
-      <c r="F35" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="H35" s="101" t="s">
-        <v>149</v>
-      </c>
-      <c r="I35" s="94" t="n">
+      <c r="F35" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" s="127" t="s">
+        <v>165</v>
+      </c>
+      <c r="I35" s="120" t="n">
         <v>45705</v>
       </c>
-      <c r="J35" s="72"/>
+      <c r="J35" s="98"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="101"/>
-      <c r="B36" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="93" t="n">
+      <c r="A36" s="127"/>
+      <c r="B36" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="119" t="n">
         <v>45604</v>
       </c>
-      <c r="D36" s="101" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="112" t="n">
+      <c r="D36" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="138" t="n">
         <v>178</v>
       </c>
-      <c r="F36" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="115" t="n">
+      <c r="F36" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="140" t="s">
+        <v>166</v>
+      </c>
+      <c r="I36" s="141" t="n">
         <v>45705</v>
       </c>
-      <c r="J36" s="72"/>
+      <c r="J36" s="98"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
-      <c r="B37" s="116" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="55" t="n">
+      <c r="B37" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="81" t="n">
         <v>45704</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="J37" s="72"/>
+        <v>167</v>
+      </c>
+      <c r="J37" s="98"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="55" t="n">
+        <v>89</v>
+      </c>
+      <c r="C38" s="81" t="n">
         <v>45705</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="J38" s="72"/>
+      <c r="J38" s="98"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
-      <c r="C39" s="117"/>
+      <c r="C39" s="143"/>
       <c r="D39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="J39" s="72"/>
+      <c r="J39" s="98"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
-      <c r="C40" s="117" t="s">
-        <v>153</v>
+      <c r="C40" s="143" t="s">
+        <v>169</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="J40" s="72"/>
+      <c r="J40" s="98"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
-      <c r="C41" s="118" t="n">
+      <c r="C41" s="144" t="n">
         <v>45717</v>
       </c>
-      <c r="D41" s="119" t="s">
+      <c r="D41" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="120" t="s">
-        <v>155</v>
-      </c>
-      <c r="F41" s="119"/>
-      <c r="G41" s="121"/>
-      <c r="H41" s="119" t="s">
-        <v>156</v>
-      </c>
-      <c r="I41" s="122" t="s">
-        <v>157</v>
-      </c>
-      <c r="J41" s="72"/>
+      <c r="E41" s="146" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="145"/>
+      <c r="G41" s="147"/>
+      <c r="H41" s="145" t="s">
+        <v>172</v>
+      </c>
+      <c r="I41" s="148" t="s">
+        <v>173</v>
+      </c>
+      <c r="J41" s="98"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
-      <c r="C42" s="123"/>
+      <c r="C42" s="149"/>
       <c r="D42" s="3" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J42" s="72"/>
+        <v>175</v>
+      </c>
+      <c r="J42" s="98"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="124"/>
-      <c r="B43" s="125" t="s">
-        <v>160</v>
-      </c>
-      <c r="C43" s="126" t="n">
+      <c r="A43" s="150"/>
+      <c r="B43" s="151" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="152" t="n">
         <v>45805</v>
       </c>
-      <c r="D43" s="127" t="n">
+      <c r="D43" s="153" t="n">
         <v>0.409722222222222</v>
       </c>
-      <c r="E43" s="124" t="s">
-        <v>161</v>
-      </c>
-      <c r="F43" s="124"/>
-      <c r="G43" s="128"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="128"/>
-      <c r="J43" s="129"/>
+      <c r="E43" s="150" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="150"/>
+      <c r="G43" s="154"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="154"/>
+      <c r="J43" s="155"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="101"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="130" t="n">
+      <c r="A44" s="127"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="156" t="n">
         <v>45805</v>
       </c>
-      <c r="D44" s="112" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="94"/>
-      <c r="J44" s="72"/>
+      <c r="D44" s="138" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="120"/>
+      <c r="J44" s="98"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
-      <c r="C46" s="117"/>
+      <c r="C46" s="143"/>
       <c r="D46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="107"/>
-      <c r="B47" s="108" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="108"/>
-      <c r="E47" s="110" t="s">
+      <c r="A47" s="133"/>
+      <c r="B47" s="134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" s="135" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="134"/>
+      <c r="E47" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="110"/>
-      <c r="G47" s="111" t="s">
-        <v>133</v>
-      </c>
-      <c r="H47" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="I47" s="108" t="s">
-        <v>135</v>
-      </c>
-      <c r="J47" s="72"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="137" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" s="134" t="s">
+        <v>150</v>
+      </c>
+      <c r="I47" s="134" t="s">
+        <v>151</v>
+      </c>
+      <c r="J47" s="98"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="101" t="s">
-        <v>147</v>
-      </c>
-      <c r="B48" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="132" t="n">
+      <c r="A48" s="127" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="158" t="n">
         <v>45588</v>
       </c>
-      <c r="D48" s="112" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" s="72"/>
-      <c r="F48" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="H48" s="101" t="s">
-        <v>164</v>
-      </c>
-      <c r="I48" s="94" t="n">
+      <c r="D48" s="138" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" s="98"/>
+      <c r="F48" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="I48" s="120" t="n">
         <v>45630</v>
       </c>
-      <c r="J48" s="72"/>
+      <c r="J48" s="98"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="101"/>
-      <c r="B49" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="93"/>
-      <c r="D49" s="101"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="101"/>
-      <c r="H49" s="114" t="s">
-        <v>165</v>
-      </c>
-      <c r="I49" s="94" t="n">
+      <c r="A49" s="127"/>
+      <c r="B49" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="119"/>
+      <c r="D49" s="127"/>
+      <c r="E49" s="98"/>
+      <c r="F49" s="127"/>
+      <c r="H49" s="140" t="s">
+        <v>181</v>
+      </c>
+      <c r="I49" s="120" t="n">
         <v>45630</v>
       </c>
-      <c r="J49" s="72"/>
+      <c r="J49" s="98"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="101"/>
-      <c r="B50" s="116" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="133" t="n">
+      <c r="A50" s="127"/>
+      <c r="B50" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="159" t="n">
         <v>45704</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="J50" s="72"/>
+      <c r="J50" s="98"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="55" t="n">
+        <v>89</v>
+      </c>
+      <c r="C51" s="81" t="n">
         <v>45709</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="J51" s="72"/>
+      <c r="J51" s="98"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
-      <c r="C52" s="117" t="s">
-        <v>153</v>
+      <c r="C52" s="143" t="s">
+        <v>169</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="J52" s="72"/>
+      <c r="J52" s="98"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
-      <c r="C53" s="117" t="n">
+      <c r="C53" s="143" t="n">
         <v>45712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="J53" s="72"/>
+      <c r="J53" s="98"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
-      <c r="C54" s="134" t="n">
+      <c r="C54" s="160" t="n">
         <v>45717</v>
       </c>
-      <c r="D54" s="135" t="s">
+      <c r="D54" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="136" t="s">
-        <v>155</v>
-      </c>
-      <c r="F54" s="135"/>
-      <c r="G54" s="137"/>
-      <c r="H54" s="135" t="s">
-        <v>156</v>
-      </c>
-      <c r="I54" s="138"/>
-      <c r="J54" s="72"/>
+      <c r="E54" s="162" t="s">
+        <v>171</v>
+      </c>
+      <c r="F54" s="161"/>
+      <c r="G54" s="163"/>
+      <c r="H54" s="161" t="s">
+        <v>172</v>
+      </c>
+      <c r="I54" s="164"/>
+      <c r="J54" s="98"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="140"/>
-      <c r="I55" s="139"/>
-      <c r="J55" s="72"/>
+      <c r="G55" s="165"/>
+      <c r="H55" s="166"/>
+      <c r="I55" s="165"/>
+      <c r="J55" s="98"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="F56" s="1"/>
-      <c r="G56" s="139"/>
-      <c r="H56" s="140"/>
-      <c r="I56" s="141" t="s">
-        <v>157</v>
-      </c>
-      <c r="J56" s="72"/>
+      <c r="G56" s="165"/>
+      <c r="H56" s="166"/>
+      <c r="I56" s="167" t="s">
+        <v>173</v>
+      </c>
+      <c r="J56" s="98"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
-      <c r="B57" s="142" t="s">
-        <v>160</v>
-      </c>
-      <c r="C57" s="143" t="n">
+      <c r="B57" s="168" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" s="169" t="n">
         <v>45805</v>
       </c>
-      <c r="D57" s="144" t="n">
+      <c r="D57" s="170" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="72"/>
+      <c r="J57" s="98"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="101"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="145" t="n">
+      <c r="A58" s="127"/>
+      <c r="B58" s="98"/>
+      <c r="C58" s="171" t="n">
         <v>45805</v>
       </c>
-      <c r="D58" s="101" t="s">
-        <v>170</v>
-      </c>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="94"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="94"/>
-      <c r="J58" s="72"/>
+      <c r="D58" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="98"/>
+      <c r="F58" s="98"/>
+      <c r="G58" s="120"/>
+      <c r="H58" s="98"/>
+      <c r="I58" s="120"/>
+      <c r="J58" s="98"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="13"/>
-      <c r="C59" s="117"/>
+      <c r="C59" s="143"/>
       <c r="D59" s="3"/>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
@@ -4690,7 +5064,7 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="13"/>
-      <c r="C60" s="117"/>
+      <c r="C60" s="143"/>
       <c r="D60" s="3"/>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
@@ -4705,307 +5079,307 @@
       <c r="H61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="146"/>
-      <c r="B62" s="147" t="s">
-        <v>131</v>
-      </c>
-      <c r="C62" s="148" t="s">
-        <v>132</v>
-      </c>
-      <c r="D62" s="147"/>
-      <c r="E62" s="149" t="s">
+      <c r="A62" s="172"/>
+      <c r="B62" s="173" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="174" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="173"/>
+      <c r="E62" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="149"/>
-      <c r="G62" s="150" t="s">
-        <v>133</v>
-      </c>
-      <c r="H62" s="147" t="s">
-        <v>134</v>
-      </c>
-      <c r="I62" s="147" t="s">
-        <v>135</v>
-      </c>
-      <c r="J62" s="151"/>
+      <c r="F62" s="175"/>
+      <c r="G62" s="176" t="s">
+        <v>149</v>
+      </c>
+      <c r="H62" s="173" t="s">
+        <v>150</v>
+      </c>
+      <c r="I62" s="173" t="s">
+        <v>151</v>
+      </c>
+      <c r="J62" s="177"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="104" t="s">
-        <v>171</v>
-      </c>
-      <c r="B63" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="93" t="n">
+      <c r="A63" s="130" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="119" t="n">
         <v>45475</v>
       </c>
-      <c r="D63" s="101" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="112" t="n">
+      <c r="D63" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E63" s="138" t="n">
         <v>214</v>
       </c>
-      <c r="F63" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="H63" s="101" t="s">
-        <v>172</v>
-      </c>
-      <c r="I63" s="94" t="n">
+      <c r="F63" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="H63" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="I63" s="120" t="n">
         <v>45702</v>
       </c>
-      <c r="J63" s="151"/>
+      <c r="J63" s="177"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="104"/>
-      <c r="B64" s="72"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="152" t="n">
+      <c r="A64" s="130"/>
+      <c r="B64" s="98"/>
+      <c r="C64" s="119"/>
+      <c r="D64" s="178" t="n">
         <v>158437</v>
       </c>
-      <c r="E64" s="72"/>
-      <c r="F64" s="101"/>
-      <c r="H64" s="114" t="s">
-        <v>173</v>
-      </c>
-      <c r="I64" s="94" t="n">
+      <c r="E64" s="98"/>
+      <c r="F64" s="127"/>
+      <c r="H64" s="140" t="s">
+        <v>189</v>
+      </c>
+      <c r="I64" s="120" t="n">
         <v>45702</v>
       </c>
-      <c r="J64" s="151"/>
+      <c r="J64" s="177"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
-      <c r="B65" s="116" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="55" t="n">
+      <c r="B65" s="142" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="81" t="n">
         <v>45704</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="J65" s="151"/>
+      <c r="J65" s="177"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="55" t="n">
+        <v>89</v>
+      </c>
+      <c r="C66" s="81" t="n">
         <v>45705</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="J66" s="151"/>
+      <c r="J66" s="177"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="J67" s="151"/>
+      <c r="J67" s="177"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
-      <c r="C68" s="117" t="s">
-        <v>153</v>
+      <c r="C68" s="143" t="s">
+        <v>169</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="J68" s="151"/>
+      <c r="J68" s="177"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
-      <c r="C69" s="153" t="n">
+      <c r="C69" s="179" t="n">
         <v>45711</v>
       </c>
-      <c r="D69" s="154" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" s="154"/>
-      <c r="F69" s="154"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="154"/>
-      <c r="I69" s="156"/>
-      <c r="J69" s="151"/>
+      <c r="D69" s="180" t="s">
+        <v>194</v>
+      </c>
+      <c r="E69" s="180"/>
+      <c r="F69" s="180"/>
+      <c r="G69" s="181"/>
+      <c r="H69" s="180"/>
+      <c r="I69" s="182"/>
+      <c r="J69" s="177"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B70" s="13"/>
-      <c r="C70" s="123" t="s">
-        <v>179</v>
-      </c>
-      <c r="D70" s="140"/>
-      <c r="E70" s="140"/>
-      <c r="F70" s="140"/>
-      <c r="G70" s="139"/>
-      <c r="H70" s="140"/>
-      <c r="I70" s="139"/>
-      <c r="J70" s="151"/>
+      <c r="C70" s="149" t="s">
+        <v>195</v>
+      </c>
+      <c r="D70" s="166"/>
+      <c r="E70" s="166"/>
+      <c r="F70" s="166"/>
+      <c r="G70" s="165"/>
+      <c r="H70" s="166"/>
+      <c r="I70" s="165"/>
+      <c r="J70" s="177"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B71" s="13"/>
-      <c r="C71" s="123" t="s">
-        <v>180</v>
+      <c r="C71" s="149" t="s">
+        <v>196</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="140"/>
-      <c r="F71" s="140"/>
-      <c r="G71" s="139"/>
-      <c r="H71" s="140"/>
-      <c r="I71" s="139"/>
-      <c r="J71" s="151"/>
+        <v>197</v>
+      </c>
+      <c r="E71" s="166"/>
+      <c r="F71" s="166"/>
+      <c r="G71" s="165"/>
+      <c r="H71" s="166"/>
+      <c r="I71" s="165"/>
+      <c r="J71" s="177"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="103" t="s">
-        <v>183</v>
-      </c>
-      <c r="J72" s="151"/>
+      <c r="I72" s="129" t="s">
+        <v>199</v>
+      </c>
+      <c r="J72" s="177"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
-      <c r="C73" s="123"/>
+      <c r="C73" s="149"/>
       <c r="D73" s="3" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="103" t="s">
-        <v>185</v>
-      </c>
-      <c r="J73" s="151"/>
+      <c r="I73" s="129" t="s">
+        <v>201</v>
+      </c>
+      <c r="J73" s="177"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
-      <c r="B74" s="125" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="157" t="n">
+      <c r="B74" s="151" t="s">
+        <v>176</v>
+      </c>
+      <c r="C74" s="183" t="n">
         <v>45792</v>
       </c>
-      <c r="D74" s="127" t="n">
+      <c r="D74" s="153" t="n">
         <v>0.399305555555556</v>
       </c>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
-      <c r="J74" s="151"/>
+      <c r="J74" s="177"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="158"/>
-      <c r="B75" s="159" t="s">
-        <v>69</v>
-      </c>
-      <c r="C75" s="160" t="n">
+      <c r="A75" s="184"/>
+      <c r="B75" s="185" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="186" t="n">
         <v>45939</v>
       </c>
-      <c r="D75" s="161" t="n">
+      <c r="D75" s="187" t="n">
         <v>0.402777777777778</v>
       </c>
-      <c r="E75" s="162"/>
-      <c r="F75" s="162"/>
-      <c r="G75" s="163" t="s">
-        <v>186</v>
-      </c>
-      <c r="H75" s="163" t="s">
-        <v>187</v>
-      </c>
-      <c r="I75" s="163" t="s">
-        <v>188</v>
-      </c>
-      <c r="J75" s="151"/>
+      <c r="E75" s="188"/>
+      <c r="F75" s="188"/>
+      <c r="G75" s="189" t="s">
+        <v>202</v>
+      </c>
+      <c r="H75" s="189" t="s">
+        <v>203</v>
+      </c>
+      <c r="I75" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="J75" s="177"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
-      <c r="C76" s="117"/>
+      <c r="C76" s="143"/>
       <c r="D76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
-      <c r="C77" s="117"/>
+      <c r="C77" s="143"/>
       <c r="D77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="164"/>
-      <c r="B78" s="165" t="s">
-        <v>131</v>
-      </c>
-      <c r="C78" s="166" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" s="165"/>
-      <c r="E78" s="167" t="s">
+      <c r="A78" s="190"/>
+      <c r="B78" s="191" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="192" t="s">
+        <v>148</v>
+      </c>
+      <c r="D78" s="191"/>
+      <c r="E78" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="167"/>
-      <c r="G78" s="168" t="s">
-        <v>133</v>
-      </c>
-      <c r="H78" s="165" t="s">
-        <v>134</v>
-      </c>
-      <c r="I78" s="165" t="s">
-        <v>135</v>
-      </c>
-      <c r="J78" s="100"/>
+      <c r="F78" s="193"/>
+      <c r="G78" s="194" t="s">
+        <v>149</v>
+      </c>
+      <c r="H78" s="191" t="s">
+        <v>150</v>
+      </c>
+      <c r="I78" s="191" t="s">
+        <v>151</v>
+      </c>
+      <c r="J78" s="126"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="101" t="s">
-        <v>171</v>
-      </c>
-      <c r="B79" s="74" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="93" t="n">
+      <c r="A79" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C79" s="119" t="n">
         <v>45676</v>
       </c>
-      <c r="D79" s="112" t="s">
-        <v>163</v>
-      </c>
-      <c r="E79" s="101"/>
-      <c r="F79" s="101" t="s">
-        <v>137</v>
+      <c r="D79" s="138" t="s">
+        <v>179</v>
+      </c>
+      <c r="E79" s="127"/>
+      <c r="F79" s="127" t="s">
+        <v>153</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J79" s="100"/>
+        <v>205</v>
+      </c>
+      <c r="J79" s="126"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="101" t="s">
-        <v>171</v>
-      </c>
-      <c r="B80" s="74" t="s">
-        <v>49</v>
-      </c>
-      <c r="C80" s="93"/>
-      <c r="D80" s="101"/>
-      <c r="E80" s="101"/>
-      <c r="F80" s="101"/>
-      <c r="H80" s="114" t="s">
-        <v>190</v>
-      </c>
-      <c r="I80" s="169" t="n">
+      <c r="A80" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="B80" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C80" s="119"/>
+      <c r="D80" s="127"/>
+      <c r="E80" s="127"/>
+      <c r="F80" s="127"/>
+      <c r="H80" s="140" t="s">
+        <v>206</v>
+      </c>
+      <c r="I80" s="195" t="n">
         <v>45714</v>
       </c>
-      <c r="J80" s="100"/>
+      <c r="J80" s="126"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
@@ -5014,7 +5388,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="J81" s="100"/>
+      <c r="J81" s="126"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
@@ -5023,531 +5397,531 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="103" t="s">
-        <v>146</v>
-      </c>
-      <c r="J82" s="100"/>
+      <c r="I82" s="129" t="s">
+        <v>162</v>
+      </c>
+      <c r="J82" s="126"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="104"/>
-      <c r="B83" s="100"/>
-      <c r="C83" s="105"/>
-      <c r="D83" s="104"/>
-      <c r="E83" s="104"/>
-      <c r="F83" s="104"/>
-      <c r="G83" s="106"/>
-      <c r="H83" s="104"/>
-      <c r="I83" s="106"/>
-      <c r="J83" s="100"/>
+      <c r="A83" s="130"/>
+      <c r="B83" s="126"/>
+      <c r="C83" s="131"/>
+      <c r="D83" s="130"/>
+      <c r="E83" s="130"/>
+      <c r="F83" s="130"/>
+      <c r="G83" s="132"/>
+      <c r="H83" s="130"/>
+      <c r="I83" s="132"/>
+      <c r="J83" s="126"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
-      <c r="C84" s="117"/>
+      <c r="C84" s="143"/>
       <c r="D84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
-      <c r="C85" s="117"/>
+      <c r="C85" s="143"/>
       <c r="D85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="146"/>
-      <c r="B86" s="147" t="s">
-        <v>131</v>
-      </c>
-      <c r="C86" s="148" t="s">
-        <v>132</v>
-      </c>
-      <c r="D86" s="147"/>
-      <c r="E86" s="149" t="s">
+      <c r="A86" s="172"/>
+      <c r="B86" s="173" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" s="174" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" s="173"/>
+      <c r="E86" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="F86" s="149"/>
-      <c r="G86" s="150" t="s">
-        <v>133</v>
-      </c>
-      <c r="H86" s="147" t="s">
-        <v>134</v>
-      </c>
-      <c r="I86" s="147" t="s">
-        <v>135</v>
-      </c>
-      <c r="J86" s="151"/>
+      <c r="F86" s="175"/>
+      <c r="G86" s="176" t="s">
+        <v>149</v>
+      </c>
+      <c r="H86" s="173" t="s">
+        <v>150</v>
+      </c>
+      <c r="I86" s="173" t="s">
+        <v>151</v>
+      </c>
+      <c r="J86" s="177"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="101" t="s">
-        <v>191</v>
-      </c>
-      <c r="B87" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="C87" s="170" t="n">
+      <c r="A87" s="127" t="s">
+        <v>207</v>
+      </c>
+      <c r="B87" s="100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87" s="196" t="n">
         <v>45603</v>
       </c>
-      <c r="D87" s="101" t="s">
-        <v>148</v>
-      </c>
-      <c r="E87" s="112" t="n">
+      <c r="D87" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E87" s="138" t="n">
         <v>156000</v>
       </c>
-      <c r="F87" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="G87" s="94"/>
+      <c r="F87" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="G87" s="120"/>
       <c r="H87" s="3" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J87" s="151"/>
+      <c r="J87" s="177"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="101"/>
-      <c r="B88" s="72"/>
-      <c r="C88" s="93"/>
-      <c r="D88" s="101"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="101"/>
-      <c r="G88" s="94"/>
-      <c r="H88" s="114" t="s">
-        <v>193</v>
+      <c r="A88" s="127"/>
+      <c r="B88" s="98"/>
+      <c r="C88" s="119"/>
+      <c r="D88" s="127"/>
+      <c r="E88" s="98"/>
+      <c r="F88" s="127"/>
+      <c r="G88" s="120"/>
+      <c r="H88" s="140" t="s">
+        <v>209</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="J88" s="151"/>
+      <c r="J88" s="177"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
-      <c r="B89" s="116" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" s="133" t="n">
+      <c r="B89" s="142" t="s">
+        <v>210</v>
+      </c>
+      <c r="C89" s="159" t="n">
         <v>45704</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="J89" s="151"/>
+      <c r="J89" s="177"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C90" s="55" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" s="81" t="n">
         <v>45705</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="J90" s="151"/>
+      <c r="J90" s="177"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
-      <c r="J91" s="151"/>
+      <c r="J91" s="177"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
-      <c r="C92" s="117" t="s">
-        <v>153</v>
+      <c r="C92" s="143" t="s">
+        <v>169</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="G92" s="171"/>
+        <v>193</v>
+      </c>
+      <c r="G92" s="197"/>
       <c r="H92" s="3"/>
-      <c r="J92" s="151"/>
+      <c r="J92" s="177"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
-      <c r="C93" s="117" t="n">
+      <c r="C93" s="143" t="n">
         <v>45706</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="J93" s="151"/>
+      <c r="J93" s="177"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
-      <c r="C94" s="172" t="n">
+      <c r="C94" s="198" t="n">
         <v>45711</v>
       </c>
-      <c r="D94" s="135" t="s">
-        <v>178</v>
-      </c>
-      <c r="E94" s="135"/>
-      <c r="F94" s="135"/>
-      <c r="G94" s="137"/>
-      <c r="H94" s="135"/>
-      <c r="I94" s="138"/>
-      <c r="J94" s="151"/>
+      <c r="D94" s="161" t="s">
+        <v>194</v>
+      </c>
+      <c r="E94" s="161"/>
+      <c r="F94" s="161"/>
+      <c r="G94" s="163"/>
+      <c r="H94" s="161"/>
+      <c r="I94" s="164"/>
+      <c r="J94" s="177"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C95" s="173"/>
+        <v>212</v>
+      </c>
+      <c r="C95" s="199"/>
       <c r="D95" s="3" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="J95" s="151"/>
+      <c r="J95" s="177"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="J96" s="151"/>
+      <c r="J96" s="177"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="D97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="103" t="s">
-        <v>199</v>
-      </c>
-      <c r="J97" s="151"/>
+      <c r="I97" s="129" t="s">
+        <v>215</v>
+      </c>
+      <c r="J97" s="177"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="103" t="s">
-        <v>183</v>
-      </c>
-      <c r="J98" s="151"/>
+      <c r="I98" s="129" t="s">
+        <v>199</v>
+      </c>
+      <c r="J98" s="177"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="174" t="s">
-        <v>160</v>
-      </c>
-      <c r="C99" s="175" t="n">
+      <c r="B99" s="200" t="s">
+        <v>176</v>
+      </c>
+      <c r="C99" s="201" t="n">
         <v>45792</v>
       </c>
-      <c r="D99" s="176" t="n">
+      <c r="D99" s="202" t="n">
         <v>0.395833333333333</v>
       </c>
       <c r="E99" s="13"/>
       <c r="F99" s="13" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
-      <c r="J99" s="151"/>
+      <c r="J99" s="177"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="151"/>
-      <c r="B100" s="177" t="s">
-        <v>69</v>
-      </c>
-      <c r="C100" s="178" t="n">
+      <c r="A100" s="177"/>
+      <c r="B100" s="203" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100" s="204" t="n">
         <v>45939</v>
       </c>
-      <c r="D100" s="179" t="n">
+      <c r="D100" s="205" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E100" s="151"/>
-      <c r="F100" s="151"/>
-      <c r="G100" s="180"/>
-      <c r="H100" s="151"/>
-      <c r="I100" s="151"/>
-      <c r="J100" s="151"/>
+      <c r="E100" s="177"/>
+      <c r="F100" s="177"/>
+      <c r="G100" s="206"/>
+      <c r="H100" s="177"/>
+      <c r="I100" s="177"/>
+      <c r="J100" s="177"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="65"/>
-      <c r="B101" s="181"/>
-      <c r="C101" s="182"/>
-      <c r="D101" s="183"/>
-      <c r="E101" s="65"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="59"/>
-      <c r="H101" s="65"/>
-      <c r="I101" s="65"/>
-      <c r="J101" s="65"/>
+      <c r="A101" s="91"/>
+      <c r="B101" s="207"/>
+      <c r="C101" s="208"/>
+      <c r="D101" s="209"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
+      <c r="G101" s="85"/>
+      <c r="H101" s="91"/>
+      <c r="I101" s="91"/>
+      <c r="J101" s="91"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="65"/>
-      <c r="B102" s="181"/>
-      <c r="C102" s="182"/>
-      <c r="D102" s="183"/>
-      <c r="E102" s="65"/>
-      <c r="F102" s="65"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="65"/>
-      <c r="I102" s="65"/>
-      <c r="J102" s="65"/>
+      <c r="A102" s="91"/>
+      <c r="B102" s="207"/>
+      <c r="C102" s="208"/>
+      <c r="D102" s="209"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="91"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="91"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="184"/>
-      <c r="B103" s="184"/>
-      <c r="C103" s="185"/>
-      <c r="D103" s="184"/>
-      <c r="E103" s="184"/>
-      <c r="F103" s="184"/>
-      <c r="G103" s="186"/>
-      <c r="H103" s="184"/>
-      <c r="I103" s="186"/>
+      <c r="A103" s="210"/>
+      <c r="B103" s="210"/>
+      <c r="C103" s="211"/>
+      <c r="D103" s="210"/>
+      <c r="E103" s="210"/>
+      <c r="F103" s="210"/>
+      <c r="G103" s="212"/>
+      <c r="H103" s="210"/>
+      <c r="I103" s="212"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="B104" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C104" s="75" t="n">
+      <c r="A104" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" s="101" t="n">
         <v>45588</v>
       </c>
-      <c r="D104" s="73" t="s">
-        <v>163</v>
-      </c>
-      <c r="E104" s="76"/>
-      <c r="F104" s="76"/>
-      <c r="G104" s="187" t="n">
+      <c r="D104" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="213" t="n">
         <v>45672</v>
       </c>
-      <c r="H104" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="I104" s="78" t="n">
+      <c r="H104" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="I104" s="104" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="73"/>
-      <c r="B105" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="73"/>
-      <c r="E105" s="76"/>
-      <c r="F105" s="76"/>
-      <c r="G105" s="187"/>
-      <c r="H105" s="73"/>
-      <c r="I105" s="78"/>
+      <c r="A105" s="99"/>
+      <c r="B105" s="100" t="s">
+        <v>218</v>
+      </c>
+      <c r="C105" s="101"/>
+      <c r="D105" s="99"/>
+      <c r="E105" s="102"/>
+      <c r="F105" s="102"/>
+      <c r="G105" s="213"/>
+      <c r="H105" s="99"/>
+      <c r="I105" s="104"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C106" s="75" t="n">
+      <c r="A106" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="B106" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" s="101" t="n">
         <v>45588</v>
       </c>
-      <c r="D106" s="73" t="s">
-        <v>163</v>
-      </c>
-      <c r="E106" s="76"/>
-      <c r="F106" s="76"/>
-      <c r="G106" s="187" t="n">
+      <c r="D106" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="E106" s="102"/>
+      <c r="F106" s="102"/>
+      <c r="G106" s="213" t="n">
         <v>45672</v>
       </c>
-      <c r="H106" s="188" t="s">
-        <v>203</v>
-      </c>
-      <c r="I106" s="78" t="n">
+      <c r="H106" s="214" t="s">
+        <v>219</v>
+      </c>
+      <c r="I106" s="104" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="114" t="s">
-        <v>191</v>
-      </c>
-      <c r="B107" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C107" s="189" t="n">
+      <c r="A107" s="140" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="C107" s="215" t="n">
         <v>45475</v>
       </c>
-      <c r="D107" s="114" t="s">
-        <v>148</v>
-      </c>
-      <c r="E107" s="190" t="n">
+      <c r="D107" s="140" t="s">
+        <v>164</v>
+      </c>
+      <c r="E107" s="216" t="n">
         <v>113</v>
       </c>
-      <c r="F107" s="114" t="s">
-        <v>137</v>
-      </c>
-      <c r="G107" s="187" t="n">
+      <c r="F107" s="140" t="s">
+        <v>153</v>
+      </c>
+      <c r="G107" s="213" t="n">
         <v>45672</v>
       </c>
-      <c r="H107" s="114" t="s">
-        <v>192</v>
-      </c>
-      <c r="I107" s="191" t="n">
+      <c r="H107" s="140" t="s">
+        <v>208</v>
+      </c>
+      <c r="I107" s="217" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="114"/>
-      <c r="B108" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="C108" s="189"/>
-      <c r="D108" s="114"/>
-      <c r="E108" s="190"/>
-      <c r="F108" s="114"/>
-      <c r="G108" s="187"/>
-      <c r="H108" s="114"/>
-      <c r="I108" s="191"/>
+      <c r="A108" s="140"/>
+      <c r="B108" s="100" t="s">
+        <v>220</v>
+      </c>
+      <c r="C108" s="215"/>
+      <c r="D108" s="140"/>
+      <c r="E108" s="216"/>
+      <c r="F108" s="140"/>
+      <c r="G108" s="213"/>
+      <c r="H108" s="140"/>
+      <c r="I108" s="217"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="114" t="s">
-        <v>191</v>
-      </c>
-      <c r="B109" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C109" s="189"/>
-      <c r="D109" s="114" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="190" t="n">
+      <c r="A109" s="140" t="s">
+        <v>207</v>
+      </c>
+      <c r="B109" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109" s="215"/>
+      <c r="D109" s="140" t="s">
+        <v>164</v>
+      </c>
+      <c r="E109" s="216" t="n">
         <v>113</v>
       </c>
-      <c r="F109" s="114" t="s">
-        <v>137</v>
-      </c>
-      <c r="G109" s="187" t="n">
+      <c r="F109" s="140" t="s">
+        <v>153</v>
+      </c>
+      <c r="G109" s="213" t="n">
         <v>45672</v>
       </c>
-      <c r="H109" s="192" t="s">
-        <v>193</v>
-      </c>
-      <c r="I109" s="191" t="n">
+      <c r="H109" s="218" t="s">
+        <v>209</v>
+      </c>
+      <c r="I109" s="217" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="193"/>
-      <c r="B113" s="184"/>
-      <c r="C113" s="185"/>
-      <c r="D113" s="193"/>
-      <c r="E113" s="184"/>
-      <c r="F113" s="186"/>
-      <c r="G113" s="186"/>
-      <c r="H113" s="186"/>
-      <c r="I113" s="186"/>
+      <c r="A113" s="219"/>
+      <c r="B113" s="210"/>
+      <c r="C113" s="211"/>
+      <c r="D113" s="219"/>
+      <c r="E113" s="210"/>
+      <c r="F113" s="212"/>
+      <c r="G113" s="212"/>
+      <c r="H113" s="212"/>
+      <c r="I113" s="212"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="B114" s="158" t="s">
-        <v>100</v>
-      </c>
-      <c r="C114" s="194" t="n">
+      <c r="A114" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="B114" s="184" t="s">
+        <v>114</v>
+      </c>
+      <c r="C114" s="220" t="n">
         <v>45438</v>
       </c>
-      <c r="D114" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="E114" s="73" t="n">
+      <c r="D114" s="99" t="s">
+        <v>164</v>
+      </c>
+      <c r="E114" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="195" t="s">
-        <v>206</v>
-      </c>
-      <c r="G114" s="77"/>
-      <c r="H114" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="I114" s="77"/>
+      <c r="F114" s="221" t="s">
+        <v>222</v>
+      </c>
+      <c r="G114" s="103"/>
+      <c r="H114" s="99" t="s">
+        <v>223</v>
+      </c>
+      <c r="I114" s="103"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="73"/>
-      <c r="B115" s="196" t="s">
-        <v>208</v>
-      </c>
-      <c r="C115" s="197" t="n">
+      <c r="A115" s="99"/>
+      <c r="B115" s="222" t="s">
+        <v>224</v>
+      </c>
+      <c r="C115" s="223" t="n">
         <v>45486</v>
       </c>
-      <c r="D115" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="E115" s="73"/>
-      <c r="F115" s="198" t="s">
-        <v>206</v>
-      </c>
-      <c r="G115" s="199" t="n">
+      <c r="D115" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="E115" s="99"/>
+      <c r="F115" s="224" t="s">
+        <v>222</v>
+      </c>
+      <c r="G115" s="225" t="n">
         <v>45588</v>
       </c>
-      <c r="H115" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="I115" s="77"/>
+      <c r="H115" s="99" t="s">
+        <v>226</v>
+      </c>
+      <c r="I115" s="103"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="73"/>
-      <c r="B116" s="196" t="s">
-        <v>211</v>
-      </c>
-      <c r="C116" s="197" t="n">
+      <c r="A116" s="99"/>
+      <c r="B116" s="222" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" s="223" t="n">
         <v>45590</v>
       </c>
-      <c r="D116" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="E116" s="73"/>
-      <c r="F116" s="198" t="s">
-        <v>206</v>
-      </c>
-      <c r="G116" s="199" t="n">
+      <c r="D116" s="99" t="s">
+        <v>157</v>
+      </c>
+      <c r="E116" s="99"/>
+      <c r="F116" s="224" t="s">
+        <v>222</v>
+      </c>
+      <c r="G116" s="225" t="n">
         <v>45688</v>
       </c>
-      <c r="H116" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="I116" s="77"/>
+      <c r="H116" s="99" t="s">
+        <v>228</v>
+      </c>
+      <c r="I116" s="103"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="73"/>
-      <c r="B117" s="200"/>
-      <c r="C117" s="201"/>
-      <c r="D117" s="200" t="s">
-        <v>213</v>
-      </c>
-      <c r="E117" s="200"/>
-      <c r="F117" s="202"/>
-      <c r="G117" s="203" t="n">
+      <c r="A117" s="99"/>
+      <c r="B117" s="226"/>
+      <c r="C117" s="227"/>
+      <c r="D117" s="226" t="s">
+        <v>229</v>
+      </c>
+      <c r="E117" s="226"/>
+      <c r="F117" s="228"/>
+      <c r="G117" s="229" t="n">
         <v>45782</v>
       </c>
-      <c r="H117" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="I117" s="77"/>
+      <c r="H117" s="99" t="s">
+        <v>230</v>
+      </c>
+      <c r="I117" s="103"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
-      <c r="B118" s="204"/>
-      <c r="C118" s="205"/>
+      <c r="B118" s="230"/>
+      <c r="C118" s="231"/>
       <c r="D118" s="3"/>
-      <c r="E118" s="204"/>
-      <c r="F118" s="206"/>
-      <c r="G118" s="207"/>
+      <c r="E118" s="230"/>
+      <c r="F118" s="232"/>
+      <c r="G118" s="233"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
-      <c r="B119" s="204"/>
-      <c r="C119" s="205"/>
+      <c r="B119" s="230"/>
+      <c r="C119" s="231"/>
       <c r="D119" s="3"/>
-      <c r="E119" s="204"/>
-      <c r="F119" s="206"/>
-      <c r="G119" s="207"/>
+      <c r="E119" s="230"/>
+      <c r="F119" s="232"/>
+      <c r="G119" s="233"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5577,13 +5951,13 @@
         <v>45967</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5591,13 +5965,13 @@
         <v>45927</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5605,21 +5979,21 @@
         <v>45708</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5629,28 +6003,28 @@
       <c r="D8" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="E8" s="208" t="n">
+      <c r="E8" s="234" t="n">
         <v>0.416666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="3" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E15" s="208" t="n">
+      <c r="E15" s="234" t="n">
         <v>0.427083333333333</v>
       </c>
     </row>
@@ -5693,7 +6067,7 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5701,10 +6075,10 @@
         <v>45725</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB088CD7-2B92-4515-B5C0-ED52EE65F8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ABDEAE-40D9-45EF-BB97-A35EEC4117B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>2026/3201</t>
-  </si>
-  <si>
-    <t>yok</t>
   </si>
   <si>
     <t>Örnek 13 – icra – itiraz edilmedi</t>
@@ -831,6 +828,9 @@
       <t>-icra</t>
     </r>
   </si>
+  <si>
+    <t>imza toplanacak - adli tıptan rapor talebi -samsun</t>
+  </si>
 </sst>
 </file>
 
@@ -842,7 +842,7 @@
     <numFmt numFmtId="166" formatCode="dd/mmm"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -880,14 +880,6 @@
       <color rgb="FFC9211E"/>
       <name val="Calibri"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC9211E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
     </font>
     <font>
       <b/>
@@ -1380,9 +1372,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -1436,13 +1428,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1455,9 +1441,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1465,31 +1448,19 @@
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1530,17 +1501,17 @@
     <xf numFmtId="164" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1567,7 +1538,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="166" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -1600,18 +1571,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1633,9 +1604,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="12" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="11" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -1659,17 +1630,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="20" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="2" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1690,66 +1661,62 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="20" fontId="11" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="18" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="17" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="22" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="24" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="24" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1759,16 +1726,13 @@
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2211,22 +2175,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="25">
         <v>45725</v>
       </c>
@@ -2234,58 +2197,51 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="34"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-    </row>
-    <row r="5" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+    </row>
+    <row r="5" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29"/>
-      <c r="B5" s="234"/>
-      <c r="C5" s="224" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-    </row>
-    <row r="6" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="225"/>
+      <c r="C5" s="217" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+    </row>
+    <row r="6" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="34"/>
       <c r="C6" s="36"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+    </row>
+    <row r="7" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="34"/>
       <c r="C7" s="36"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>45959</v>
       </c>
@@ -2295,146 +2251,133 @@
       <c r="C9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="26">
-        <v>46009</v>
-      </c>
-      <c r="E9" s="27">
+      <c r="D9" s="27">
         <v>196170</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="21"/>
       <c r="C10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>46009</v>
+      </c>
       <c r="B11" s="3"/>
       <c r="C11" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="29"/>
       <c r="B12" s="30"/>
       <c r="C12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45475</v>
       </c>
-      <c r="B16" s="238" t="s">
+      <c r="B16" s="228" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="228"/>
+      <c r="C17" s="218" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="27"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="26">
         <v>45482</v>
       </c>
-      <c r="E16" s="27">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="238"/>
-      <c r="C17" s="225" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="227"/>
-      <c r="B18" s="237"/>
-      <c r="C18" s="235" t="s">
+      <c r="B18" s="227"/>
+      <c r="C18" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="236"/>
-      <c r="E18" s="229"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D18" s="220"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>45604</v>
       </c>
-      <c r="B19" s="238" t="s">
+      <c r="B19" s="228" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="26">
-        <v>45615</v>
-      </c>
-      <c r="E19" s="27">
+      <c r="D19" s="27">
         <v>140835</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="238"/>
+      <c r="B20" s="228"/>
       <c r="C20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="227"/>
-      <c r="B21" s="237"/>
-      <c r="C21" s="235" t="s">
+      <c r="D20" s="27"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="26">
+        <v>45615</v>
+      </c>
+      <c r="B21" s="227"/>
+      <c r="C21" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="228"/>
-      <c r="E21" s="229"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D21" s="220"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45704</v>
       </c>
-      <c r="B22" s="239" t="s">
+      <c r="B22" s="229" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="C23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45989</v>
       </c>
@@ -2442,10 +2385,9 @@
       <c r="C24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>46042</v>
       </c>
@@ -2453,932 +2395,861 @@
       <c r="C25" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="18">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33">
         <v>46155</v>
       </c>
-      <c r="B26" s="23">
-        <v>0.37777777777777799</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="34"/>
+      <c r="C26" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="50"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>46288</v>
+      </c>
+      <c r="B27" s="23">
+        <v>0.37638888888888888</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="D27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="D28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
         <v>45603</v>
       </c>
-      <c r="B28" s="240" t="s">
+      <c r="B29" s="230" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D29" s="27"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="228"/>
+      <c r="C30" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="27"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="26">
         <v>45615</v>
       </c>
-      <c r="E28" s="27"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="238"/>
-      <c r="C29" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="27"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="237"/>
-      <c r="C30" s="28" t="s">
+      <c r="B31" s="227"/>
+      <c r="C31" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5">
+      <c r="D31" s="5">
         <v>156000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>45704</v>
       </c>
-      <c r="B31" s="239" t="s">
+      <c r="B32" s="229" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="3"/>
-      <c r="C32" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D32" s="4">
         <v>86000</v>
       </c>
-      <c r="E32" s="37" t="s">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="3"/>
+      <c r="C33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>46086</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="3"/>
-      <c r="C34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
       <c r="C35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="3"/>
+      <c r="C36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
         <v>46196</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>0.41319444444444398</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C37" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="D37" s="5"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="3"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
         <v>45588</v>
       </c>
-      <c r="B38" s="238" t="s">
+      <c r="B39" s="228" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D39" s="27"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="26">
         <v>45596</v>
       </c>
-      <c r="E38" s="27"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="237"/>
-      <c r="C39" s="28" t="s">
+      <c r="B40" s="227"/>
+      <c r="C40" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>45704</v>
       </c>
-      <c r="B40" s="239" t="s">
+      <c r="B41" s="229" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>46021</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="C42" s="31"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>46036</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="33">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="33">
         <v>46155</v>
       </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="35" t="s">
+      <c r="B44" s="34"/>
+      <c r="C44" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="18">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="33">
         <v>46155</v>
       </c>
-      <c r="B44" s="23">
-        <v>0.37708333333333299</v>
-      </c>
-      <c r="C44" s="20" t="s">
+      <c r="B45" s="34"/>
+      <c r="C45" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" s="50"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>46288</v>
+      </c>
+      <c r="B46" s="23">
+        <v>0.375</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="3"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="D46" s="5"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="3"/>
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
         <v>45475</v>
       </c>
-      <c r="B46" s="238" t="s">
+      <c r="B48" s="228" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D48" s="27">
+        <v>158437</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="26">
         <v>45482</v>
       </c>
-      <c r="E46" s="27">
-        <v>158437</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-      <c r="B47" s="238"/>
-      <c r="C47" s="225" t="s">
+      <c r="B49" s="228"/>
+      <c r="C49" s="218" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="27"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="237"/>
-      <c r="C48" s="28" t="s">
+      <c r="D49" s="27"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="227"/>
+      <c r="C50" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>46069</v>
       </c>
-      <c r="B49" s="239" t="s">
+      <c r="B51" s="229" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="3"/>
-      <c r="C50" s="13" t="s">
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+      <c r="C52" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>46077</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="2" t="s">
+      <c r="B53" s="3"/>
+      <c r="C53" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="38">
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="38">
         <v>46175</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B54" s="23">
         <v>0.41319444444444398</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C54" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E52" s="4"/>
-      <c r="G52" s="4"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="3"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="3"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B55" s="3"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B56" s="3"/>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="3"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
         <v>45342</v>
       </c>
-      <c r="B56" s="240" t="s">
+      <c r="B58" s="230" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D56" s="9" t="s">
+      <c r="C58" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="27"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="237"/>
-      <c r="C57" s="13" t="s">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="227"/>
+      <c r="C59" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="39">
+      <c r="D59" s="5"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="39">
         <v>45450</v>
       </c>
-      <c r="B58" s="241" t="s">
+      <c r="B60" s="231" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="C60" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>45680</v>
       </c>
-      <c r="B59" s="237"/>
-      <c r="C59" s="13" t="s">
+      <c r="B61" s="227"/>
+      <c r="C61" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="233" t="s">
+      <c r="D61" s="224" t="s">
         <v>74</v>
       </c>
-      <c r="E59" s="5"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>45726</v>
       </c>
-      <c r="B60" s="242"/>
-      <c r="C60" s="2" t="s">
+      <c r="B62" s="232"/>
+      <c r="C62" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="226">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="219">
         <v>45765</v>
       </c>
-      <c r="B61" s="243" t="s">
+      <c r="B63" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="C61" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="G61" s="5"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="230"/>
-      <c r="B62" s="231"/>
-      <c r="C62" s="232" t="s">
+      <c r="C63" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="F63" s="5"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="221"/>
+      <c r="B64" s="222"/>
+      <c r="C64" s="223" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="228"/>
-      <c r="E62" s="229"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="3"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="3"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="5"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="220"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B65" s="3"/>
       <c r="C65" s="13"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="5"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B66" s="3"/>
       <c r="C66" s="13"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="40">
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="3"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="3"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="40">
         <v>46076</v>
       </c>
-      <c r="B67" s="41" t="s">
+      <c r="B69" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="41" t="s">
+      <c r="C69" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D67" s="43" t="s">
+      <c r="D69" s="20">
+        <v>515608</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="40"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="20">
-        <v>515608</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="40"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D68" s="42">
+      <c r="D70" s="42">
         <v>46088</v>
       </c>
-      <c r="E68" s="44"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="40">
-        <v>46120</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="44"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="44"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="40">
         <v>46120</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="44"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D71" s="43"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="40">
         <v>46121</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="43"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="40">
+        <v>46120</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="44"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="40">
+      <c r="D73" s="43"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="40">
         <v>46121</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="44"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B74" s="3"/>
+      <c r="B74" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="C74" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="44"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="40"/>
+        <v>83</v>
+      </c>
+      <c r="D74" s="43"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="40">
+        <v>46121</v>
+      </c>
       <c r="B75" s="3"/>
       <c r="C75" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="44"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="40"/>
+        <v>85</v>
+      </c>
+      <c r="D75" s="43"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="40">
+        <v>46122</v>
+      </c>
       <c r="B76" s="3"/>
       <c r="C76" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="44"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="D76" s="43"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="40"/>
       <c r="B77" s="3"/>
       <c r="C77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="43"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="40"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D78" s="43"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="40"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="43"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="40"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="44"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="40"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="31" t="s">
+      <c r="D80" s="43"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="40">
+        <v>46122</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="44"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="40">
+      <c r="D81" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="40">
         <v>46122</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="C82" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E79" s="44"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="D82" s="48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="40">
+        <v>46127</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E80" s="44"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="40">
-        <v>46127</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="28" t="s">
+      <c r="D83" s="44">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="40"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="50" t="s">
+      <c r="D84" s="43"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="40"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" s="43"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="43"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" s="43"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B87" s="3"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="5"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="40">
+        <v>45676</v>
+      </c>
+      <c r="B88" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D88" s="47"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="46">
+        <v>45698</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="47"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="40"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D90" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="33"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="50"/>
+    </row>
+    <row r="92" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="40">
+        <v>46205</v>
+      </c>
+      <c r="B92" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D92" s="47"/>
+    </row>
+    <row r="93" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="46">
+        <v>45482</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="47"/>
+    </row>
+    <row r="94" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="40">
+        <v>45672</v>
+      </c>
+      <c r="B94" s="45"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B95" s="3"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="5"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="52">
+        <v>45588</v>
+      </c>
+      <c r="B96" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D96" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="52"/>
+      <c r="B97" s="53"/>
+      <c r="C97" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" s="55"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="56">
+        <v>45438</v>
+      </c>
+      <c r="B98" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D98" s="48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="56"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="D99" s="47">
+        <v>193500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="56">
+        <v>45288</v>
+      </c>
+      <c r="B100" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="E81" s="46">
-        <v>375000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="40"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D82" s="45"/>
-      <c r="E82" s="44"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="40"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D83" s="4"/>
-      <c r="E83" s="44"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="44"/>
-      <c r="B84" s="44"/>
-      <c r="C84" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D84" s="44"/>
-      <c r="E84" s="44"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B85" s="3"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="5"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="40">
-        <v>45676</v>
-      </c>
-      <c r="B86" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C86" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" s="48">
-        <v>45698</v>
-      </c>
-      <c r="E86" s="49"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="40"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D87" s="4"/>
-      <c r="E87" s="49"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="40"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D88" s="50"/>
-      <c r="E88" s="49" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="33"/>
-      <c r="B89" s="34"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="52"/>
-      <c r="E89" s="53"/>
-    </row>
-    <row r="90" spans="1:5" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="40">
-        <v>46205</v>
-      </c>
-      <c r="B90" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="C90" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="D90" s="48">
-        <v>45482</v>
-      </c>
-      <c r="E90" s="49"/>
-    </row>
-    <row r="91" spans="1:5" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="40"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D91" s="4"/>
-      <c r="E91" s="49"/>
-    </row>
-    <row r="92" spans="1:5" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="40">
-        <v>45672</v>
-      </c>
-      <c r="B92" s="47"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="50"/>
-      <c r="E92" s="49" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="3"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="55">
-        <v>45588</v>
-      </c>
-      <c r="B94" s="56" t="s">
+      <c r="C100" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="56"/>
+      <c r="B101" s="60"/>
+      <c r="C101" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="C94" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="D94" s="58"/>
-      <c r="E94" s="49" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="55"/>
-      <c r="B95" s="56"/>
-      <c r="C95" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D95" s="58"/>
-      <c r="E95" s="59"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="60">
-        <v>45438</v>
-      </c>
-      <c r="B96" s="61" t="s">
+      <c r="D101" s="59"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="56">
+        <v>45148</v>
+      </c>
+      <c r="B102" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C102" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="D102" s="62" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="56"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="61"/>
+      <c r="D103" s="59"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="56">
+        <v>44928</v>
+      </c>
+      <c r="B104" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="C96" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96" s="63"/>
-      <c r="E96" s="64"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="60"/>
-      <c r="B97" s="61"/>
-      <c r="C97" s="62" t="s">
+      <c r="D104" s="47">
+        <v>24316</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="56"/>
+      <c r="B105" s="60"/>
+      <c r="C105" s="61"/>
+      <c r="D105" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="D97" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="E97" s="49">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="60">
-        <v>45288</v>
-      </c>
-      <c r="B98" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="C98" s="66" t="s">
-        <v>113</v>
-      </c>
-      <c r="D98" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="E98" s="64"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="60"/>
-      <c r="B99" s="65"/>
-      <c r="C99" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" s="63"/>
-      <c r="E99" s="64"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="60">
-        <v>45148</v>
-      </c>
-      <c r="B100" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="C100" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="68" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="60"/>
-      <c r="B101" s="65"/>
-      <c r="C101" s="66"/>
-      <c r="D101" s="63"/>
-      <c r="E101" s="64"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="60">
-        <v>44928</v>
-      </c>
-      <c r="B102" s="65" t="s">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="56">
+        <v>44333</v>
+      </c>
+      <c r="B106" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="C102" s="66" t="s">
-        <v>109</v>
-      </c>
-      <c r="D102" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="E102" s="49">
-        <v>24316</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="60"/>
-      <c r="B103" s="65"/>
-      <c r="C103" s="66"/>
-      <c r="D103" s="63"/>
-      <c r="E103" s="64"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="60">
-        <v>44333</v>
-      </c>
-      <c r="B104" s="65" t="s">
+      <c r="C106" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="C104" s="66" t="s">
-        <v>119</v>
-      </c>
-      <c r="D104" s="50"/>
-      <c r="E104" s="49"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="60"/>
-      <c r="B105" s="65"/>
-      <c r="C105" s="66"/>
-      <c r="D105" s="63"/>
-      <c r="E105" s="64"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B106" s="3"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="5"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-      <c r="C107"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-      <c r="C108"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D106" s="47"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="56"/>
+      <c r="B107" s="60"/>
+      <c r="C107" s="61"/>
+      <c r="D107" s="59"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B108" s="3"/>
+      <c r="D108" s="5"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="B109"/>
       <c r="C109"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B110" s="3"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="5"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B111" s="3"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="5"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B112" s="3"/>
-      <c r="D112" s="69"/>
-      <c r="E112" s="5"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D112" s="5"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B113" s="3"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="5"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D117" s="11"/>
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D118" s="11"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D121" s="11"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D123" s="11"/>
-      <c r="E123" s="2"/>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B136" s="2"/>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B137" s="2"/>
+      <c r="D113" s="5"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B114" s="3"/>
+      <c r="D114" s="5"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="3"/>
+      <c r="D115" s="5"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="2"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D119" s="2"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D125" s="2"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B138" s="2"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B139" s="2"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -3420,10 +3291,10 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -3437,7 +3308,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="13"/>
     </row>
@@ -3537,10 +3408,10 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
@@ -3551,7 +3422,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C11" s="13"/>
     </row>
@@ -3610,7 +3481,7 @@
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="70" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="63" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="7" style="2" customWidth="1"/>
     <col min="6" max="6" width="4" style="2" customWidth="1"/>
@@ -3620,105 +3491,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="64"/>
+      <c r="B2" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="71"/>
-      <c r="B2" s="75" t="s">
+      <c r="C2" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="64"/>
+      <c r="B4" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="76" t="s">
+      <c r="C4" s="66"/>
+      <c r="D4" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="75" t="s">
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="75" t="s">
+      <c r="H4" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="75" t="s">
+      <c r="I4" s="65"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="64"/>
+      <c r="B5" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="I4" s="72"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="76" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="72" t="s">
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="77" t="s">
+      <c r="H5" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="65"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="64"/>
+      <c r="B7" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="75" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="72"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
-      <c r="B7" s="78" t="s">
+      <c r="C7" s="63">
+        <v>45827</v>
+      </c>
+      <c r="D7" s="66" t="s">
         <v>133</v>
-      </c>
-      <c r="C7" s="70">
-        <v>45827</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>134</v>
       </c>
       <c r="E7" s="2">
         <v>9</v>
@@ -3726,77 +3597,77 @@
       <c r="F7" s="2">
         <v>40</v>
       </c>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7" s="65"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="64"/>
+      <c r="B9" s="72" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="63">
+        <v>45939</v>
+      </c>
+      <c r="D9" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="I7" s="72"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
-      <c r="B9" s="79" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="70">
+      <c r="E9" s="73">
+        <v>9</v>
+      </c>
+      <c r="F9" s="73">
+        <v>30</v>
+      </c>
+      <c r="H9" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="65"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="64"/>
+      <c r="B10" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="66">
         <v>45939</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D10" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="65">
+        <v>9</v>
+      </c>
+      <c r="F10" s="65">
+        <v>40</v>
+      </c>
+      <c r="G10" s="67"/>
+      <c r="H10" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="E9" s="80">
-        <v>9</v>
-      </c>
-      <c r="F9" s="80">
-        <v>30</v>
-      </c>
-      <c r="H9" s="72" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="72"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="79" t="s">
+      <c r="I10" s="65"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="64"/>
+      <c r="B11" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="66">
+        <v>45952</v>
+      </c>
+      <c r="D11" s="65" t="s">
         <v>138</v>
-      </c>
-      <c r="C10" s="73">
-        <v>45939</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="72">
-        <v>9</v>
-      </c>
-      <c r="F10" s="72">
-        <v>40</v>
-      </c>
-      <c r="G10" s="74"/>
-      <c r="H10" s="72" t="s">
-        <v>137</v>
-      </c>
-      <c r="I10" s="72"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="73">
-        <v>45952</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>139</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -3804,227 +3675,227 @@
       <c r="F11" s="2">
         <v>36</v>
       </c>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72" t="s">
+      <c r="G11" s="65"/>
+      <c r="H11" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="67"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="64"/>
+      <c r="B12" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="66">
+        <v>45952</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="65">
+        <v>9</v>
+      </c>
+      <c r="F12" s="65">
+        <v>35</v>
+      </c>
+      <c r="G12" s="67"/>
+      <c r="H12" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="67"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="64"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="67"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="64"/>
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="64"/>
+      <c r="I15" s="65"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="74"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="75"/>
+      <c r="B17" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="I11" s="74"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="79" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="73">
-        <v>45952</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="72">
-        <v>9</v>
-      </c>
-      <c r="F12" s="72">
-        <v>35</v>
-      </c>
-      <c r="G12" s="74"/>
-      <c r="H12" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="I12" s="74"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="74"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="71"/>
-      <c r="I14" s="72"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
-      <c r="I15" s="72"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
-      <c r="J16" s="13"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="82"/>
-      <c r="B17" s="83" t="s">
+      <c r="C17" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="84" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="85"/>
-      <c r="G17" s="86" t="s">
+      <c r="H17" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="I17" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="I17" s="83" t="s">
+      <c r="J17" s="80"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="83">
+        <v>45342</v>
+      </c>
+      <c r="D18" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="J17" s="87"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="90">
-        <v>45342</v>
-      </c>
-      <c r="D18" s="88" t="s">
+      <c r="E18" s="84"/>
+      <c r="F18" s="85" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="91"/>
-      <c r="F18" s="92" t="s">
+      <c r="G18" s="86"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="80"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="81"/>
+      <c r="B19" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="93"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="87"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="94" t="s">
+      <c r="C19" s="83">
+        <v>45537</v>
+      </c>
+      <c r="D19" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="90">
-        <v>45537</v>
-      </c>
-      <c r="D19" s="88" t="s">
+      <c r="E19" s="84"/>
+      <c r="F19" s="88" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="91"/>
-      <c r="F19" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="G19" s="93">
+      <c r="G19" s="86">
         <v>45691</v>
       </c>
-      <c r="H19" s="91"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="87"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
-      <c r="B20" s="96"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="98" t="s">
-        <v>151</v>
+      <c r="B20" s="89"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="91" t="s">
+        <v>150</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="87"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="C21" s="99">
+      <c r="C21" s="92">
         <v>45726</v>
       </c>
-      <c r="D21" s="100" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" s="100"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="87"/>
+      <c r="D21" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="93"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="87"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="81"/>
-      <c r="J23" s="87"/>
+      <c r="A23" s="74"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="107"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="81"/>
+      <c r="A25" s="74"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="81"/>
+      <c r="A26" s="74"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="110"/>
-      <c r="B27" s="111" t="s">
+      <c r="A27" s="103"/>
+      <c r="B27" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="105" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="D27" s="104"/>
+      <c r="E27" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="106"/>
+      <c r="G27" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="111"/>
-      <c r="E27" s="113" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="113"/>
-      <c r="G27" s="114" t="s">
+      <c r="H27" s="104" t="s">
         <v>143</v>
       </c>
-      <c r="H27" s="111" t="s">
+      <c r="I27" s="104" t="s">
         <v>144</v>
       </c>
-      <c r="I27" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="J27" s="115"/>
+      <c r="J27" s="108"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="81" t="s">
+      <c r="A28" s="74" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="H28" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="116" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28" s="117">
+      <c r="I28" s="110">
         <v>45712</v>
       </c>
-      <c r="J28" s="115"/>
+      <c r="J28" s="108"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="81"/>
-      <c r="J29" s="115"/>
+      <c r="A29" s="74"/>
+      <c r="J29" s="108"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -4033,420 +3904,420 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="118" t="s">
+      <c r="I30" s="111" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="108"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="112"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="114"/>
+      <c r="J31" s="108"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="74"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="74"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="115"/>
+      <c r="B34" s="116" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="117" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="116"/>
+      <c r="E34" s="118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="118"/>
+      <c r="G34" s="119" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="116" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" s="80"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="J30" s="115"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="119"/>
-      <c r="B31" s="115"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="121"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="121"/>
-      <c r="J31" s="115"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="81"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="81"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="122"/>
-      <c r="B34" s="123" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="124" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="123"/>
-      <c r="E34" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="125"/>
-      <c r="G34" s="126" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="123" t="s">
-        <v>144</v>
-      </c>
-      <c r="I34" s="123" t="s">
-        <v>145</v>
-      </c>
-      <c r="J34" s="87"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="119" t="s">
+      <c r="B35" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="101">
+        <v>45475</v>
+      </c>
+      <c r="D35" s="109" t="s">
         <v>157</v>
       </c>
-      <c r="B35" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="108">
-        <v>45475</v>
-      </c>
-      <c r="D35" s="116" t="s">
+      <c r="E35" s="120">
+        <v>97</v>
+      </c>
+      <c r="F35" s="109" t="s">
+        <v>146</v>
+      </c>
+      <c r="H35" s="109" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="127">
-        <v>97</v>
-      </c>
-      <c r="F35" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="H35" s="116" t="s">
+      <c r="I35" s="102">
+        <v>45705</v>
+      </c>
+      <c r="J35" s="80"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="109"/>
+      <c r="B36" s="121" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="101">
+        <v>45604</v>
+      </c>
+      <c r="D36" s="109" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="120">
+        <v>178</v>
+      </c>
+      <c r="F36" s="109" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="122" t="s">
         <v>159</v>
       </c>
-      <c r="I35" s="109">
+      <c r="I36" s="123">
         <v>45705</v>
       </c>
-      <c r="J35" s="87"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="116"/>
-      <c r="B36" s="128" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="108">
-        <v>45604</v>
-      </c>
-      <c r="D36" s="116" t="s">
-        <v>158</v>
-      </c>
-      <c r="E36" s="127">
-        <v>178</v>
-      </c>
-      <c r="F36" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="H36" s="129" t="s">
-        <v>160</v>
-      </c>
-      <c r="I36" s="130">
-        <v>45705</v>
-      </c>
-      <c r="J36" s="87"/>
+      <c r="J36" s="80"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
-      <c r="B37" s="131" t="s">
+      <c r="B37" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="70">
+      <c r="C37" s="63">
         <v>45704</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="J37" s="87"/>
+        <v>160</v>
+      </c>
+      <c r="J37" s="80"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="70">
+        <v>82</v>
+      </c>
+      <c r="C38" s="63">
         <v>45705</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="J38" s="87"/>
+      <c r="J38" s="80"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="C39" s="132"/>
+      <c r="C39" s="125"/>
       <c r="D39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="J39" s="87"/>
+      <c r="J39" s="80"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="C40" s="132" t="s">
+      <c r="C40" s="125" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="22" t="s">
-        <v>164</v>
-      </c>
       <c r="H40" s="3"/>
-      <c r="J40" s="87"/>
+      <c r="J40" s="80"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
-      <c r="C41" s="133">
+      <c r="C41" s="126">
         <v>45717</v>
       </c>
-      <c r="D41" s="134" t="s">
+      <c r="D41" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="135" t="s">
+      <c r="E41" s="128" t="s">
+        <v>164</v>
+      </c>
+      <c r="F41" s="127"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="F41" s="134"/>
-      <c r="G41" s="136"/>
-      <c r="H41" s="134" t="s">
+      <c r="I41" s="130" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="137" t="s">
-        <v>167</v>
-      </c>
-      <c r="J41" s="87"/>
+      <c r="J41" s="80"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
-      <c r="C42" s="138"/>
+      <c r="C42" s="131"/>
       <c r="D42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="J42" s="80"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="132"/>
+      <c r="B43" s="133" t="s">
         <v>169</v>
       </c>
-      <c r="J42" s="87"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="139"/>
-      <c r="B43" s="140" t="s">
+      <c r="C43" s="134">
+        <v>45805</v>
+      </c>
+      <c r="D43" s="135">
+        <v>0.40972222222222199</v>
+      </c>
+      <c r="E43" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="C43" s="141">
+      <c r="F43" s="132"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="137"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="109"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="138">
         <v>45805</v>
       </c>
-      <c r="D43" s="142">
-        <v>0.40972222222222199</v>
-      </c>
-      <c r="E43" s="139" t="s">
+      <c r="D44" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="F43" s="139"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="143"/>
-      <c r="J43" s="144"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="116"/>
-      <c r="B44" s="87"/>
-      <c r="C44" s="145">
-        <v>45805</v>
-      </c>
-      <c r="D44" s="127" t="s">
-        <v>172</v>
-      </c>
-      <c r="E44" s="127"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="146"/>
-      <c r="H44" s="87"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="87"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="80"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
-      <c r="C46" s="132"/>
+      <c r="C46" s="125"/>
       <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="122"/>
-      <c r="B47" s="123" t="s">
+      <c r="A47" s="115"/>
+      <c r="B47" s="116" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="124" t="s">
+      <c r="D47" s="116"/>
+      <c r="E47" s="118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="118"/>
+      <c r="G47" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="D47" s="123"/>
-      <c r="E47" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="125"/>
-      <c r="G47" s="126" t="s">
+      <c r="H47" s="116" t="s">
         <v>143</v>
       </c>
-      <c r="H47" s="123" t="s">
+      <c r="I47" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="I47" s="123" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="87"/>
+      <c r="J47" s="80"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="116" t="s">
-        <v>157</v>
-      </c>
-      <c r="B48" s="89" t="s">
+      <c r="A48" s="109" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="147">
+      <c r="C48" s="140">
         <v>45588</v>
       </c>
-      <c r="D48" s="127" t="s">
+      <c r="D48" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" s="80"/>
+      <c r="F48" s="109" t="s">
+        <v>146</v>
+      </c>
+      <c r="H48" s="109" t="s">
         <v>173</v>
       </c>
-      <c r="E48" s="87"/>
-      <c r="F48" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="H48" s="116" t="s">
+      <c r="I48" s="102">
+        <v>45630</v>
+      </c>
+      <c r="J48" s="80"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="109"/>
+      <c r="B49" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="101"/>
+      <c r="D49" s="109"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="109"/>
+      <c r="H49" s="122" t="s">
         <v>174</v>
       </c>
-      <c r="I48" s="109">
+      <c r="I49" s="102">
         <v>45630</v>
       </c>
-      <c r="J48" s="87"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="116"/>
-      <c r="B49" s="89" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="108"/>
-      <c r="D49" s="116"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="116"/>
-      <c r="H49" s="129" t="s">
+      <c r="J49" s="80"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="109"/>
+      <c r="B50" s="124" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="141">
+        <v>45704</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>175</v>
-      </c>
-      <c r="I49" s="109">
-        <v>45630</v>
-      </c>
-      <c r="J49" s="87"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="116"/>
-      <c r="B50" s="131" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="148">
-        <v>45704</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>176</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="J50" s="87"/>
+      <c r="J50" s="80"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="70">
+        <v>82</v>
+      </c>
+      <c r="C51" s="63">
         <v>45709</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="J51" s="87"/>
+      <c r="J51" s="80"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
-      <c r="C52" s="132" t="s">
-        <v>163</v>
+      <c r="C52" s="125" t="s">
+        <v>162</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="J52" s="87"/>
+      <c r="J52" s="80"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="C53" s="132">
+      <c r="C53" s="125">
         <v>45712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="J53" s="87"/>
+      <c r="J53" s="80"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
-      <c r="C54" s="149">
+      <c r="C54" s="142">
         <v>45717</v>
       </c>
-      <c r="D54" s="150" t="s">
+      <c r="D54" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="151" t="s">
+      <c r="E54" s="144" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" s="143"/>
+      <c r="G54" s="145"/>
+      <c r="H54" s="143" t="s">
         <v>165</v>
       </c>
-      <c r="F54" s="150"/>
-      <c r="G54" s="152"/>
-      <c r="H54" s="150" t="s">
-        <v>166</v>
-      </c>
-      <c r="I54" s="153"/>
-      <c r="J54" s="87"/>
+      <c r="I54" s="146"/>
+      <c r="J54" s="80"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="154"/>
-      <c r="H55" s="155"/>
-      <c r="I55" s="154"/>
-      <c r="J55" s="87"/>
+      <c r="G55" s="147"/>
+      <c r="H55" s="148"/>
+      <c r="I55" s="147"/>
+      <c r="J55" s="80"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F56" s="1"/>
-      <c r="G56" s="154"/>
-      <c r="H56" s="155"/>
-      <c r="I56" s="156" t="s">
-        <v>167</v>
-      </c>
-      <c r="J56" s="87"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="148"/>
+      <c r="I56" s="149" t="s">
+        <v>166</v>
+      </c>
+      <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
-      <c r="B57" s="157" t="s">
-        <v>170</v>
-      </c>
-      <c r="C57" s="158">
+      <c r="B57" s="150" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="151">
         <v>45805</v>
       </c>
-      <c r="D57" s="159">
+      <c r="D57" s="152">
         <v>0</v>
       </c>
-      <c r="J57" s="87"/>
+      <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="116"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="160">
+      <c r="A58" s="109"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="153">
         <v>45805</v>
       </c>
-      <c r="D58" s="116" t="s">
-        <v>180</v>
-      </c>
-      <c r="E58" s="87"/>
-      <c r="F58" s="87"/>
-      <c r="G58" s="109"/>
-      <c r="H58" s="87"/>
-      <c r="I58" s="109"/>
-      <c r="J58" s="87"/>
+      <c r="D58" s="109" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="102"/>
+      <c r="H58" s="80"/>
+      <c r="I58" s="102"/>
+      <c r="J58" s="80"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="13"/>
-      <c r="C59" s="132"/>
+      <c r="C59" s="125"/>
       <c r="D59" s="3"/>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
@@ -4456,7 +4327,7 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="13"/>
-      <c r="C60" s="132"/>
+      <c r="C60" s="125"/>
       <c r="D60" s="3"/>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
@@ -4471,307 +4342,307 @@
       <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="161"/>
-      <c r="B62" s="162" t="s">
+      <c r="A62" s="154"/>
+      <c r="B62" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="156" t="s">
         <v>141</v>
       </c>
-      <c r="C62" s="163" t="s">
+      <c r="D62" s="155"/>
+      <c r="E62" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="157"/>
+      <c r="G62" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="D62" s="162"/>
-      <c r="E62" s="164" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="164"/>
-      <c r="G62" s="165" t="s">
+      <c r="H62" s="155" t="s">
         <v>143</v>
       </c>
-      <c r="H62" s="162" t="s">
+      <c r="I62" s="155" t="s">
         <v>144</v>
       </c>
-      <c r="I62" s="162" t="s">
-        <v>145</v>
-      </c>
-      <c r="J62" s="166"/>
+      <c r="J62" s="159"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="119" t="s">
+      <c r="A63" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="101">
+        <v>45475</v>
+      </c>
+      <c r="D63" s="109" t="s">
+        <v>157</v>
+      </c>
+      <c r="E63" s="120">
+        <v>214</v>
+      </c>
+      <c r="F63" s="109" t="s">
+        <v>146</v>
+      </c>
+      <c r="H63" s="109" t="s">
         <v>181</v>
       </c>
-      <c r="B63" s="89" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" s="108">
-        <v>45475</v>
-      </c>
-      <c r="D63" s="116" t="s">
-        <v>158</v>
-      </c>
-      <c r="E63" s="127">
-        <v>214</v>
-      </c>
-      <c r="F63" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="H63" s="116" t="s">
+      <c r="I63" s="102">
+        <v>45702</v>
+      </c>
+      <c r="J63" s="159"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="112"/>
+      <c r="B64" s="80"/>
+      <c r="C64" s="101"/>
+      <c r="D64" s="160">
+        <v>158437</v>
+      </c>
+      <c r="E64" s="80"/>
+      <c r="F64" s="109"/>
+      <c r="H64" s="122" t="s">
         <v>182</v>
       </c>
-      <c r="I63" s="109">
+      <c r="I64" s="102">
         <v>45702</v>
       </c>
-      <c r="J63" s="166"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="119"/>
-      <c r="B64" s="87"/>
-      <c r="C64" s="108"/>
-      <c r="D64" s="167">
-        <v>158437</v>
-      </c>
-      <c r="E64" s="87"/>
-      <c r="F64" s="116"/>
-      <c r="H64" s="129" t="s">
-        <v>183</v>
-      </c>
-      <c r="I64" s="109">
-        <v>45702</v>
-      </c>
-      <c r="J64" s="166"/>
+      <c r="J64" s="159"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="131" t="s">
+      <c r="B65" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="70">
+      <c r="C65" s="63">
         <v>45704</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="J65" s="166"/>
+      <c r="J65" s="159"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C66" s="70">
+        <v>82</v>
+      </c>
+      <c r="C66" s="63">
         <v>45705</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="J66" s="166"/>
+      <c r="J66" s="159"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="J67" s="166"/>
+      <c r="J67" s="159"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="C68" s="132" t="s">
-        <v>163</v>
+      <c r="C68" s="125" t="s">
+        <v>162</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="J68" s="166"/>
+      <c r="J68" s="159"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="C69" s="168">
+      <c r="C69" s="161">
         <v>45711</v>
       </c>
-      <c r="D69" s="169" t="s">
-        <v>188</v>
-      </c>
-      <c r="E69" s="169"/>
-      <c r="F69" s="169"/>
-      <c r="G69" s="170"/>
-      <c r="H69" s="169"/>
-      <c r="I69" s="171"/>
-      <c r="J69" s="166"/>
+      <c r="D69" s="162" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="162"/>
+      <c r="F69" s="162"/>
+      <c r="G69" s="163"/>
+      <c r="H69" s="162"/>
+      <c r="I69" s="164"/>
+      <c r="J69" s="159"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B70" s="13"/>
-      <c r="C70" s="138" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="155"/>
-      <c r="E70" s="155"/>
-      <c r="F70" s="155"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="155"/>
-      <c r="I70" s="154"/>
-      <c r="J70" s="166"/>
+      <c r="C70" s="131" t="s">
+        <v>188</v>
+      </c>
+      <c r="D70" s="148"/>
+      <c r="E70" s="148"/>
+      <c r="F70" s="148"/>
+      <c r="G70" s="147"/>
+      <c r="H70" s="148"/>
+      <c r="I70" s="147"/>
+      <c r="J70" s="159"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>1</v>
       </c>
       <c r="B71" s="13"/>
-      <c r="C71" s="138" t="s">
+      <c r="C71" s="131" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="D71" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="E71" s="155"/>
-      <c r="F71" s="155"/>
-      <c r="G71" s="154"/>
-      <c r="H71" s="155"/>
-      <c r="I71" s="154"/>
-      <c r="J71" s="166"/>
+      <c r="E71" s="148"/>
+      <c r="F71" s="148"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="148"/>
+      <c r="I71" s="147"/>
+      <c r="J71" s="159"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="D72" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H72" s="3"/>
+      <c r="I72" s="111" t="s">
         <v>192</v>
       </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="118" t="s">
-        <v>193</v>
-      </c>
-      <c r="J72" s="166"/>
+      <c r="J72" s="159"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="C73" s="138"/>
+      <c r="C73" s="131"/>
       <c r="D73" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H73" s="3"/>
+      <c r="I73" s="111" t="s">
         <v>194</v>
       </c>
-      <c r="H73" s="3"/>
-      <c r="I73" s="118" t="s">
-        <v>195</v>
-      </c>
-      <c r="J73" s="166"/>
+      <c r="J73" s="159"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="140" t="s">
-        <v>170</v>
-      </c>
-      <c r="C74" s="172">
+      <c r="B74" s="133" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="165">
         <v>45792</v>
       </c>
-      <c r="D74" s="142">
+      <c r="D74" s="135">
         <v>0.39930555555555602</v>
       </c>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
-      <c r="J74" s="166"/>
+      <c r="J74" s="159"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="173"/>
-      <c r="B75" s="174" t="s">
+      <c r="A75" s="166"/>
+      <c r="B75" s="167" t="s">
         <v>44</v>
       </c>
-      <c r="C75" s="175">
+      <c r="C75" s="168">
         <v>45939</v>
       </c>
-      <c r="D75" s="176">
+      <c r="D75" s="169">
         <v>0.40277777777777801</v>
       </c>
-      <c r="E75" s="177"/>
-      <c r="F75" s="177"/>
-      <c r="G75" s="178" t="s">
+      <c r="E75" s="170"/>
+      <c r="F75" s="170"/>
+      <c r="G75" s="171" t="s">
+        <v>195</v>
+      </c>
+      <c r="H75" s="171" t="s">
         <v>196</v>
       </c>
-      <c r="H75" s="178" t="s">
+      <c r="I75" s="171" t="s">
         <v>197</v>
       </c>
-      <c r="I75" s="178" t="s">
-        <v>198</v>
-      </c>
-      <c r="J75" s="166"/>
+      <c r="J75" s="159"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
-      <c r="C76" s="132"/>
+      <c r="C76" s="125"/>
       <c r="D76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
-      <c r="C77" s="132"/>
+      <c r="C77" s="125"/>
       <c r="D77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="179"/>
-      <c r="B78" s="180" t="s">
+      <c r="A78" s="172"/>
+      <c r="B78" s="173" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="174" t="s">
         <v>141</v>
       </c>
-      <c r="C78" s="181" t="s">
+      <c r="D78" s="173"/>
+      <c r="E78" s="175" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="175"/>
+      <c r="G78" s="176" t="s">
         <v>142</v>
       </c>
-      <c r="D78" s="180"/>
-      <c r="E78" s="182" t="s">
-        <v>4</v>
-      </c>
-      <c r="F78" s="182"/>
-      <c r="G78" s="183" t="s">
+      <c r="H78" s="173" t="s">
         <v>143</v>
       </c>
-      <c r="H78" s="180" t="s">
+      <c r="I78" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="I78" s="180" t="s">
-        <v>145</v>
-      </c>
-      <c r="J78" s="115"/>
+      <c r="J78" s="108"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="116" t="s">
-        <v>181</v>
-      </c>
-      <c r="B79" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" s="108">
+      <c r="A79" s="109" t="s">
+        <v>180</v>
+      </c>
+      <c r="B79" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79" s="101">
         <v>45676</v>
       </c>
-      <c r="D79" s="127" t="s">
-        <v>173</v>
-      </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116" t="s">
-        <v>147</v>
+      <c r="D79" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="E79" s="109"/>
+      <c r="F79" s="109" t="s">
+        <v>146</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J79" s="108"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="109" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" s="101"/>
+      <c r="D80" s="109"/>
+      <c r="E80" s="109"/>
+      <c r="F80" s="109"/>
+      <c r="H80" s="122" t="s">
         <v>199</v>
       </c>
-      <c r="J79" s="115"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="116" t="s">
-        <v>181</v>
-      </c>
-      <c r="B80" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="108"/>
-      <c r="D80" s="116"/>
-      <c r="E80" s="116"/>
-      <c r="F80" s="116"/>
-      <c r="H80" s="129" t="s">
-        <v>200</v>
-      </c>
-      <c r="I80" s="184">
+      <c r="I80" s="177">
         <v>45714</v>
       </c>
-      <c r="J80" s="115"/>
+      <c r="J80" s="108"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
@@ -4780,7 +4651,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="J81" s="115"/>
+      <c r="J81" s="108"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
@@ -4789,531 +4660,531 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="118" t="s">
-        <v>156</v>
-      </c>
-      <c r="J82" s="115"/>
+      <c r="I82" s="111" t="s">
+        <v>155</v>
+      </c>
+      <c r="J82" s="108"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="119"/>
-      <c r="B83" s="115"/>
-      <c r="C83" s="120"/>
-      <c r="D83" s="119"/>
-      <c r="E83" s="119"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="121"/>
-      <c r="H83" s="119"/>
-      <c r="I83" s="121"/>
-      <c r="J83" s="115"/>
+      <c r="A83" s="112"/>
+      <c r="B83" s="108"/>
+      <c r="C83" s="113"/>
+      <c r="D83" s="112"/>
+      <c r="E83" s="112"/>
+      <c r="F83" s="112"/>
+      <c r="G83" s="114"/>
+      <c r="H83" s="112"/>
+      <c r="I83" s="114"/>
+      <c r="J83" s="108"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
-      <c r="C84" s="132"/>
+      <c r="C84" s="125"/>
       <c r="D84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
-      <c r="C85" s="132"/>
+      <c r="C85" s="125"/>
       <c r="D85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="161"/>
-      <c r="B86" s="162" t="s">
+      <c r="A86" s="154"/>
+      <c r="B86" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86" s="156" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="163" t="s">
+      <c r="D86" s="155"/>
+      <c r="E86" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" s="157"/>
+      <c r="G86" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="162"/>
-      <c r="E86" s="164" t="s">
-        <v>4</v>
-      </c>
-      <c r="F86" s="164"/>
-      <c r="G86" s="165" t="s">
+      <c r="H86" s="155" t="s">
         <v>143</v>
       </c>
-      <c r="H86" s="162" t="s">
+      <c r="I86" s="155" t="s">
         <v>144</v>
       </c>
-      <c r="I86" s="162" t="s">
-        <v>145</v>
-      </c>
-      <c r="J86" s="166"/>
+      <c r="J86" s="159"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="116" t="s">
+      <c r="A87" s="109" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" s="178">
+        <v>45603</v>
+      </c>
+      <c r="D87" s="109" t="s">
+        <v>157</v>
+      </c>
+      <c r="E87" s="120">
+        <v>156000</v>
+      </c>
+      <c r="F87" s="109" t="s">
+        <v>146</v>
+      </c>
+      <c r="G87" s="102"/>
+      <c r="H87" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="B87" s="89" t="s">
-        <v>45</v>
-      </c>
-      <c r="C87" s="185">
-        <v>45603</v>
-      </c>
-      <c r="D87" s="116" t="s">
-        <v>158</v>
-      </c>
-      <c r="E87" s="127">
-        <v>156000</v>
-      </c>
-      <c r="F87" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="G87" s="109"/>
-      <c r="H87" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="I87" s="1">
         <v>45705</v>
       </c>
-      <c r="J87" s="166"/>
+      <c r="J87" s="159"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="116"/>
-      <c r="B88" s="87"/>
-      <c r="C88" s="108"/>
-      <c r="D88" s="116"/>
-      <c r="E88" s="87"/>
-      <c r="F88" s="116"/>
-      <c r="G88" s="109"/>
-      <c r="H88" s="129" t="s">
-        <v>203</v>
+      <c r="A88" s="109"/>
+      <c r="B88" s="80"/>
+      <c r="C88" s="101"/>
+      <c r="D88" s="109"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="109"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="122" t="s">
+        <v>202</v>
       </c>
       <c r="I88" s="1">
         <v>45705</v>
       </c>
-      <c r="J88" s="166"/>
+      <c r="J88" s="159"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
-      <c r="B89" s="131" t="s">
+      <c r="B89" s="124" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" s="141">
+        <v>45704</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C89" s="148">
-        <v>45704</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="J89" s="166"/>
+      <c r="J89" s="159"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C90" s="70">
+        <v>82</v>
+      </c>
+      <c r="C90" s="63">
         <v>45705</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="J90" s="166"/>
+      <c r="J90" s="159"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
-      <c r="J91" s="166"/>
+      <c r="J91" s="159"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
-      <c r="C92" s="132" t="s">
-        <v>163</v>
+      <c r="C92" s="125" t="s">
+        <v>162</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="G92" s="186"/>
+        <v>186</v>
+      </c>
+      <c r="G92" s="179"/>
       <c r="H92" s="3"/>
-      <c r="J92" s="166"/>
+      <c r="J92" s="159"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
-      <c r="C93" s="132">
+      <c r="C93" s="125">
         <v>45706</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="J93" s="166"/>
+      <c r="J93" s="159"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
-      <c r="C94" s="187">
+      <c r="C94" s="180">
         <v>45711</v>
       </c>
-      <c r="D94" s="150" t="s">
-        <v>188</v>
-      </c>
-      <c r="E94" s="150"/>
-      <c r="F94" s="150"/>
-      <c r="G94" s="152"/>
-      <c r="H94" s="150"/>
-      <c r="I94" s="153"/>
-      <c r="J94" s="166"/>
+      <c r="D94" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="E94" s="143"/>
+      <c r="F94" s="143"/>
+      <c r="G94" s="145"/>
+      <c r="H94" s="143"/>
+      <c r="I94" s="146"/>
+      <c r="J94" s="159"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="181"/>
+      <c r="D95" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C95" s="188"/>
-      <c r="D95" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="H95" s="3"/>
-      <c r="J95" s="166"/>
+      <c r="J95" s="159"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="J96" s="166"/>
+      <c r="J96" s="159"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="D97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="118" t="s">
-        <v>209</v>
-      </c>
-      <c r="J97" s="166"/>
+      <c r="I97" s="111" t="s">
+        <v>208</v>
+      </c>
+      <c r="J97" s="159"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="118" t="s">
-        <v>193</v>
-      </c>
-      <c r="J98" s="166"/>
+      <c r="I98" s="111" t="s">
+        <v>192</v>
+      </c>
+      <c r="J98" s="159"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B99" s="189" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" s="190">
+      <c r="B99" s="182" t="s">
+        <v>169</v>
+      </c>
+      <c r="C99" s="183">
         <v>45792</v>
       </c>
-      <c r="D99" s="191">
+      <c r="D99" s="184">
         <v>0.39583333333333298</v>
       </c>
       <c r="E99" s="13"/>
       <c r="F99" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
-      <c r="J99" s="166"/>
+      <c r="J99" s="159"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="166"/>
-      <c r="B100" s="192" t="s">
+      <c r="A100" s="159"/>
+      <c r="B100" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="C100" s="193">
+      <c r="C100" s="186">
         <v>45939</v>
       </c>
-      <c r="D100" s="194">
+      <c r="D100" s="187">
         <v>0.39583333333333298</v>
       </c>
-      <c r="E100" s="166"/>
-      <c r="F100" s="166"/>
-      <c r="G100" s="195"/>
-      <c r="H100" s="166"/>
-      <c r="I100" s="166"/>
-      <c r="J100" s="166"/>
+      <c r="E100" s="159"/>
+      <c r="F100" s="159"/>
+      <c r="G100" s="188"/>
+      <c r="H100" s="159"/>
+      <c r="I100" s="159"/>
+      <c r="J100" s="159"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="80"/>
-      <c r="B101" s="196"/>
-      <c r="C101" s="197"/>
-      <c r="D101" s="198"/>
-      <c r="E101" s="80"/>
-      <c r="F101" s="80"/>
-      <c r="G101" s="74"/>
-      <c r="H101" s="80"/>
-      <c r="I101" s="80"/>
-      <c r="J101" s="80"/>
+      <c r="A101" s="73"/>
+      <c r="B101" s="189"/>
+      <c r="C101" s="190"/>
+      <c r="D101" s="191"/>
+      <c r="E101" s="73"/>
+      <c r="F101" s="73"/>
+      <c r="G101" s="67"/>
+      <c r="H101" s="73"/>
+      <c r="I101" s="73"/>
+      <c r="J101" s="73"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
-      <c r="B102" s="196"/>
-      <c r="C102" s="197"/>
-      <c r="D102" s="198"/>
-      <c r="E102" s="80"/>
-      <c r="F102" s="80"/>
-      <c r="G102" s="74"/>
-      <c r="H102" s="80"/>
-      <c r="I102" s="80"/>
-      <c r="J102" s="80"/>
+      <c r="A102" s="73"/>
+      <c r="B102" s="189"/>
+      <c r="C102" s="190"/>
+      <c r="D102" s="191"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="67"/>
+      <c r="H102" s="73"/>
+      <c r="I102" s="73"/>
+      <c r="J102" s="73"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="199"/>
-      <c r="B103" s="199"/>
-      <c r="C103" s="200"/>
-      <c r="D103" s="199"/>
-      <c r="E103" s="199"/>
-      <c r="F103" s="199"/>
-      <c r="G103" s="201"/>
-      <c r="H103" s="199"/>
-      <c r="I103" s="201"/>
+      <c r="A103" s="192"/>
+      <c r="B103" s="192"/>
+      <c r="C103" s="193"/>
+      <c r="D103" s="192"/>
+      <c r="E103" s="192"/>
+      <c r="F103" s="192"/>
+      <c r="G103" s="194"/>
+      <c r="H103" s="192"/>
+      <c r="I103" s="194"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="88" t="s">
+      <c r="A104" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="B104" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="C104" s="83">
+        <v>45588</v>
+      </c>
+      <c r="D104" s="81" t="s">
+        <v>172</v>
+      </c>
+      <c r="E104" s="84"/>
+      <c r="F104" s="84"/>
+      <c r="G104" s="195">
+        <v>45672</v>
+      </c>
+      <c r="H104" s="81" t="s">
+        <v>210</v>
+      </c>
+      <c r="I104" s="86">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="81"/>
+      <c r="B105" s="82" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="83"/>
+      <c r="D105" s="81"/>
+      <c r="E105" s="84"/>
+      <c r="F105" s="84"/>
+      <c r="G105" s="195"/>
+      <c r="H105" s="81"/>
+      <c r="I105" s="86"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="B106" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="C106" s="83">
+        <v>45588</v>
+      </c>
+      <c r="D106" s="81" t="s">
+        <v>172</v>
+      </c>
+      <c r="E106" s="84"/>
+      <c r="F106" s="84"/>
+      <c r="G106" s="195">
+        <v>45672</v>
+      </c>
+      <c r="H106" s="196" t="s">
+        <v>212</v>
+      </c>
+      <c r="I106" s="86">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="B107" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="C107" s="197">
+        <v>45475</v>
+      </c>
+      <c r="D107" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="E107" s="198">
+        <v>113</v>
+      </c>
+      <c r="F107" s="122" t="s">
+        <v>146</v>
+      </c>
+      <c r="G107" s="195">
+        <v>45672</v>
+      </c>
+      <c r="H107" s="122" t="s">
         <v>201</v>
       </c>
-      <c r="B104" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="C104" s="90">
+      <c r="I107" s="199">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="122"/>
+      <c r="B108" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="C108" s="197"/>
+      <c r="D108" s="122"/>
+      <c r="E108" s="198"/>
+      <c r="F108" s="122"/>
+      <c r="G108" s="195"/>
+      <c r="H108" s="122"/>
+      <c r="I108" s="199"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="B109" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="C109" s="197"/>
+      <c r="D109" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="E109" s="198">
+        <v>113</v>
+      </c>
+      <c r="F109" s="122" t="s">
+        <v>146</v>
+      </c>
+      <c r="G109" s="195">
+        <v>45672</v>
+      </c>
+      <c r="H109" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="I109" s="199">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="201"/>
+      <c r="B113" s="192"/>
+      <c r="C113" s="193"/>
+      <c r="D113" s="201"/>
+      <c r="E113" s="192"/>
+      <c r="F113" s="194"/>
+      <c r="G113" s="194"/>
+      <c r="H113" s="194"/>
+      <c r="I113" s="194"/>
+    </row>
+    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="81" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114" s="166" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="202">
+        <v>45438</v>
+      </c>
+      <c r="D114" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="E114" s="81">
+        <v>0</v>
+      </c>
+      <c r="F114" s="203" t="s">
+        <v>215</v>
+      </c>
+      <c r="G114" s="85"/>
+      <c r="H114" s="81" t="s">
+        <v>216</v>
+      </c>
+      <c r="I114" s="85"/>
+    </row>
+    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="81"/>
+      <c r="B115" s="204" t="s">
+        <v>217</v>
+      </c>
+      <c r="C115" s="205">
+        <v>45486</v>
+      </c>
+      <c r="D115" s="81" t="s">
+        <v>218</v>
+      </c>
+      <c r="E115" s="81"/>
+      <c r="F115" s="206" t="s">
+        <v>215</v>
+      </c>
+      <c r="G115" s="207">
         <v>45588</v>
       </c>
-      <c r="D104" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="E104" s="91"/>
-      <c r="F104" s="91"/>
-      <c r="G104" s="202">
-        <v>45672</v>
-      </c>
-      <c r="H104" s="88" t="s">
-        <v>211</v>
-      </c>
-      <c r="I104" s="93">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="88"/>
-      <c r="B105" s="89" t="s">
-        <v>212</v>
-      </c>
-      <c r="C105" s="90"/>
-      <c r="D105" s="88"/>
-      <c r="E105" s="91"/>
-      <c r="F105" s="91"/>
-      <c r="G105" s="202"/>
-      <c r="H105" s="88"/>
-      <c r="I105" s="93"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="88" t="s">
-        <v>201</v>
-      </c>
-      <c r="B106" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="C106" s="90">
-        <v>45588</v>
-      </c>
-      <c r="D106" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="E106" s="91"/>
-      <c r="F106" s="91"/>
-      <c r="G106" s="202">
-        <v>45672</v>
-      </c>
-      <c r="H106" s="203" t="s">
-        <v>213</v>
-      </c>
-      <c r="I106" s="93">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="129" t="s">
-        <v>201</v>
-      </c>
-      <c r="B107" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="C107" s="204">
-        <v>45475</v>
-      </c>
-      <c r="D107" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="E107" s="205">
-        <v>113</v>
-      </c>
-      <c r="F107" s="129" t="s">
-        <v>147</v>
-      </c>
-      <c r="G107" s="202">
-        <v>45672</v>
-      </c>
-      <c r="H107" s="129" t="s">
-        <v>202</v>
-      </c>
-      <c r="I107" s="206">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="129"/>
-      <c r="B108" s="89" t="s">
-        <v>214</v>
-      </c>
-      <c r="C108" s="204"/>
-      <c r="D108" s="129"/>
-      <c r="E108" s="205"/>
-      <c r="F108" s="129"/>
-      <c r="G108" s="202"/>
-      <c r="H108" s="129"/>
-      <c r="I108" s="206"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="129" t="s">
-        <v>201</v>
-      </c>
-      <c r="B109" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="C109" s="204"/>
-      <c r="D109" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="E109" s="205">
-        <v>113</v>
-      </c>
-      <c r="F109" s="129" t="s">
-        <v>147</v>
-      </c>
-      <c r="G109" s="202">
-        <v>45672</v>
-      </c>
-      <c r="H109" s="207" t="s">
-        <v>203</v>
-      </c>
-      <c r="I109" s="206">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="208"/>
-      <c r="B113" s="199"/>
-      <c r="C113" s="200"/>
-      <c r="D113" s="208"/>
-      <c r="E113" s="199"/>
-      <c r="F113" s="201"/>
-      <c r="G113" s="201"/>
-      <c r="H113" s="201"/>
-      <c r="I113" s="201"/>
-    </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="88" t="s">
+      <c r="H115" s="81" t="s">
+        <v>219</v>
+      </c>
+      <c r="I115" s="85"/>
+    </row>
+    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="81"/>
+      <c r="B116" s="204" t="s">
+        <v>220</v>
+      </c>
+      <c r="C116" s="205">
+        <v>45590</v>
+      </c>
+      <c r="D116" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="E116" s="81"/>
+      <c r="F116" s="206" t="s">
         <v>215</v>
       </c>
-      <c r="B114" s="173" t="s">
-        <v>108</v>
-      </c>
-      <c r="C114" s="209">
-        <v>45438</v>
-      </c>
-      <c r="D114" s="88" t="s">
-        <v>158</v>
-      </c>
-      <c r="E114" s="88">
-        <v>0</v>
-      </c>
-      <c r="F114" s="210" t="s">
-        <v>216</v>
-      </c>
-      <c r="G114" s="92"/>
-      <c r="H114" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="I114" s="92"/>
-    </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="88"/>
-      <c r="B115" s="211" t="s">
-        <v>218</v>
-      </c>
-      <c r="C115" s="212">
-        <v>45486</v>
-      </c>
-      <c r="D115" s="88" t="s">
-        <v>219</v>
-      </c>
-      <c r="E115" s="88"/>
-      <c r="F115" s="213" t="s">
-        <v>216</v>
-      </c>
-      <c r="G115" s="214">
-        <v>45588</v>
-      </c>
-      <c r="H115" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="I115" s="92"/>
-    </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="88"/>
-      <c r="B116" s="211" t="s">
+      <c r="G116" s="207">
+        <v>45688</v>
+      </c>
+      <c r="H116" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="C116" s="212">
-        <v>45590</v>
-      </c>
-      <c r="D116" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="E116" s="88"/>
-      <c r="F116" s="213" t="s">
-        <v>216</v>
-      </c>
-      <c r="G116" s="214">
-        <v>45688</v>
-      </c>
-      <c r="H116" s="88" t="s">
+      <c r="I116" s="85"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="81"/>
+      <c r="B117" s="208"/>
+      <c r="C117" s="209"/>
+      <c r="D117" s="208" t="s">
         <v>222</v>
       </c>
-      <c r="I116" s="92"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="88"/>
-      <c r="B117" s="215"/>
-      <c r="C117" s="216"/>
-      <c r="D117" s="215" t="s">
+      <c r="E117" s="208"/>
+      <c r="F117" s="210"/>
+      <c r="G117" s="211">
+        <v>45782</v>
+      </c>
+      <c r="H117" s="81" t="s">
         <v>223</v>
       </c>
-      <c r="E117" s="215"/>
-      <c r="F117" s="217"/>
-      <c r="G117" s="218">
-        <v>45782</v>
-      </c>
-      <c r="H117" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="I117" s="92"/>
+      <c r="I117" s="85"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
-      <c r="B118" s="219"/>
-      <c r="C118" s="220"/>
+      <c r="B118" s="212"/>
+      <c r="C118" s="213"/>
       <c r="D118" s="3"/>
-      <c r="E118" s="219"/>
-      <c r="F118" s="221"/>
-      <c r="G118" s="222"/>
+      <c r="E118" s="212"/>
+      <c r="F118" s="214"/>
+      <c r="G118" s="215"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
-      <c r="B119" s="219"/>
-      <c r="C119" s="220"/>
+      <c r="B119" s="212"/>
+      <c r="C119" s="213"/>
       <c r="D119" s="3"/>
-      <c r="E119" s="219"/>
-      <c r="F119" s="221"/>
-      <c r="G119" s="222"/>
+      <c r="E119" s="212"/>
+      <c r="F119" s="214"/>
+      <c r="G119" s="215"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5335,13 +5206,13 @@
         <v>45967</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5349,13 +5220,13 @@
         <v>45927</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5363,21 +5234,21 @@
         <v>45708</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G7" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5387,28 +5258,28 @@
       <c r="D8" s="1">
         <v>46064</v>
       </c>
-      <c r="E8" s="223">
+      <c r="E8" s="216">
         <v>0.41666666666666702</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D15" s="1">
         <v>46028</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="216">
         <v>0.42708333333333298</v>
       </c>
     </row>

--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ABDEAE-40D9-45EF-BB97-A35EEC4117B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B712A76-A3C7-40A6-8930-1E23BD8C0B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="252">
   <si>
     <t>dava tarihi</t>
   </si>
@@ -237,9 +237,6 @@
     <t>yemin için duruşma günü</t>
   </si>
   <si>
-    <t>Yemin duruşması</t>
-  </si>
-  <si>
     <t>2024/3369</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
   </si>
   <si>
     <t>2025/1410</t>
-  </si>
-  <si>
-    <t>istinaf</t>
   </si>
   <si>
     <t>2026/3201</t>
@@ -830,6 +824,61 @@
   </si>
   <si>
     <t>imza toplanacak - adli tıptan rapor talebi -samsun</t>
+  </si>
+  <si>
+    <t>samsundan pozitif rapor geldi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>duruşma</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Davacı vekilinin 30/09/2023-15/01/2025 tarihleri yönünden davasını alacak davası olarak ıslah ettiği, ıslah dilekçesine binaen bu yönde hesaplatma yapılması için dosyanın hesap uzmanı bilirkişisine tevdii</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">duruşma </t>
+  </si>
+  <si>
+    <t>rapor pozitif geldi</t>
+  </si>
+  <si>
+    <t>Yemin duruşması - duruşma yapıldı. Tahliye kararı verildi</t>
+  </si>
+  <si>
+    <t>dosya icra dosyası üzerinden devam edecek</t>
+  </si>
+  <si>
+    <t>istinaf tan başvuru reddedildi dosya kaldığı yerden devam edecek</t>
+  </si>
+  <si>
+    <t>imza inkarı için</t>
+  </si>
+  <si>
+    <t>talep tebliğ tarihi</t>
+  </si>
+  <si>
+    <t>ödeme tarihi</t>
+  </si>
+  <si>
+    <t>dosya hatalı kapatıldığını farkettim</t>
+  </si>
+  <si>
+    <t>avukat işlem başlatacak</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1114,7 @@
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1246,6 +1295,18 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFA9D18E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFA9D18E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -1374,7 +1435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="26" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -1722,8 +1783,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -1733,6 +1792,29 @@
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="21" fontId="2" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2175,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2217,9 +2299,9 @@
     </row>
     <row r="5" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29"/>
-      <c r="B5" s="225"/>
+      <c r="B5" s="223"/>
       <c r="C5" s="217" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="50"/>
@@ -2298,7 +2380,7 @@
       <c r="A16" s="6">
         <v>45475</v>
       </c>
-      <c r="B16" s="228" t="s">
+      <c r="B16" s="226" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -2310,7 +2392,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="228"/>
+      <c r="B17" s="226"/>
       <c r="C17" s="218" t="s">
         <v>34</v>
       </c>
@@ -2320,8 +2402,8 @@
       <c r="A18" s="26">
         <v>45482</v>
       </c>
-      <c r="B18" s="227"/>
-      <c r="C18" s="226" t="s">
+      <c r="B18" s="225"/>
+      <c r="C18" s="224" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="220"/>
@@ -2330,7 +2412,7 @@
       <c r="A19" s="6">
         <v>45604</v>
       </c>
-      <c r="B19" s="228" t="s">
+      <c r="B19" s="226" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -2342,7 +2424,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="228"/>
+      <c r="B20" s="226"/>
       <c r="C20" s="8" t="s">
         <v>38</v>
       </c>
@@ -2352,8 +2434,8 @@
       <c r="A21" s="26">
         <v>45615</v>
       </c>
-      <c r="B21" s="227"/>
-      <c r="C21" s="226" t="s">
+      <c r="B21" s="225"/>
+      <c r="C21" s="224" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="220"/>
@@ -2362,7 +2444,7 @@
       <c r="A22" s="1">
         <v>45704</v>
       </c>
-      <c r="B22" s="229" t="s">
+      <c r="B22" s="227" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="13" t="s">
@@ -2403,857 +2485,936 @@
       </c>
       <c r="B26" s="34"/>
       <c r="C26" s="35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D26" s="50"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+    <row r="27" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="33">
+        <v>46204</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="232" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="50"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
         <v>46288</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>0.37638888888888888</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C28" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="3"/>
       <c r="D28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="B29" s="3"/>
+      <c r="D29" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
         <v>45603</v>
       </c>
-      <c r="B29" s="230" t="s">
+      <c r="B30" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C30" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="27"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="228"/>
-      <c r="C30" s="32" t="s">
+      <c r="D30" s="27"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="226"/>
+      <c r="C31" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="27"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="26">
+      <c r="D31" s="27"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="26">
         <v>45615</v>
       </c>
-      <c r="B31" s="227"/>
-      <c r="C31" s="28" t="s">
+      <c r="B32" s="225"/>
+      <c r="C32" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D32" s="5">
         <v>156000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>45704</v>
       </c>
-      <c r="B32" s="229" t="s">
+      <c r="B33" s="227" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D33" s="4">
         <v>86000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="3"/>
-      <c r="C33" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D34" s="37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>46086</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="3"/>
-      <c r="C35" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
       <c r="C36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="3"/>
+      <c r="C37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="18">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A38" s="233">
         <v>46196</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="234">
         <v>0.41319444444444398</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C38" s="235" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="236">
+        <v>46318</v>
+      </c>
+      <c r="B39" s="237"/>
+      <c r="C39" s="238" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="50"/>
+      <c r="F39" s="50"/>
+    </row>
+    <row r="40" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="233"/>
+      <c r="B40" s="234"/>
+      <c r="C40" s="239"/>
+      <c r="D40" s="50"/>
+      <c r="F40" s="50"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>45588</v>
+      </c>
+      <c r="B42" s="226" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="27"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="26">
+        <v>45596</v>
+      </c>
+      <c r="B43" s="225"/>
+      <c r="C43" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>45704</v>
+      </c>
+      <c r="B44" s="227" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46021</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="31"/>
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="3"/>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>45588</v>
-      </c>
-      <c r="B39" s="228" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="27"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="26">
-        <v>45596</v>
-      </c>
-      <c r="B40" s="227"/>
-      <c r="C40" s="28" t="s">
+      <c r="C46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="33">
+        <v>46155</v>
+      </c>
+      <c r="B47" s="34"/>
+      <c r="C47" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="33">
+        <v>46155</v>
+      </c>
+      <c r="B48" s="34"/>
+      <c r="C48" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="50"/>
+    </row>
+    <row r="49" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="33">
+        <v>46204</v>
+      </c>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D49" s="50"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="18">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="23">
+        <v>0.375</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="3"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="240"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>45475</v>
+      </c>
+      <c r="B52" s="226" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" s="27">
+        <v>158437</v>
+      </c>
+      <c r="E52" s="240"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="26">
+        <v>45482</v>
+      </c>
+      <c r="B53" s="226"/>
+      <c r="C53" s="218" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="27"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="225"/>
+      <c r="C54" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>45704</v>
-      </c>
-      <c r="B41" s="229" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>46021</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>46036</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="33">
-        <v>46155</v>
-      </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="33">
-        <v>46155</v>
-      </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="D45" s="50"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="18">
-        <v>46288</v>
-      </c>
-      <c r="B46" s="23">
-        <v>0.375</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="3"/>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>45475</v>
-      </c>
-      <c r="B48" s="228" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D48" s="27">
-        <v>158437</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="26">
-        <v>45482</v>
-      </c>
-      <c r="B49" s="228"/>
-      <c r="C49" s="218" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" s="27"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="227"/>
-      <c r="C50" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>46069</v>
       </c>
-      <c r="B51" s="229" t="s">
+      <c r="B55" s="227" t="s">
         <v>65</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="3"/>
-      <c r="C52" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>46077</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="38">
-        <v>46175</v>
-      </c>
-      <c r="B54" s="23">
-        <v>0.41319444444444398</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="F54" s="4"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B55" s="3"/>
       <c r="D55" s="5"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="3"/>
+      <c r="C56" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46077</v>
+      </c>
       <c r="B57" s="3"/>
-      <c r="C57" s="13"/>
+      <c r="C57" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="D57" s="5"/>
     </row>
-    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+    <row r="58" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="33"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="50"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="38">
+        <v>46175</v>
+      </c>
+      <c r="B59" s="23">
+        <v>0.41319444444444398</v>
+      </c>
+      <c r="C59" s="241" t="s">
+        <v>244</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="3"/>
+      <c r="C60" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D60" s="5"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="3"/>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="3"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
         <v>45342</v>
       </c>
-      <c r="B58" s="230" t="s">
+      <c r="B63" s="228" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="D58" s="9" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="225"/>
+      <c r="C64" s="13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="227"/>
-      <c r="C59" s="13" t="s">
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="39">
+        <v>45450</v>
+      </c>
+      <c r="B65" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="D59" s="5"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="39">
-        <v>45450</v>
-      </c>
-      <c r="B60" s="231" t="s">
+      <c r="C65" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="D60" s="2" t="s">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>45680</v>
+      </c>
+      <c r="B66" s="225"/>
+      <c r="C66" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="244" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>45680</v>
-      </c>
-      <c r="B61" s="227"/>
-      <c r="C61" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" s="224" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>45726</v>
+      </c>
+      <c r="B67" s="230"/>
+      <c r="C67" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>45726</v>
-      </c>
-      <c r="B62" s="232"/>
-      <c r="C62" s="2" t="s">
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="219">
+        <v>45765</v>
+      </c>
+      <c r="B68" s="231" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="219">
-        <v>45765</v>
-      </c>
-      <c r="B63" s="233" t="s">
+      <c r="C68" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D68" s="5"/>
+      <c r="F68" s="5"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="221"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" s="220"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="3"/>
+      <c r="C70" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" s="5"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="3"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="5"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="40">
+        <v>46076</v>
+      </c>
+      <c r="B72" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="F63" s="5"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="221"/>
-      <c r="B64" s="222"/>
-      <c r="C64" s="223" t="s">
+      <c r="C72" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D72" s="20">
+        <v>515608</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="40"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D64" s="220"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B65" s="3"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="3"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B67" s="3"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B68" s="3"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="40">
-        <v>46076</v>
-      </c>
-      <c r="B69" s="41" t="s">
+      <c r="D73" s="42">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="40">
+        <v>46120</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C69" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D69" s="20">
-        <v>515608</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="40"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="41" t="s">
+      <c r="C74" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D70" s="42">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="40">
-        <v>46120</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D71" s="43"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D72" s="43"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="40">
-        <v>46120</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D73" s="43"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D74" s="43"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="40">
         <v>46121</v>
       </c>
-      <c r="B75" s="3"/>
+      <c r="B75" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="C75" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D75" s="43"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B76" s="3"/>
+        <v>46120</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D76" s="43"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="40"/>
-      <c r="B77" s="3"/>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="40">
+        <v>46121</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="C77" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D77" s="43"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="40"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="40">
+        <v>46121</v>
+      </c>
       <c r="B78" s="3"/>
       <c r="C78" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D78" s="43"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="40"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="40">
+        <v>46122</v>
+      </c>
       <c r="B79" s="3"/>
       <c r="C79" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D79" s="43"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="40"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D80" s="43"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="40"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D81" s="43"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="40"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="43"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="40"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="43"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="40">
+        <v>46122</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D79" s="43"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="40"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="31" t="s">
+      <c r="D84" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D80" s="43"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="40">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="40">
         <v>46122</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B85" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D85" s="48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="40">
+        <v>46127</v>
+      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="28" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="D86" s="44">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="40"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D82" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="40">
-        <v>46127</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="28" t="s">
+      <c r="D87" s="43"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="40"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D83" s="44">
-        <v>375000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="40"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="28" t="s">
+      <c r="D88" s="43"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="43"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="D84" s="43"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="40"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D85" s="43"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="43"/>
-      <c r="B86" s="43"/>
-      <c r="C86" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D86" s="43"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B87" s="3"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="40">
-        <v>45676</v>
-      </c>
-      <c r="B88" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C88" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D88" s="47"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="46">
-        <v>45698</v>
-      </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D89" s="47"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="40"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D90" s="47" t="s">
-        <v>102</v>
-      </c>
+      <c r="D89" s="43"/>
+    </row>
+    <row r="90" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="40">
+        <v>46206</v>
+      </c>
+      <c r="B90" s="43"/>
+      <c r="C90" s="242" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" s="43"/>
     </row>
     <row r="91" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="33"/>
-      <c r="B91" s="34"/>
-      <c r="C91" s="49"/>
-      <c r="D91" s="50"/>
+      <c r="A91" s="40">
+        <v>46126</v>
+      </c>
+      <c r="B91" s="43"/>
+      <c r="C91" s="242" t="s">
+        <v>249</v>
+      </c>
+      <c r="D91" s="43"/>
     </row>
     <row r="92" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="40">
+        <v>46217</v>
+      </c>
+      <c r="B92" s="43"/>
+      <c r="C92" s="242" t="s">
+        <v>250</v>
+      </c>
+      <c r="D92" s="43"/>
+    </row>
+    <row r="93" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="43"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="242" t="s">
+        <v>251</v>
+      </c>
+      <c r="D93" s="43"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B94" s="3"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="5"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="40">
+        <v>45676</v>
+      </c>
+      <c r="B95" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95" s="47"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="46">
+        <v>45698</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D96" s="47"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="40"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97" s="243" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="33"/>
+      <c r="B98" s="34"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="50"/>
+    </row>
+    <row r="99" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="40">
         <v>46205</v>
       </c>
-      <c r="B92" s="45" t="s">
+      <c r="B99" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" s="47"/>
+    </row>
+    <row r="100" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="46">
+        <v>45482</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="47"/>
+    </row>
+    <row r="101" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="40">
+        <v>45672</v>
+      </c>
+      <c r="B101" s="45"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="243" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B102" s="3"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="5"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="52">
+        <v>45588</v>
+      </c>
+      <c r="B103" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C92" s="41" t="s">
+      <c r="C103" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" s="243" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="52"/>
+      <c r="B104" s="53"/>
+      <c r="C104" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="D92" s="47"/>
-    </row>
-    <row r="93" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="46">
-        <v>45482</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D93" s="47"/>
-    </row>
-    <row r="94" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="40">
-        <v>45672</v>
-      </c>
-      <c r="B94" s="45"/>
-      <c r="C94" s="41"/>
-      <c r="D94" s="47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B95" s="3"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="5"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="52">
-        <v>45588</v>
-      </c>
-      <c r="B96" s="53" t="s">
+      <c r="D104" s="55"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="56">
+        <v>45438</v>
+      </c>
+      <c r="B105" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="C96" s="54" t="s">
+      <c r="C105" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" s="48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="56"/>
+      <c r="B106" s="57"/>
+      <c r="C106" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D106" s="47">
+        <v>193500</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="56">
+        <v>45288</v>
+      </c>
+      <c r="B107" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D107" s="61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="56"/>
+      <c r="B108" s="60"/>
+      <c r="C108" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="D96" s="47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="52"/>
-      <c r="B97" s="53"/>
-      <c r="C97" s="54" t="s">
+      <c r="D108" s="59"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="56">
+        <v>45148</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="C109" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" s="62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="56"/>
+      <c r="B110" s="60"/>
+      <c r="C110" s="61"/>
+      <c r="D110" s="59"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="56">
+        <v>44928</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C111" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="D97" s="55"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="56">
-        <v>45438</v>
-      </c>
-      <c r="B98" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="C98" s="58" t="s">
+      <c r="D111" s="47">
+        <v>24316</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="56"/>
+      <c r="B112" s="60"/>
+      <c r="C112" s="61"/>
+      <c r="D112" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="D98" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="56"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D99" s="47">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="56">
-        <v>45288</v>
-      </c>
-      <c r="B100" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="D100" s="61" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="56"/>
-      <c r="B101" s="60"/>
-      <c r="C101" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D101" s="59"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="56">
-        <v>45148</v>
-      </c>
-      <c r="B102" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C102" s="61" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" s="62" t="s">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="56">
+        <v>44333</v>
+      </c>
+      <c r="B113" s="60" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="56"/>
-      <c r="B103" s="60"/>
-      <c r="C103" s="61"/>
-      <c r="D103" s="59"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="56">
-        <v>44928</v>
-      </c>
-      <c r="B104" s="60" t="s">
+      <c r="C113" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="C104" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" s="47">
-        <v>24316</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="56"/>
-      <c r="B105" s="60"/>
-      <c r="C105" s="61"/>
-      <c r="D105" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="56">
-        <v>44333</v>
-      </c>
-      <c r="B106" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="C106" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D106" s="47"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="56"/>
-      <c r="B107" s="60"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="59"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B108" s="3"/>
-      <c r="D108" s="5"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-      <c r="C109"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-      <c r="C110"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111"/>
-      <c r="C111"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B112" s="3"/>
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B113" s="3"/>
-      <c r="D113" s="5"/>
+      <c r="D113" s="47"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B114" s="3"/>
-      <c r="D114" s="5"/>
+      <c r="A114" s="56"/>
+      <c r="B114" s="60"/>
+      <c r="C114" s="61"/>
+      <c r="D114" s="59"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B115" s="3"/>
       <c r="D115" s="5"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D119" s="2"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D125" s="2"/>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B138" s="2"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="2"/>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B140" s="2"/>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B141" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="D119" s="5"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B120" s="3"/>
+      <c r="D120" s="5"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="3"/>
+      <c r="D121" s="5"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="3"/>
+      <c r="D122" s="5"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D126" s="2"/>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D132" s="2"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="2"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="2"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="2"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
@@ -3291,10 +3452,10 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -3308,7 +3469,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" s="13"/>
     </row>
@@ -3408,10 +3569,10 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
@@ -3422,7 +3583,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" s="13"/>
     </row>
@@ -3492,7 +3653,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="66"/>
@@ -3506,10 +3667,10 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="68" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="65"/>
@@ -3532,40 +3693,40 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="64"/>
       <c r="B4" s="69" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" s="66"/>
       <c r="D4" s="68" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
       <c r="G4" s="68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" s="68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="64"/>
       <c r="B5" s="69" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E5" s="65"/>
       <c r="F5" s="65"/>
       <c r="G5" s="70" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H5" s="68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I5" s="65"/>
     </row>
@@ -3583,13 +3744,13 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="64"/>
       <c r="B7" s="71" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7" s="63">
         <v>45827</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2">
         <v>9</v>
@@ -3598,7 +3759,7 @@
         <v>40</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I7" s="65"/>
     </row>
@@ -3622,7 +3783,7 @@
         <v>45939</v>
       </c>
       <c r="D9" s="73" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" s="73">
         <v>9</v>
@@ -3631,20 +3792,20 @@
         <v>30</v>
       </c>
       <c r="H9" s="65" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I9" s="65"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
       <c r="B10" s="72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C10" s="66">
         <v>45939</v>
       </c>
       <c r="D10" s="65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E10" s="65">
         <v>9</v>
@@ -3654,7 +3815,7 @@
       </c>
       <c r="G10" s="67"/>
       <c r="H10" s="65" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I10" s="65"/>
     </row>
@@ -3667,7 +3828,7 @@
         <v>45952</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -3677,7 +3838,7 @@
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I11" s="67"/>
     </row>
@@ -3690,7 +3851,7 @@
         <v>45952</v>
       </c>
       <c r="D12" s="65" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="65">
         <v>9</v>
@@ -3700,7 +3861,7 @@
       </c>
       <c r="G12" s="67"/>
       <c r="H12" s="65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I12" s="67"/>
     </row>
@@ -3730,10 +3891,10 @@
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="75"/>
       <c r="B17" s="76" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D17" s="76"/>
       <c r="E17" s="78" t="s">
@@ -3741,32 +3902,32 @@
       </c>
       <c r="F17" s="78"/>
       <c r="G17" s="79" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="76" t="s">
         <v>142</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>143</v>
-      </c>
-      <c r="I17" s="76" t="s">
-        <v>144</v>
       </c>
       <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="81" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="83">
         <v>45342</v>
       </c>
       <c r="D18" s="81" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" s="84"/>
       <c r="F18" s="85" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G18" s="86"/>
       <c r="H18" s="84"/>
@@ -3776,17 +3937,17 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="81"/>
       <c r="B19" s="87" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C19" s="83">
         <v>45537</v>
       </c>
       <c r="D19" s="81" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E19" s="84"/>
       <c r="F19" s="88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G19" s="86">
         <v>45691</v>
@@ -3800,7 +3961,7 @@
       <c r="B20" s="89"/>
       <c r="C20" s="90"/>
       <c r="D20" s="91" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
@@ -3812,7 +3973,7 @@
         <v>45726</v>
       </c>
       <c r="D21" s="93" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E21" s="93"/>
       <c r="F21" s="94"/>
@@ -3857,10 +4018,10 @@
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="103"/>
       <c r="B27" s="104" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C27" s="105" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D27" s="104"/>
       <c r="E27" s="106" t="s">
@@ -3868,25 +4029,25 @@
       </c>
       <c r="F27" s="106"/>
       <c r="G27" s="107" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="104" t="s">
+        <v>141</v>
+      </c>
+      <c r="I27" s="104" t="s">
         <v>142</v>
-      </c>
-      <c r="H27" s="104" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="104" t="s">
-        <v>144</v>
       </c>
       <c r="J27" s="108"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="109" t="s">
         <v>152</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H28" s="109" t="s">
-        <v>154</v>
       </c>
       <c r="I28" s="110">
         <v>45712</v>
@@ -3905,7 +4066,7 @@
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="111" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J30" s="108"/>
     </row>
@@ -3930,10 +4091,10 @@
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="115"/>
       <c r="B34" s="116" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C34" s="117" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D34" s="116"/>
       <c r="E34" s="118" t="s">
@@ -3941,19 +4102,19 @@
       </c>
       <c r="F34" s="118"/>
       <c r="G34" s="119" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="116" t="s">
+        <v>141</v>
+      </c>
+      <c r="I34" s="116" t="s">
         <v>142</v>
-      </c>
-      <c r="H34" s="116" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="116" t="s">
-        <v>144</v>
       </c>
       <c r="J34" s="80"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="112" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B35" s="82" t="s">
         <v>32</v>
@@ -3962,16 +4123,16 @@
         <v>45475</v>
       </c>
       <c r="D35" s="109" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E35" s="120">
         <v>97</v>
       </c>
       <c r="F35" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H35" s="109" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I35" s="102">
         <v>45705</v>
@@ -3987,16 +4148,16 @@
         <v>45604</v>
       </c>
       <c r="D36" s="109" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E36" s="120">
         <v>178</v>
       </c>
       <c r="F36" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H36" s="122" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I36" s="123">
         <v>45705</v>
@@ -4012,20 +4173,20 @@
         <v>45704</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J37" s="80"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C38" s="63">
         <v>45705</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H38" s="3"/>
       <c r="J38" s="80"/>
@@ -4040,10 +4201,10 @@
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="C40" s="125" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H40" s="3"/>
       <c r="J40" s="80"/>
@@ -4057,15 +4218,15 @@
         <v>2</v>
       </c>
       <c r="E41" s="128" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F41" s="127"/>
       <c r="G41" s="129"/>
       <c r="H41" s="127" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I41" s="130" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J41" s="80"/>
     </row>
@@ -4073,17 +4234,17 @@
       <c r="A42" s="3"/>
       <c r="C42" s="131"/>
       <c r="D42" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J42" s="80"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="132"/>
       <c r="B43" s="133" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C43" s="134">
         <v>45805</v>
@@ -4092,7 +4253,7 @@
         <v>0.40972222222222199</v>
       </c>
       <c r="E43" s="132" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F43" s="132"/>
       <c r="G43" s="136"/>
@@ -4107,7 +4268,7 @@
         <v>45805</v>
       </c>
       <c r="D44" s="120" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E44" s="120"/>
       <c r="F44" s="120"/>
@@ -4127,10 +4288,10 @@
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="115"/>
       <c r="B47" s="116" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C47" s="117" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D47" s="116"/>
       <c r="E47" s="118" t="s">
@@ -4138,19 +4299,19 @@
       </c>
       <c r="F47" s="118"/>
       <c r="G47" s="119" t="s">
+        <v>140</v>
+      </c>
+      <c r="H47" s="116" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" s="116" t="s">
         <v>142</v>
-      </c>
-      <c r="H47" s="116" t="s">
-        <v>143</v>
-      </c>
-      <c r="I47" s="116" t="s">
-        <v>144</v>
       </c>
       <c r="J47" s="80"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="109" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B48" s="82" t="s">
         <v>55</v>
@@ -4159,14 +4320,14 @@
         <v>45588</v>
       </c>
       <c r="D48" s="120" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E48" s="80"/>
       <c r="F48" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H48" s="109" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I48" s="102">
         <v>45630</v>
@@ -4183,7 +4344,7 @@
       <c r="E49" s="80"/>
       <c r="F49" s="109"/>
       <c r="H49" s="122" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I49" s="102">
         <v>45630</v>
@@ -4199,7 +4360,7 @@
         <v>45704</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -4209,13 +4370,13 @@
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C51" s="63">
         <v>45709</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="80"/>
@@ -4223,10 +4384,10 @@
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="C52" s="125" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H52" s="3"/>
       <c r="J52" s="80"/>
@@ -4237,7 +4398,7 @@
         <v>45712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3"/>
       <c r="J53" s="80"/>
@@ -4251,12 +4412,12 @@
         <v>2</v>
       </c>
       <c r="E54" s="144" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F54" s="143"/>
       <c r="G54" s="145"/>
       <c r="H54" s="143" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I54" s="146"/>
       <c r="J54" s="80"/>
@@ -4264,7 +4425,7 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="147"/>
@@ -4275,20 +4436,20 @@
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="147"/>
       <c r="H56" s="148"/>
       <c r="I56" s="149" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="150" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C57" s="151">
         <v>45805</v>
@@ -4305,7 +4466,7 @@
         <v>45805</v>
       </c>
       <c r="D58" s="109" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E58" s="80"/>
       <c r="F58" s="80"/>
@@ -4344,10 +4505,10 @@
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="154"/>
       <c r="B62" s="155" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C62" s="156" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D62" s="155"/>
       <c r="E62" s="157" t="s">
@@ -4355,19 +4516,19 @@
       </c>
       <c r="F62" s="157"/>
       <c r="G62" s="158" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" s="155" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" s="155" t="s">
         <v>142</v>
-      </c>
-      <c r="H62" s="155" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" s="155" t="s">
-        <v>144</v>
       </c>
       <c r="J62" s="159"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="112" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B63" s="82" t="s">
         <v>62</v>
@@ -4376,16 +4537,16 @@
         <v>45475</v>
       </c>
       <c r="D63" s="109" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E63" s="120">
         <v>214</v>
       </c>
       <c r="F63" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H63" s="109" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I63" s="102">
         <v>45702</v>
@@ -4402,7 +4563,7 @@
       <c r="E64" s="80"/>
       <c r="F64" s="109"/>
       <c r="H64" s="122" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I64" s="102">
         <v>45702</v>
@@ -4418,7 +4579,7 @@
         <v>45704</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H65" s="3"/>
       <c r="J65" s="159"/>
@@ -4426,13 +4587,13 @@
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C66" s="63">
         <v>45705</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H66" s="3"/>
       <c r="J66" s="159"/>
@@ -4440,7 +4601,7 @@
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H67" s="3"/>
       <c r="J67" s="159"/>
@@ -4448,10 +4609,10 @@
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="C68" s="125" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H68" s="3"/>
       <c r="J68" s="159"/>
@@ -4462,7 +4623,7 @@
         <v>45711</v>
       </c>
       <c r="D69" s="162" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E69" s="162"/>
       <c r="F69" s="162"/>
@@ -4477,7 +4638,7 @@
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="131" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D70" s="148"/>
       <c r="E70" s="148"/>
@@ -4493,10 +4654,10 @@
       </c>
       <c r="B71" s="13"/>
       <c r="C71" s="131" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E71" s="148"/>
       <c r="F71" s="148"/>
@@ -4508,11 +4669,11 @@
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J72" s="159"/>
     </row>
@@ -4520,18 +4681,18 @@
       <c r="A73" s="3"/>
       <c r="C73" s="131"/>
       <c r="D73" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="111" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J73" s="159"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="133" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C74" s="165">
         <v>45792</v>
@@ -4557,13 +4718,13 @@
       <c r="E75" s="170"/>
       <c r="F75" s="170"/>
       <c r="G75" s="171" t="s">
+        <v>193</v>
+      </c>
+      <c r="H75" s="171" t="s">
+        <v>194</v>
+      </c>
+      <c r="I75" s="171" t="s">
         <v>195</v>
-      </c>
-      <c r="H75" s="171" t="s">
-        <v>196</v>
-      </c>
-      <c r="I75" s="171" t="s">
-        <v>197</v>
       </c>
       <c r="J75" s="159"/>
     </row>
@@ -4582,10 +4743,10 @@
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="172"/>
       <c r="B78" s="173" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C78" s="174" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D78" s="173"/>
       <c r="E78" s="175" t="s">
@@ -4593,51 +4754,51 @@
       </c>
       <c r="F78" s="175"/>
       <c r="G78" s="176" t="s">
+        <v>140</v>
+      </c>
+      <c r="H78" s="173" t="s">
+        <v>141</v>
+      </c>
+      <c r="I78" s="173" t="s">
         <v>142</v>
-      </c>
-      <c r="H78" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="I78" s="173" t="s">
-        <v>144</v>
       </c>
       <c r="J78" s="108"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="109" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B79" s="82" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C79" s="101">
         <v>45676</v>
       </c>
       <c r="D79" s="120" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E79" s="109"/>
       <c r="F79" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J79" s="108"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="109" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C80" s="101"/>
       <c r="D80" s="109"/>
       <c r="E80" s="109"/>
       <c r="F80" s="109"/>
       <c r="H80" s="122" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I80" s="177">
         <v>45714</v>
@@ -4661,7 +4822,7 @@
       <c r="F82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="111" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J82" s="108"/>
     </row>
@@ -4692,10 +4853,10 @@
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="154"/>
       <c r="B86" s="155" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C86" s="156" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D86" s="155"/>
       <c r="E86" s="157" t="s">
@@ -4703,19 +4864,19 @@
       </c>
       <c r="F86" s="157"/>
       <c r="G86" s="158" t="s">
+        <v>140</v>
+      </c>
+      <c r="H86" s="155" t="s">
+        <v>141</v>
+      </c>
+      <c r="I86" s="155" t="s">
         <v>142</v>
-      </c>
-      <c r="H86" s="155" t="s">
-        <v>143</v>
-      </c>
-      <c r="I86" s="155" t="s">
-        <v>144</v>
       </c>
       <c r="J86" s="159"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="109" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B87" s="82" t="s">
         <v>45</v>
@@ -4724,17 +4885,17 @@
         <v>45603</v>
       </c>
       <c r="D87" s="109" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E87" s="120">
         <v>156000</v>
       </c>
       <c r="F87" s="109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G87" s="102"/>
       <c r="H87" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I87" s="1">
         <v>45705</v>
@@ -4750,7 +4911,7 @@
       <c r="F88" s="109"/>
       <c r="G88" s="102"/>
       <c r="H88" s="122" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I88" s="1">
         <v>45705</v>
@@ -4760,13 +4921,13 @@
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="124" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C89" s="141">
         <v>45704</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="3"/>
@@ -4775,13 +4936,13 @@
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C90" s="63">
         <v>45705</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H90" s="3"/>
       <c r="J90" s="159"/>
@@ -4793,10 +4954,10 @@
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="C92" s="125" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G92" s="179"/>
       <c r="H92" s="3"/>
@@ -4808,7 +4969,7 @@
         <v>45706</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H93" s="3"/>
       <c r="J93" s="159"/>
@@ -4819,7 +4980,7 @@
         <v>45711</v>
       </c>
       <c r="D94" s="143" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E94" s="143"/>
       <c r="F94" s="143"/>
@@ -4831,11 +4992,11 @@
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C95" s="181"/>
       <c r="D95" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H95" s="3"/>
       <c r="J95" s="159"/>
@@ -4843,7 +5004,7 @@
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H96" s="3"/>
       <c r="J96" s="159"/>
@@ -4853,7 +5014,7 @@
       <c r="D97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="111" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J97" s="159"/>
     </row>
@@ -4862,13 +5023,13 @@
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J98" s="159"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" s="182" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C99" s="183">
         <v>45792</v>
@@ -4878,7 +5039,7 @@
       </c>
       <c r="E99" s="13"/>
       <c r="F99" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
@@ -4939,16 +5100,16 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="81" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B104" s="82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C104" s="83">
         <v>45588</v>
       </c>
       <c r="D104" s="81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E104" s="84"/>
       <c r="F104" s="84"/>
@@ -4956,7 +5117,7 @@
         <v>45672</v>
       </c>
       <c r="H104" s="81" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I104" s="86">
         <v>45625</v>
@@ -4965,7 +5126,7 @@
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="81"/>
       <c r="B105" s="82" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C105" s="83"/>
       <c r="D105" s="81"/>
@@ -4977,16 +5138,16 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="81" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B106" s="82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C106" s="83">
         <v>45588</v>
       </c>
       <c r="D106" s="81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E106" s="84"/>
       <c r="F106" s="84"/>
@@ -4994,7 +5155,7 @@
         <v>45672</v>
       </c>
       <c r="H106" s="196" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I106" s="86">
         <v>45625</v>
@@ -5002,28 +5163,28 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="122" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B107" s="82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C107" s="197">
         <v>45475</v>
       </c>
       <c r="D107" s="122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E107" s="198">
         <v>113</v>
       </c>
       <c r="F107" s="122" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G107" s="195">
         <v>45672</v>
       </c>
       <c r="H107" s="122" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I107" s="199">
         <v>45705</v>
@@ -5032,7 +5193,7 @@
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="122"/>
       <c r="B108" s="82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C108" s="197"/>
       <c r="D108" s="122"/>
@@ -5044,26 +5205,26 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="122" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B109" s="82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C109" s="197"/>
       <c r="D109" s="122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E109" s="198">
         <v>113</v>
       </c>
       <c r="F109" s="122" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G109" s="195">
         <v>45672</v>
       </c>
       <c r="H109" s="200" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I109" s="199">
         <v>45705</v>
@@ -5082,72 +5243,72 @@
     </row>
     <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="81" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B114" s="166" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C114" s="202">
         <v>45438</v>
       </c>
       <c r="D114" s="81" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E114" s="81">
         <v>0</v>
       </c>
       <c r="F114" s="203" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G114" s="85"/>
       <c r="H114" s="81" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I114" s="85"/>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="81"/>
       <c r="B115" s="204" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C115" s="205">
         <v>45486</v>
       </c>
       <c r="D115" s="81" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E115" s="81"/>
       <c r="F115" s="206" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G115" s="207">
         <v>45588</v>
       </c>
       <c r="H115" s="81" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I115" s="85"/>
     </row>
     <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="81"/>
       <c r="B116" s="204" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C116" s="205">
         <v>45590</v>
       </c>
       <c r="D116" s="81" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E116" s="81"/>
       <c r="F116" s="206" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G116" s="207">
         <v>45688</v>
       </c>
       <c r="H116" s="81" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I116" s="85"/>
     </row>
@@ -5156,7 +5317,7 @@
       <c r="B117" s="208"/>
       <c r="C117" s="209"/>
       <c r="D117" s="208" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E117" s="208"/>
       <c r="F117" s="210"/>
@@ -5164,7 +5325,7 @@
         <v>45782</v>
       </c>
       <c r="H117" s="81" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I117" s="85"/>
     </row>
@@ -5206,13 +5367,13 @@
         <v>45967</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5220,13 +5381,13 @@
         <v>45927</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5234,21 +5395,21 @@
         <v>45708</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G7" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5264,17 +5425,17 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D15" s="1">
         <v>46028</v>

--- a/mahkeme/2026-01-Dosya Listesi.xlsx
+++ b/mahkeme/2026-01-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B712A76-A3C7-40A6-8930-1E23BD8C0B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88AB579-1302-4511-9B63-66F8AD4826C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="258">
   <si>
     <t>dava tarihi</t>
   </si>
@@ -866,19 +866,58 @@
     <t>istinaf tan başvuru reddedildi dosya kaldığı yerden devam edecek</t>
   </si>
   <si>
-    <t>imza inkarı için</t>
-  </si>
-  <si>
     <t>talep tebliğ tarihi</t>
   </si>
   <si>
-    <t>ödeme tarihi</t>
-  </si>
-  <si>
     <t>dosya hatalı kapatıldığını farkettim</t>
   </si>
   <si>
     <t>avukat işlem başlatacak</t>
+  </si>
+  <si>
+    <t>2026/289</t>
+  </si>
+  <si>
+    <t>kiralananın tahliyesi-icra</t>
+  </si>
+  <si>
+    <t>ön inceleme duruşması</t>
+  </si>
+  <si>
+    <t>imza inkarı için DOSYA KAPATILMIŞ !!!!!!!!!!!!!!!!!!!!!!!!!!</t>
+  </si>
+  <si>
+    <t>GERKEÇELİ KARAR YAZILDI. TEBLİGAT VE İSTİNAF BEKLENİYOR</t>
+  </si>
+  <si>
+    <t>icra hukuk aşağıda izleniyor</t>
+  </si>
+  <si>
+    <t>ödeme tarihi - ödeme 30 gün içinde yapılmadığı için temerrüt</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">salih ant - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>icra hukuk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> - 2026/3201 den tahliye talebi</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -891,7 +930,7 @@
     <numFmt numFmtId="166" formatCode="dd/mmm"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1113,8 +1152,17 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1307,6 +1355,18 @@
         <bgColor rgb="FFA9D18E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFA9D18E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -1435,7 +1495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="26" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -1807,14 +1867,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2257,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2308,8 +2380,12 @@
     </row>
     <row r="6" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="36"/>
+      <c r="B6" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>255</v>
+      </c>
       <c r="D6" s="50"/>
       <c r="E6" s="50"/>
     </row>
@@ -2805,16 +2881,16 @@
       <c r="D58" s="50"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="38">
+      <c r="A59" s="245">
         <v>46175</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="234">
         <v>0.41319444444444398</v>
       </c>
-      <c r="C59" s="241" t="s">
+      <c r="C59" s="246" t="s">
         <v>244</v>
       </c>
-      <c r="D59" s="4"/>
+      <c r="D59" s="247"/>
       <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2825,7 +2901,11 @@
       <c r="D60" s="5"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B61" s="3"/>
+      <c r="A61" s="248"/>
+      <c r="B61" s="249"/>
+      <c r="C61" s="250" t="s">
+        <v>254</v>
+      </c>
       <c r="D61" s="5"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2876,7 +2956,7 @@
       <c r="C66" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="244" t="s">
+      <c r="D66" s="242" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2912,8 +2992,8 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B70" s="3"/>
-      <c r="C70" s="34" t="s">
-        <v>247</v>
+      <c r="C70" s="254" t="s">
+        <v>253</v>
       </c>
       <c r="D70" s="5"/>
     </row>
@@ -3104,8 +3184,8 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="43"/>
-      <c r="B89" s="43"/>
-      <c r="C89" s="43" t="s">
+      <c r="B89" s="251"/>
+      <c r="C89" s="251" t="s">
         <v>95</v>
       </c>
       <c r="D89" s="43"/>
@@ -3114,9 +3194,9 @@
       <c r="A90" s="40">
         <v>46206</v>
       </c>
-      <c r="B90" s="43"/>
-      <c r="C90" s="242" t="s">
-        <v>248</v>
+      <c r="B90" s="251"/>
+      <c r="C90" s="252" t="s">
+        <v>247</v>
       </c>
       <c r="D90" s="43"/>
     </row>
@@ -3124,9 +3204,9 @@
       <c r="A91" s="40">
         <v>46126</v>
       </c>
-      <c r="B91" s="43"/>
-      <c r="C91" s="242" t="s">
-        <v>249</v>
+      <c r="B91" s="251"/>
+      <c r="C91" s="252" t="s">
+        <v>256</v>
       </c>
       <c r="D91" s="43"/>
     </row>
@@ -3134,221 +3214,211 @@
       <c r="A92" s="40">
         <v>46217</v>
       </c>
-      <c r="B92" s="43"/>
-      <c r="C92" s="242" t="s">
-        <v>250</v>
+      <c r="B92" s="251"/>
+      <c r="C92" s="252" t="s">
+        <v>248</v>
       </c>
       <c r="D92" s="43"/>
     </row>
     <row r="93" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="43"/>
-      <c r="B93" s="43"/>
-      <c r="C93" s="242" t="s">
+      <c r="B93" s="251"/>
+      <c r="C93" s="252" t="s">
+        <v>249</v>
+      </c>
+      <c r="D93" s="43"/>
+    </row>
+    <row r="94" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="253"/>
+      <c r="B94" s="243" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="244" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="253"/>
+      <c r="C95" s="244" t="s">
         <v>251</v>
       </c>
-      <c r="D93" s="43"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B94" s="3"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="5"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="40">
+    </row>
+    <row r="96" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="253"/>
+      <c r="C96" s="244"/>
+    </row>
+    <row r="97" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="38">
+        <v>46289</v>
+      </c>
+      <c r="B97" s="23">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C97" s="244" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B98" s="3"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="5"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="40">
         <v>45676</v>
       </c>
-      <c r="B95" s="45" t="s">
+      <c r="B99" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="41" t="s">
+      <c r="C99" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="D95" s="47"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="46">
+      <c r="D99" s="47"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="46">
         <v>45698</v>
-      </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D96" s="47"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="40"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D97" s="243" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="33"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="49"/>
-      <c r="D98" s="50"/>
-    </row>
-    <row r="99" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="40">
-        <v>46205</v>
-      </c>
-      <c r="B99" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="C99" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D99" s="47"/>
-    </row>
-    <row r="100" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="46">
-        <v>45482</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D100" s="47"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="40"/>
+      <c r="B101" s="45"/>
+      <c r="C101" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D101" s="241" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="33"/>
+      <c r="B102" s="34"/>
+      <c r="C102" s="49"/>
+      <c r="D102" s="50"/>
+    </row>
+    <row r="103" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="40">
+        <v>46205</v>
+      </c>
+      <c r="B103" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C103" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" s="47"/>
+    </row>
+    <row r="104" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="46">
+        <v>45482</v>
+      </c>
+      <c r="B104" s="3"/>
+      <c r="C104" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D100" s="47"/>
-    </row>
-    <row r="101" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="40">
+      <c r="D104" s="47"/>
+    </row>
+    <row r="105" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="40">
         <v>45672</v>
       </c>
-      <c r="B101" s="45"/>
-      <c r="C101" s="41"/>
-      <c r="D101" s="243" t="s">
+      <c r="B105" s="45"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="241" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B102" s="3"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="52">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B106" s="3"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="5"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="52">
         <v>45588</v>
       </c>
-      <c r="B103" s="53" t="s">
+      <c r="B107" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="54" t="s">
+      <c r="C107" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="D103" s="243" t="s">
+      <c r="D107" s="241" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="52"/>
-      <c r="B104" s="53"/>
-      <c r="C104" s="54" t="s">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="52"/>
+      <c r="B108" s="53"/>
+      <c r="C108" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="D104" s="55"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="56">
-        <v>45438</v>
-      </c>
-      <c r="B105" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="C105" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="D105" s="48" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="56"/>
-      <c r="B106" s="57"/>
-      <c r="C106" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D106" s="47">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="56">
-        <v>45288</v>
-      </c>
-      <c r="B107" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C107" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="D107" s="61" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="56"/>
-      <c r="B108" s="60"/>
-      <c r="C108" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="D108" s="59"/>
+      <c r="D108" s="55"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="56">
-        <v>45148</v>
-      </c>
-      <c r="B109" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="C109" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="D109" s="62" t="s">
-        <v>113</v>
+        <v>45438</v>
+      </c>
+      <c r="B109" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109" s="48" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="56"/>
-      <c r="B110" s="60"/>
-      <c r="C110" s="61"/>
-      <c r="D110" s="59"/>
+      <c r="B110" s="57"/>
+      <c r="C110" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D110" s="47">
+        <v>193500</v>
+      </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="56">
-        <v>44928</v>
+        <v>45288</v>
       </c>
       <c r="B111" s="60" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C111" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" s="47">
-        <v>24316</v>
+        <v>110</v>
+      </c>
+      <c r="D111" s="61" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="56"/>
       <c r="B112" s="60"/>
-      <c r="C112" s="61"/>
-      <c r="D112" s="48" t="s">
-        <v>108</v>
-      </c>
+      <c r="C112" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D112" s="59"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="56">
-        <v>44333</v>
+        <v>45148</v>
       </c>
       <c r="B113" s="60" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C113" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D113" s="47"/>
+        <v>112</v>
+      </c>
+      <c r="D113" s="62" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="56"/>
@@ -3357,60 +3427,100 @@
       <c r="D114" s="59"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B115" s="3"/>
-      <c r="D115" s="5"/>
+      <c r="A115" s="56">
+        <v>44928</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" s="47">
+        <v>24316</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116"/>
-      <c r="B116"/>
-      <c r="C116"/>
+      <c r="A116" s="56"/>
+      <c r="B116" s="60"/>
+      <c r="C116" s="61"/>
+      <c r="D116" s="48" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117"/>
-      <c r="B117"/>
-      <c r="C117"/>
+      <c r="A117" s="56">
+        <v>44333</v>
+      </c>
+      <c r="B117" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C117" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="D117" s="47"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118"/>
-      <c r="B118"/>
-      <c r="C118"/>
+      <c r="A118" s="56"/>
+      <c r="B118" s="60"/>
+      <c r="C118" s="61"/>
+      <c r="D118" s="59"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B119" s="3"/>
       <c r="D119" s="5"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B120" s="3"/>
-      <c r="D120" s="5"/>
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B121" s="3"/>
-      <c r="D121" s="5"/>
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B122" s="3"/>
-      <c r="D122" s="5"/>
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
+      <c r="B123" s="3"/>
+      <c r="D123" s="5"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="3"/>
+      <c r="D124" s="5"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="3"/>
+      <c r="D125" s="5"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D126" s="2"/>
-    </row>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D132" s="2"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145" s="2"/>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146" s="2"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="2"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148" s="2"/>
+      <c r="B126" s="3"/>
+      <c r="D126" s="5"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="2"/>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D130" s="2"/>
+    </row>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D136" s="2"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="2"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="2"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="2"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
